--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O743"/>
+  <dimension ref="A1:O775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47524,6 +47524,2060 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>2026-07-27T20:58:12.000Z</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuka Streamlines Travel Requests with SAP Concur AI solutions
+</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-t006CRn3v0</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-t006CRn3v0</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:26:51.000Z</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 actions pour renforcer votre leadership financier en 2026
+</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fGEK77lJ29A</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fGEK77lJ29A</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>2026-07-27T20:17:38.000Z</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How SAP Concur Scales with Your Business — Global Growth, Acquisitions &amp; Finance Transformation
+</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C0raOviYdJs</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C0raOviYdJs</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 22:11:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>PorTAL is now open for (your) business</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr"/>
+      <c r="J747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2081865015624098183</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>Ramp announces that its new 'PorTAL' platform is now open for businesses, signaling a new product launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 22:06:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>@RampLabs @thinkymachines OPEN IT UP https://t.co/4ajnIr9GBs</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr"/>
+      <c r="J748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2081863875541037419</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>Ramp announces a collaboration with Thinky Machines, teasing a new initiative or product titled "OPEN IT UP".</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 18:11:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>@axrahman See you aboard.</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+      <c r="J749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2081804678241694049</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>Leadership Changes</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>Brex welcomes new team member @axrahman aboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:50:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Nos pensées vont aux victimes des incendies en France.
+https://t.co/AsDX3PLw0V s’associe avec la Mairie de Biscarosse, la Mairie de Pontenx-les-Forges et les mairies des dix municipalités de la Communauté de communes de Médullienne pour identifier les résidents déplacés ayant besoin d'un hébergement et leur trouver un lieu de séjour gratuit. Les résidents touchés par les incendies en Gironde et dans les Landes peuvent contacter leur mairie locale pour obtenir un soutien en matière de logement.
+https://t.co/AsDX3PLw0V travaille également avec la Fédération nationale des sapeurs-pompiers de France pour fournir un logement gratuit aux pompiers déployés pour lutter contre les incendies de Gironde.
+Restez au courant des activations d'https://t.co/AsDX3PLw0V en consultant le lien ci-dessous:
+https://t.co/cspKNIywBc</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr"/>
+      <c r="J750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2081904994484461666</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>Airbnb is partnering with local municipalities and the national fire federation in France to provide free accommodation for residents displaced by fires and for firefighters deployed in the region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:50:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>As wildfires in France force people from their homes, our hearts go out to those affected.
+Our nonprofit, https://t.co/AsDX3PLw0V is working with Mairie de Biscarosse, Mairie de Pontenx-les-Forges, and the town halls of the ten municipalities in the Médullienne Community of Municipalities to identify displaced residents in need of shelter and connect them to a free place to stay. Residents affected by the fires in Gironde and Landes should contact their local town hall for housing support.
+https://t.co/AsDX3PLw0V is also working with Fédération nationale des sapeurs-pompiers de France to provide free housing to firefighters who have deployed to fight the Gironde fires.
+Stay up to date on https://t.co/AsDX3PLw0V’s response at the link below.
+https://t.co/cspKNIywBc</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr"/>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr"/>
+      <c r="J751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2081904988096487869</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>AirBnb is collaborating with French local governments and fire services to offer free housing for residents and firefighters displaced by wildfires in Gironde and Landes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Think California camping means roughing it in a crowded lot? 🌲
+➡️ Railroad Park Resort: Sleep inside a restored vintage train caboose at the base of Mount Shasta
+➡️ Treebones Resort: Swap the sleeping bag for a coastal yurt perched on the cliffs of Big Sur
+➡️ Pioneertown: Stay off-grid in a retro Airstream under the dark skies of Joshua Tree
+🔗 Plan your travel:https://t.co/wKMbuqzi9E</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr"/>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr"/>
+      <c r="J752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2081892392240623903</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>Expedia promotes unique California camping experiences featuring a vintage train caboose, a coastal yurt, and an off‑grid Airstream, encouraging travelers to book these distinctive stays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 07:37:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Hola Omid, gracias por escribirnos. Si necesitas asistencia con una reserva de alojamiento, comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr"/>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr"/>
+      <c r="J753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082007419861848491</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user with standard instructions for reservation assistance and directs them to 24/7 customer service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 07:24:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Hi there, thanks for contacting us. Although we'd like to assist you with your taxi reservation, we're unable to do so via social media. We recommend that you complete the web form available via 'https://t.co/zsciWtyp4S'. Alternatively, you can contact our specialized team, available 24/7 at +44 (0) 161 850 3290.</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr"/>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr"/>
+      <c r="J754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082004239522447484</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>Booking.com is directing a user to a web form for taxi reservations and providing a phone number for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 07:23:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Olá, agradecemos pelo seu contato e sentimos saber do ocorrido. Sentimos também saber que mantém-se à espera de um retorno. Gostaríamos de verificar a situação para você; para isso, pedimos que nos contate pelo privado com:
+• O seu número de confirmação
+• O código PIN
+• O nome do titular da reserva
+E te daremos um retorno breve. Pra suporte imediato, sugerimos que efetue contato pelo telefone com o nosso SAC 24h através de um dos seguintes números: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr"/>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="inlineStr"/>
+      <c r="J755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082003902824608055</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, offering to resolve the issue via private message or phone contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 07:20:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>@Time2897 Hi there, unfortunately we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr"/>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr"/>
+      <c r="J756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082003305652232570</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the Flights team through a link or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 06:54:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Ciao Toni, ci dispiace leggere che la pensi in questo modo del nostro servizio. Se sei cliente Genius VIP, hai diritto al nostro Servizio Prioritario VIP Genius, che ti dà accesso all’assistenza specialistica 24 ore su 24, 7 giorni su 7, con il nostro team in lingua inglese. Ti basta trovare il numero pertinente qui:  https://t.co/o8QyR8SaDb. Assicurati di avere a portata di mano il numero di conferma e il PIN. Saranno lieti di aiutarti.</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr"/>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr"/>
+      <c r="J757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081996795299672564</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint by offering VIP Genius support and providing contact details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 06:52:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Hola, Gabriela. Lamentamos la tardanza en nuestra respuesta y que hayas recibido un cargo que no reconoces. ¿Podría ser que este cargo esté vinculado a otra reserva?.
+Para poder analizar tu situación, te pedimos que nos envíes el nombre de la persona que se pone en contacto y el correo electrónico asociado a tu cuenta de https://t.co/fGhmZE7riF. Una vez que recibamos esta información, procederemos a verificar tu caso y a darle seguimiento. 
+Por otro lado, por favor envía una captura de pantalla, escaneo o foto del extracto bancario, en formato PDF, en la que se vean claramente:
+- Nombre y apellidos 
+- Correo electrónico: 
+- Importe cobrado originalmente (antes de la conversión); 
+- Captura de pantalla de los detalles del cargo (no el resumen del extracto, sino los detalles del cargo, sin que se vean otros pagos); 
+- Nombre del comerciante: 
+- 6 primeros dígitos:
+- 4 últimos dígitos de la CC: 
+- Referencia de la transacción/número de autorización: 
+- Hora/fecha de la transacción:
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr"/>
+      <c r="J758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081996271468904950</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint about an unrecognized charge, apologizing for the delay and requesting detailed information to verify the transaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 06:08:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Hola, Alison. Lamentamos la tardanza en responder y los inconvenientes que has tenido con tu reserva. No ofrecemos asistencia inmediata a través de las redes sociales.
+En https://t.co/fGhmZE7riF, la disponibilidad de habitaciones la gestiona directamente el alojamiento y es su responsabilidad mantenerla actualizada. Si un alojamiento no puede cumplir con una reserva, debería ayudarte a encontrar un lugar alternativo donde alojarte. Si no puede o no quiere hacerlo, debería informarnos lo antes posible para que podamos ayudar a encontrar una solución. En ese caso, envíanos un mensaje privado con los siguientes datos:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí:  https://t.co/o8QyR8SaDb.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr"/>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr"/>
+      <c r="J759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081985179371905095</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer complaint about a reservation, outlining its policy and offering alternative contact options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 06:08:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Agradecemos tu respuesta. Valoramos tu opinión porque nos ayuda a mejorar la calidad de nuestros servicios. Las facturas son emitidas por los alojamientos, ya que son los que ofrecen el servicio. Si necesitas la factura, puedes comunicarte con ellos a través de la reserva para solicitarla. 
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr"/>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+      <c r="J760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081985059876139241</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>Booking.com thanks a customer for their feedback and explains that invoices are issued by the accommodations, directing the customer to contact the property via the reservation to request the invoice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 05:21:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Lamentamos tu experiencia. Esperamos que hayas podido comunicar cualquier inconveniente directamente con el alojamiento mientras estabas allí, ya que son quienes están en mejor posición para abordar y resolver cualquier incidencia. 
+Si quieres que lo revisemos, envíanos un mensaje privado con la siguiente información y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles sobre tu estancia: 
+Como alternativa, para recibir ayuda inmediata, siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr"/>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="inlineStr"/>
+      <c r="J761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081973318022738355</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a customer's negative experience and provides instructions for reporting issues and contacting support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 04:08:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about this. However, we're unable to assist with Flight reservations through social media, but if you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr"/>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="inlineStr"/>
+      <c r="J762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081954958627213447</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>Booking.com informs users that flight reservations cannot be handled via social media and directs them to the Flights team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 01:33:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>@baicheyassin Hi Yassin, thank you for reaching out to us and regrettably learning this. We've sent you a private message. Kindly check it at your earliest convenience. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr"/>
+      <c r="H763" t="inlineStr"/>
+      <c r="I763" t="inlineStr"/>
+      <c r="J763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081915856997568686</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via private message, thanking them and directing them to check their DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 01:30:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Hi Yash, thank you for reaching out to us. We understand your concern, especially since the same flight itinerary seems to have been booked twice. However, we're unable to assist with flight reservations through social media, but if you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE}+353 19075677.</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr"/>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr"/>
+      <c r="J764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081915059756781911</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user about a duplicate flight booking, offering contact details for their Flights team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:43:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Hi there, thanks for reaching out to us. We regret to hear about the negative experience you encountered and your dissatisfaction with us. We’d like to hear more about what happened and how we can help. If your request is related to an accommodation booking, please DM us the following details, and we’ll get back to you as soon as possible: 
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation: 
+Please bear in mind that our Social Media Team doesn’t work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb. 
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr"/>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="inlineStr"/>
+      <c r="J765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081903311117062398</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s negative experience, requesting booking details via DM and directing them to 24/7 support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:35:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Hi Omar, thank you for reaching out to us. We understand your frustration after waiting 23 days for your refund request, especially since you bought your ticket with the WIZZ Flex option and expect the refund to follow the policy. However, we're unable to assist with flight reservations through social media. If you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE}+353 19075677.</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr"/>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="inlineStr"/>
+      <c r="J766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081901423009124817</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s refund delay complaint, acknowledging frustration but directing them to the Flights team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:03:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Hi Diksha,  thank you fof reaching out to us. We regret to hear about the inconvenience you have encountered. It sounds like your booking didn't confirm successfully, but the payment was collected. Were you charged by https://t.co/fGhmZE7riF or by the accommodation? If we've charged you, our system will recognize that the payment isn't linked to a booking and automatically refund it back. Once the refund is processed, it can take 7-12 days to reflect in your account - you should've also received an email confirming this. 
+It's also possible that you made a typo when entering your email address, as you wouldn't receive the confirmation email afterward. If you send us a private message with the following details, we'll look into our system to see if we can locate your booking:
+• Full guest name &amp; name of the person contacting us:
+• Email address used to make the booking:</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr"/>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="inlineStr"/>
+      <c r="J767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081893336533684707</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s complaint about an unconfirmed booking that still incurred payment, offering a refund and troubleshooting steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 23:10:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>@waleeddalea Hi there, we regret to hear about your concern. We acknowledge your message and would like to inform you that we have already replied to your direct message—kindly check your DM at your convenience. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr"/>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="inlineStr"/>
+      <c r="J768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081879954149576729</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s concern via direct message, acknowledging the issue and directing them to check their DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 22:26:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret to hear about your experience with our chat support. Waiting late at night for assistance only to be disconnected without explanation is understandably upsetting. 
+To help us review your account and provide the necessary assistance, please direct message us with the following details: 
+• Name of the individual contacting us 
+• Email address linked to the account 
+Additionally, kindly share a detailed explanation of your concerns regarding your account. This clarity will enable us to proceed with the appropriate actions. Thank you.</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr"/>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="inlineStr"/>
+      <c r="J769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081868947888967786</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about chat support, apologizes for the issue, and requests additional details via direct message for investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 22:22:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Hi Andrea, thank you for reaching out. We regret to hear that you’re experiencing difficulties accessing support due to login requirements. We understand how frustrating it can be when the very issue you need help with prevents you from reaching us. 
+You can call our 24/7 Customer Service Team directly - contact details are available here: https://t.co/o8QyR8SaDb. 
+If your concern is related to an accommodation booking, please DM us the following details, so we can assist you promptly: 
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation: 
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about flights, taxis, or insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr"/>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="inlineStr"/>
+      <c r="J770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081867970620379308</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s login‑related support issue, offering phone assistance and clarifying that only accommodation bookings are handled via social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 21:02:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>@shrikant535 We understand your frustration, Shrikant, but due to GDPR laws, our specialized team is the only one with access to your information.</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr"/>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="inlineStr"/>
+      <c r="J771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081847706662715531</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint by emphasizing GDPR compliance, stating that only a specialized team can access user data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 20:55:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>@LakeN8588 We understand your frustration, Nick, but due to GDPR laws, our specialized team is the only one with access to your information.</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr"/>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="inlineStr"/>
+      <c r="J772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081845927803769205</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s frustration about data access, citing GDPR restrictions as the reason only a specialized team can access the information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 18:48:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>From boutique gems to 5⭐ luxury, WINGS gives your clients more choices &amp;amp; you earn 15% commission on pre-paid hotels. Book smarter, earn more! 
+https://t.co/ctFwiJyiud #TravelAdvisor #HotelBookings #LuxuryTravel #BoutiqueHotels #EarnMore #WINGS https://t.co/StNTZjZIn3</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr"/>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="inlineStr"/>
+      <c r="J773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2081814122254254144</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes its new WINGS platform, offering a range of boutique to 5-star hotels and a 15% commission on pre-paid bookings, urging travel advisors to book smarter and earn more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 07:55:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Hi there, we would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr"/>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="inlineStr"/>
+      <c r="J774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082011995440570723</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents informs users that they can send a private message with booking details for support, but real‑time support is via a 24/7 call; social media support is limited to accommodation bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 07:48:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Hi Omukimwei, we’d be happy to review the charges further, but we’ll need some additional information first.
+Please send us a DM with more details of the charges you received. If they relate to a booking made through us, please also share the following details so we can look into this further:
+* Confirmation number
+* PIN code
+* Full name of the guest on the reservation
+Once we receive this information, we’ll review and follow up accordingly.</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr"/>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="inlineStr"/>
+      <c r="J775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082010285003440623</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is offering to review charges and requesting additional details from a customer.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2694,6 +2694,1999 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 18:51:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Watch: https://t.co/wzJ7DIVDBZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2082177073431404924</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Navan posted a video link, presumably highlighting a new product or feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 18:51:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AI when it’s faster. A human when things get complicated. No repeating yourself either way ✈️
+Navan CEO and co-founder @arielcoco joined @AnnBerry_NYC on @brewmarkets to explain how we make the handoff seamless. https://t.co/HaXzhjMfa2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2082177021082259566</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Navan showcases its AI‑driven, human‑assisted travel booking solution, emphasizing a seamless handoff and efficiency, as CEO @arielcoco discusses it on @brewmarkets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:26:02.652Z</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Your Navan x GBTA | Global Business Travel Association itinerary, mapped.
+There are so many ways to connect with us, face-to-face, all GBTA long. Here's what you need to know:
+🪩 Party @ Adler Planetarium
+→ 8/3: 7:30pm - 11:30pm
+🧠 The Giant Brain
+401 N Michigan Ave
+→ 8/3: 8am – 5:45pm
+→ 8/4: 8am – 6:15pm
+→ 8/5: 8am – 4:45pm
+👥💬 Lounge &amp; Executive Meeting Room Hours
+→ 8/3: 8am – 5:45pm
+→ 8/4: 8am – 6:15pm
+→ 8/5: 8am – 4:45pm
+See you in Chicago.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQHupy3HC9g5tA/feedshare-shrink_1280/B4EZ.u6W5pJYAM-/0/1785345962132?e=1787184000&amp;v=beta&amp;t=W_dDoSQLRbLH243kqi9X8fgTXUEV_8PTgqq_rujhGpE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_your-navan-x-gbta-global-business-travel-activity-7488283712535678976-MAK9</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Navan is partnering with the Global Business Travel Association (GBTA) to host a series of events in Chicago, providing attendees with a detailed itinerary and venue schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:01:02.311Z</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AI when it’s faster. A human when expertise matters most. One seamless experience throughout.
+Our CEO and co-founder, Ariel Cohen, explains how Navan brings AI and experienced travel agents together to give travelers the right support at the right moment. 👇</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_the-hidden-complexity-of-business-travel-activity-7487945230772731904-C1_x</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Navan showcases its hybrid AI and human travel agent model, emphasizing a seamless experience that delivers expert support at the right moment for travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 17:02:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Find all the details and grab your ticket: https://t.co/RmB1Nvt7M0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082512047816749431</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Brex is promoting an event and encouraging followers to grab tickets through a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 17:01:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Feeling extremely bullish about this partner lineup.
+@theziphq, @Meet_campfire, Vat IT, @RilletHQ,  Zensuite Partners, @Navan, and @zanovoy are joining us for the intelligent finance summit. https://t.co/elsvEvD1hS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082511828433735822</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Brex announces a lineup of partners for its Intelligent Finance Summit, expressing bullish optimism about the collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 19:19:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>@zachdotai @pedroh96 ☕🤝</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082184093823893653</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Brex acknowledges a meeting or collaboration with @zachdotai and @pedroh96, indicating a potential partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 19:11:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://t.co/sOYfRlHUa0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082182236598882814</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Brex posted a link to an external resource, likely related to company updates or industry news.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Think you need to cross the globe for dramatic volcanic coastlines? The real magic is in Madeira 🇵🇹
+➡️ The Trails: Brave the glass-floored skywalk at Cabo Girão and hike above the clouds at Pico do Arieiro
+➡️ The Sea: Swim in Porto Moniz’s natural saltwater pools formed by ancient volcanic rock
+➡️ The Stays: Skip the standard hotels and fall asleep in a luxury cliffside resort surrounded by lush botanical gardens
+🔗 Plan your travel: 
+https://t.co/uOAMMGVZLQ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2082254780387201504</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Expedia promotes Madeira as a must-visit destination, highlighting its volcanic coastlines, skywalks, natural pools, and luxury cliffside resorts to entice travelers to book through their platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 17:26:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>@MissAwori Hi there, thank you for reaching out to us. If you still need assistance, kindly send us a private message. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082518190966362545</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, offering further assistance via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 15:47:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>@PratapGaur53688 Hello Gaurav, we regret to hear about your experience. We've sent you a DM with more information regarding your case. Please review it and get back to us. Regards</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082493298619355546</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint via direct message, offering further information and requesting a review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 15:09:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>@rapolasbernotas Hello there, we regret to hear about your experience. Please note that situations like the one you mentioned may require cancellations to issue refunds. However, we've sent you a DM with more information regarding your case. Please review it and get back. Regards https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082483740333179278</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for a negative experience and directs them to a DM with further information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 13:29:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>We understand why it may feel unfair when different users see different prices or promotions for what appears to be the same stay.
+Genius discounts are set by the accommodation and can vary by property and by Genius level. At the same time, other promotions are separate and may follow different conditions, which can result in different users seeing different deals.
+This does not indicate an issue with your account, but reflects how individual properties and separate promotions are configured across the platform.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082458505814978960</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies that price differences arise from Genius discounts and separate promotions, not from account issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 13:05:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>@sofiahayat Hi Sofia. We're here to help. Please send us a private message with the following details of your booking:
+- Confirmation number
+- PIN
+- Name on the reservation
+And we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082452526587076773</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user’s inquiry by requesting booking details for customer support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 13:00:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hi Zoe, we regret to hear, that you still did not get a resolution through our Customer Service Team. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082451139123941443</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a customer for an unresolved issue and requests booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:59:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Hi Elsie, as said in our previous messages, we are here to assist you as long as you can share a brief summary of your claim and provide the following details in DM: 
+- booking number
+- pin code
+- full name of the guest on the reservation
+Once we receive this information, together with your request, we'll follow up as soon as possible.
+Please note that we cannot share details of our CEO due to confidentiality but we're here to assist you. 
+Regards</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082451026062266601</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer’s claim request, asking for booking details while noting confidentiality limits on sharing executive information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:35:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>@4134emsie As much as we would like to support you here, due to GDPR laws, only our specialized Flight team has access to your details and tools to assist you.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082444987380203848</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that GDPR restrictions limit support to their specialized flight team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:35:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>@NairSatyjeet Hi there,
+We regret to hear that you did not receive your refund and be happy to look into the status for you. In order to do so, please send us a DM with your:
+- pin code
+- name on the reservation https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082444940835963307</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about a missing refund, offering to investigate via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:31:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Hi Emma, thanks for contacting us. Although we'd like to assist you with your Taxi reservation, we're unable to do so via social media. We recommend that you complete the web form available via 'https://t.co/zsciWtyp4S'.  Alternatively you can contact our specialized team, available 24/7 on +44 (0) 161 850 3290.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082443981007249418</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user about a taxi reservation, directing them to a web form or phone contact for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:09:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Hi Sydney, we regret to hear that you're still waiting for your cash credits to be paid out. 
+For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082438427807515073</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a customer for a delayed cash credit payout and requests booking details via direct message for investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:08:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Merci pour votre retour. Comme nous l'avons indiqué dans notre message précédent, afin de vérifier votre dossier, nous vous invitons à nous communiquer uniquement en message privé pour des raisons de confidentialité :
+- le numéro de confirmation
+- le code confidentiel
+- le nom complet du voyageur
+Nous reviendrons ensuite au plus vite vers vous mais gardez à l'esprit que notre équipe des réseaux sociaux ne fonctionne pas en temps réel.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082438009182445889</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer on X, requesting private details for verification and noting that social media responses are not real-time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:02:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>@markhedger9019 Hi Mark, thanks for contacting us.
+We regret hearing you were unable to stay in the hotel you booked.
+Please send us the following details via DM: 
+- Confirmation number, 
+- Pin code, 
+- Full guest name,
+and we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082436511711076436</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about a hotel booking, requesting confirmation details via DM to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:01:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>@stewbrophotos Hello there, we regret hearing about this. In order to review your case, please DM us the Confirmation number, Pin code, and Name on the reservation. We will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082436358711165046</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint by asking for confirmation details via direct message to review the case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:55:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Oi Samuel, bom dia! Tudo bem? Agradecemos pelo contato. Nossos parabéns pela sua uniao, mas infelizmente não estamos oferecendo cupons de desconto no momento, mas você pode sempre encontrar as melhores tarifas disponíveis no nosso site/app por aqui:  https://t.co/KhsdMZU0ZC — esperamos que encontre algo que goste. Desejamos uma ótima continuação de semana!</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082434912640966921</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Booking.com politely declines a user’s request for a discount, directing them to the site/app for the best rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:47:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Hi Alexy, thanks for reaching out to us.
+We regret hearing about your discontent with our customer service team. The fastest way to receive support is by calling (https://t.co/o8QyR8SaDb).
+Alternatively, our social media team can help as well.
+You can always send us a DM and share the following details: 
+- Confirmation number, 
+- Pin code, 
+- Full guest name,
+- Your request, 
+and we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082432792684601606</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering phone and social media support and requesting specific details to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:45:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bonjour, merci de nous interpeller ici. Nous sommes navrés de lire que votre réservation a été impacté par cette situation.
+Vous pouvez annuler votre réservation depuis votre e‑mail de confirmation, notre application ou le site web de https://t.co/fGhmZE7riF. Les conditions que vous avez sélectionnées au moment de la réservation s’appliqueront. Chaque établissement gère ses propres conditions, donc lorsqu’une annulation est demandée en dehors de ces conditions, seul l’établissement peut l’approuver à titre d’exception, par confirmation écrite.
+Nous serons ravis de contacter l’établissement en votre nom si vous nous envoyez un message privé avec les informations suivantes :
+- Numéro de confirmation:
+- Code confidentiel:
+- Nom indiqué sur la réservation:
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082432239988580509</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for reservation disruptions and provides instructions for cancellation and how to request exceptions, offering to contact the property on the customer's behalf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:36:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>@Virg1_979 Bonjour Virginie! Nous avons bien reçu votre message privé et nous venons à l'instant de vous répondre, nous vous invitons à le consulter dès que vous aurez un moment.
+Merci à vous ! https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082430125161828499</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, acknowledging receipt and inviting them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:14:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Thank you for reaching out to us, Lynn. We regret to hear the property wasn’t able to accommodate you. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+If a property can’t honor a booking, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution. Please send a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082424595353592281</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint about a property failing to accommodate a booking, apologizes, and outlines steps for resolution and support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 10:35:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gracias por contactarnos y lamentamos los inconvenientes que esta situación te haya podido causar. En https://t.co/fGhmZE7riF, la disponibilidad de habitaciones la gestiona directamente el alojamiento y es su responsabilidad mantenerla actualizada. 
+Si un alojamiento no puede cumplir con una reserva, debería ayudarte a encontrar un lugar alternativo donde alojarte. Si no puede o no quiere hacerlo, debería informarnos lo antes posible para que podamos ayudar a encontrar una solución. En ese caso, envíanos un mensaje privado con los siguientes datos: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082414629515391413</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizing for inconvenience and outlining steps for resolving reservation issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 16:44:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Discover what Sky Bird’s valued clients have to say about their booking experience!
+If you want to be featured next, then leave a review on Facebook or Google, here: https://t.co/5Iiq1ApRVA!
+#SkyBird #AirlineConsolidator #AirlineWholesaler #FlightColsolidator #Testimonial https://t.co/BTgoCz1YK1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2082507472993161459</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes customer testimonials and invites clients to leave reviews on Facebook or Google, showcasing positive booking experiences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-07-29T16:43:49.045Z</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Discover what Sky Bird’s valued clients have to say about their booking experience! 
+If you want to be featured next, then leave a review on Facebook or Google, here: bit.ly/4hJsABc! 
+#SkyBird #AirlineConsolidator #AirlineWholesaler #FlightColsolidator #Testimonial #Review</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5622AQFGLmHwSQJdeA/feedshare-shrink_1280/B56Z.uwsTpGUAM-/0/1785343428142?e=1787184000&amp;v=beta&amp;t=jDGx4OcG5ZK56VcE93Aggcko0d5im2GHeth-Yt9PL-w</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_skybird-airlineconsolidator-airlinewholesaler-activity-7488273085817647104-CYl0</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel is encouraging its clients to leave reviews on Facebook or Google in hopes of being featured next, highlighting its focus on customer feedback and brand visibility.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4687,6 +4687,2029 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:44:00.266Z</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Last week, we introduced Entry Ready: Perk is now the first AI-native travel and spend management platform to integrate visa applications and purchase at the point of booking. ✨
+In this video, our Chief Product Officer, Nikita Miller explains how Entry Ready automatically identifies requirements, guides travelers to the right option, and lets them apply and pay without leaving Perk.
+Built end to end by our Real Work Incubator team, Entry Ready is another step toward removing shadow work from work travel.
+Learn more: https://okt.to/CLoKri.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQEBoyCjoSfvsg/mp4-720p-30fp-crf28/B4EZ.zQ9nzH4Bk-/0/1785419008418?e=1786042800&amp;v=beta&amp;t=rbbs6T9S0uwdtM6Ar1vtS0K0SdUXHelEtor2PuEHicM</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_last-week-we-introduced-entry-ready-perk-activity-7488590222264463361-qT-_</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>TravelPerk unveiled Entry Ready, an AI-driven feature that automatically handles visa requirements and payments during booking, aiming to eliminate shadow work in business travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 04:22:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>@hamidships https://t.co/ltJ5C9NzX1</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2082683114183123290</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Ramp shares a link to @hamidships, indicating a potential partnership or collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 15:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Your team's time is worth more than chasing a $40 Uber receipt. Act like it.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082843662807888050</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Brex highlights the importance of valuing team time over minor expenses, urging companies to prioritize efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 12:32:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>@chrisdndx @mshuffett A full house for founders? We'd do it again.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082806543293059160</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Brex expresses enthusiasm about a recent initiative or event for founders, indicating satisfaction and a willingness to repeat it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 19:37:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>@youdotcom @Meta @composio @Stanford Stacked is an understatement.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082551174922752008</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Brex highlights a collaboration with YouDotCom, Meta, Composio, and Stanford, describing the partnership as "Stacked is an understatement," indicating a significant joint effort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 22:18:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://t.co/AlJ3K70h6Y is providing emergency housing to Madrid and Ávila residents displaced by the wildfires, in partnership with Mensajeros de la Paz. Stays are completely free for guests and funded by https://t.co/AlJ3K70h6Y.
+https://t.co/v3gZktfL4J https://t.co/XlJQUpvuel</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2082591529378693530</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Airbnb is partnering with Mensajeros de la Paz to provide free emergency housing to residents displaced by wildfires in Madrid and Ávila, funded by Airbnb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:30:17.000Z</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Who’s gonna tell him he could just list his space on Airbnb? 👀</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://scontent-ord5-2.cdninstagram.com/v/t51.82787-15/758707304_18618482614063838_1970535724819002567_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gEicR_eY5gN7Z04RTv2Ti1vAqbIhVT0qtQGvF3JqHj6U0AmCZ93JKjD9xa3NSA8xZFgHKVW08u7yaza8AzwmXXg&amp;_nc_ohc=0djIQ73x1_MQ7kNvwFjTY37&amp;_nc_gid=G9D9X2gqGY-uunaEJ8LHsQ&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQGYbEed2sR9PFOlx3bRQThXRpVpLhSxdcpP9aKXybBU7Q&amp;oe=6A717A35&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m86/AQPsaXMfHzHPbWRY8qcTQbPOSpza6vZ7piQ1Pli7HAgSsZWfCL87k9c8L02x35nJIVcxt7g6ceJ8YhqcGqcKLlMkaPxIPEyn2aMsumU.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=X3zi2p0xqesQ7kNvwFiv-hS&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTAxNjcxNTU4NDQ4OTMxNiwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjoxOSwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=fef22a0eff5e9f6b&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC82QTQ2MDNENzU5MUE0NEZEN0VFMkZFMDdGN0ZERDdBQl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q2NDQxNTYyQUJBMzIzMkRDNzNBNkY0RDA5ODFGMkFGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbInYK00azOAxUCKAJDMywXQDNVP3ztkWgYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=G9D9X2gqGY-uunaEJ8LHsQ&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQGBgi_vByZeRpyd4zcHSbEfZ8RBtGkRv_d6Oil1D4NzKA&amp;oe=6A6D5858</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbbA1ZmxCJy/</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Airbnb promotes the idea that anyone can list their space on the platform, encouraging new hosts to join.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Airbnb.org</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:28:47.675Z</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>To support Madrid and Ávila residents who lost their homes or had to evacuate due to the wildfires, Airbnb.org is working with the Asociación Mensajeros de la Paz to offer emergency housing. Stays are completely free for guests and are funded by donations to Airbnb.org.
+Stay up to date and learn how to get and give help: airbnb.org/spain 
+____
+Airbnb.org colabora con la Asociación Mensajeros de la Paz para ofrecer alojamiento de emergencia a los residentes de Madrid y Ávila que han perdido su hogar o han sido evacuados por los incendios. Las estancias son completamente gratuitas para los huéspedes y se financian gracias a las donaciones a Airbnb.org.
+Para más información y descubrir cómo recibir y ofrecer ayuda, visita: airbnb.org/spain</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/airbnb-dot-org_airbnborg-is-providing-free-emergency-housing-ugcPost-7488357115653160960-GYXC</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Airbnb.org partners with Asociación Mensajeros de la Paz to offer free emergency housing for Madrid and Ávila residents displaced by wildfires, funded through donations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Think the ultimate escape is a crowded beach resort? The real adventure is in Tanzania. 🇹🇿
+➡️ The Wildlife: Watch the sunrise over the Serengeti as elephants wander past your jeep
+➡️ The Coast: Sail a traditional wooden dhow across the turquoise waters of Zanzibar
+➡️ The Stays: Skip standard hotels and sleep in a luxury canvas safari tent under the stars
+🔗 Plan your travel: 
+https://t.co/e9cJb6143x</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2082617168760275415</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Expedia is promoting Tanzania as a prime travel destination, showcasing wildlife, coastal experiences, and luxury canvas safari tents to entice bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:07:38.479Z</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Barcelona’s calling.🇪🇸
+Whether you’re dreaming of Gaudí’s whimsical architecture or a tapas crawls through the Gothic Quarter, Barcelona blends big‑city culture with relaxed Mediterranean charm. 
+Explore Barcelona stays and things to do on Expedia: http://ms.spr.ly/6040a6cqI</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_visit-barcelona-activity-7488611270175244288-kJLO</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Expedia promotes Barcelona travel packages, highlighting attractions and encouraging bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 15:08:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Hola Luis, gracias por contactarnos. Ten en cuenta que los precios que aparecen en nuestra plataforma son establecidos por los propios alojamientos; deben respetar el precio indicado en tu correo de confirmación. Sin embargo, si existiera una diferencia importante en el precio y se tratara de un error evidente, dicho precio podría no ser vinculante. En esos casos, el alojamiento puede solicitar la cancelación de la reserva.
+Si deseas que lo revisemos, envíanos por favor un mensaje privado con los siguientes datos:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082845817279287381</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Booking.com explains that accommodation prices are set by hosts and may not be binding if there is a significant discrepancy, and directs customers to provide confirmation details for review while noting that social media support is not real-time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 14:47:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bonjour Jean-Christophe, merci de nous contacter ici. Nous sommes navrés d'apprendre que votre séjour ne se passe pas comme prévu.
+Pour que nous puissions nous renseigner davantage sur la situation, nous vous invitons à nous communiquer, uniquement en message privé pour des raisons de confidentialité :
+- le numéro de confirmation
+- le code confidentiel
+- le nom complet du voyageur
+Nous reviendrons ensuite au plus vite vers vous mais gardez à l'esprit que notre équipe des réseaux sociaux ne fonctionne pas en temps réel.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082840467956175032</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizing and requesting private details for further investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 13:55:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>@ShubhamTanlek Hi Shubham Taneja, we see that our colleagues sent you a private message a few days ago regarding this and asked for more information in order to assist you. Please review it and reply to us, so we can check it for you further.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082827490897052139</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to a user, asking them to review a previous message for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 13:28:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Hi Conchy,
+As the accommodation is providing you with the service and receiving payment, only they can provide you with an invoice. You can request your invoice during your stay, upon check-out, by email, or by calling the phone number provided in your confirmation email. If you'd like us to request this on your behalf, please send us a private message with the following details:
+Confirmation number:
+Pin code:
+Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082820543347032340</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user how to obtain an invoice for their stay, offering options to request it during or after the stay, or via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 13:09:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>@KhojaShahzad Hi Shahzad, safety and security of our platform is always our top priority. Please note that we are unable to provide any information in public. Feel free to send us a private message if you have any other questions.
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082815788839305677</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Booking.com emphasizes its commitment to platform safety and security, stating it cannot share details publicly and encourages private inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 13:05:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Hola Mariela, sentimos escuchar que tienes esta opinión acerca de nuestro servicio.
+Si necesitas asistencia con el reembolso de una reserva de alojamiento, comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082814727751614635</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a refund, providing instructions for private messaging and directing to 24/7 support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 12:01:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082798614053560371</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, requesting booking details for review and directing the user to 24/7 phone support, noting limited social media support for accommodation bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 11:57:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Hi Ceylan, we regret that you have issues with your reservation. However, we recommend that you never share the details of your reservation in public as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment. Please send a private message, so we can check it for you further.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082797852300878271</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s complaint about reservation issues, advising them to keep details private and to send a private message for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 11:43:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>We regret to learn about your experience, Peter. We hope you had the chance to report any issues directly to the property during your stay, as they are in the best position to handle and resolve any concerns. 
+To assist you further, please send us a direct message with the following details (you should now be able to reach us privately): 
+- Confirmation number 
+- PIN code 
+- Name associated with the reservation 
+We will respond to you as quickly as we can.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082794230250897437</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizing and directing the user to contact the property directly while offering to assist via direct message with reservation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 11:33:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Hola Pepe, gracias por escribirnos. Sentimos escuchar que tu reserva ha sido cancelada.
+No tenemos información precisa sobre lo sucedido con tu reserva, sin embargo, nos gustaría revisarlo para brindarte una respuesta y determinar cómo podemos ayudarte.
+Comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082791733499162998</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user about a cancelled reservation, offering to review the issue and providing contact details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 10:36:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>@tjfp57 Hi Timothy, we regret to hear that your still waiting for your refund. 
+For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082777426111733803</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Booking.com is addressing a user’s refund issue by requesting booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 10:33:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>@lCqnl1dq7QGnGJN Hi there, we regret to hear about the situation you’ve described. To assist you, please send us a DM with the following information, and we will get back to you as soon as possible: 
+- PIN code 
+- Full name of the guest confirmed on the reservation https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082776541360959926</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint via direct message, requesting PIN code and guest name for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 09:09:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>We are saying that the reviews can help you to take a decision before choosing an accommodation as they were left by previous travelers that stayed there. If you wanna know more about how guest reviews work, please check the information provided here: https://t.co/CM3ktXsoZb, and if you'd like us to check your booking, please DM us with the information requested in our previous message. Thank you.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082755370615730385</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Booking.com highlights the value of guest reviews for booking decisions and invites users to learn more or request booking assistance via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 09:08:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Sentimos que tengas esa impresión de nuestros servicios, Seba. ¿En qué podemos ayudarte? Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb
+Además, por el momento solo ofrecemos soporte para reservas de alojamiento a través de las redes sociales. Para preguntas sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí: https://t.co/TBejpc4vOA
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082755205880299963</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s concern on X, offering private message support for accommodation bookings and directing other inquiries to dedicated teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 08:36:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lamentamos que el hospedaje no tenga calefacción. Si quieres que lo revisemos, envíanos un mensaje privado con la siguiente información: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+Te responderemos lo antes posible. Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082747048063869089</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a property lacking heating and invites customers to send a private message with booking details or call for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 08:21:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Hi Samir, thanks for contacting us.
+We regret hearing the accommodation didn't fulfil your expectations.
+We recommend checking the guest reviews before booking, that way you get a good insight on the overall quality of the accommodations.
+Refunds can only be approved by the accommodations themselves, as the policies belong to them. We can share guest complaints with them to try to negotiate a solution on their behalf.
+If you received compensation from our colleagues, this would be a separate offer from us, and not in relation to the refund request you had.
+While we might not be able to provide you with a different outcome, but we can take a look at your booking if you DM us  the following details: 
+- Pin code, 
+- Full guest name</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082743306887270586</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizes, explains refund policy, and offers to review booking details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 07:33:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>@dutta050 Hi there, we regret to hear about the payment you were asked to pay.
+In order for us to check your reservation, please send a private message with your:
+- confirmation number
+- pin code and 
+- the name of the guest.
+Looking forward to hear from you.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082731253212537257</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a payment issue, requesting confirmation details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 05:26:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Olá Agda, lamentamos em saber do ocorrido. Nós gostaríamos muito de poder ajudar, no entanto, a equipe de redes sociais oferece suporte apenas para reservas de acomodação. Para qualquer assunto referente a uma reserva de voo, pedimos que entre em contato com a equipe dedicada para o suporte através do telefone 11 4700 8306.
+Se preferir enviar uma mensagem, por favor, siga estes passos:
+» Clique neste link: https://t.co/nBevMHsVrX
+» Faça o login na sua conta de usuária e clique na sua reserva de voo 
+» Na página "Como podemos te ajudar?", selecione o tópico com o qual precisa de ajuda, (por exemplo, "Alterações e cancelamentos")
+» Clique em "Mais opções de contato"
+» Nesta etapa, você tem a opção de administrar a sua reserva ou de enviar uma mensagem para o SAC.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082699318721388825</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a flight booking issue and informs the user that its social media team only supports accommodation reservations, directing them to a dedicated flight support line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 01:32:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret to hear about the difficulties you’ve experienced while trying to reach us and being routed only to AI. We understand how important it is for you to receive direct assistance from a human representative. How may we assist you? Please provide further details regarding your concern and the circumstances of it. If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible:
+Confirmation number: 
+Pin code: 
+Name on the reservation: 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb. 
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082640415040164251</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about difficulty reaching support, apologizes, offers assistance, and directs users to appropriate contact channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 01:13:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret to hear about the difficulties you’ve experienced while trying to request a travel voucher for your flight to Bordeaux. We understand how frustrating it must have been to spend so much time going back and forth with support. As much as we’d like to assist you, we’re unable to assist with flight reservations through social media. If you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082635675027820650</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer complaint about difficulties obtaining a flight voucher, directing them to dedicated support channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-07-30T08:00:03.895Z</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>At Booking.com, we believe that connection drives collaboration. 💬✨
+To kick off World Pride in Amsterdam, all six of our Employee Resource Groups (ERGs) came together for the very first time for United in Pride. This milestone event brought B.proud and our wider ERG community together under one roof to connect, collaborate, and celebrate as one.
+By combining our unique perspectives, talent, and mutual respect, we aim to create an inclusive environment where everyone can perform with confidence and show up as their fullest selves.
+Events like this remind us that when we support each other and build trust across our teams, we win as one team because here, everyone means everyone. 💙🌈</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQGM9ZkJKp7tSA/image-shrink_1280/B4EZ.vBaoHK8Ac-/0/1785347812701?e=1786042800&amp;v=beta&amp;t=OwyR0Cb2JHRgJtUsRPLjs8AsWp9U6uQ7sv5n1BsldTI</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_at-bookingcom-we-believe-that-connection-activity-7488503667051003905-_5wl</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Booking.com announced its first joint event among six Employee Resource Groups to celebrate World Pride, emphasizing inclusion, collaboration, and a supportive workplace culture.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6710,6 +6710,1679 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-07-31T08:01:08.693Z</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>"You look happier." Thanks, since using Perk MCP, my AI assistant finds the answers I need in seconds.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQEoPjovjRiIMg/image-shrink_1280/B4EZ.3MFg.HsAg-/0/1785484827022?e=1786129200&amp;v=beta&amp;t=7gLd0o6R6tJKQh0neg2AWvhxxK9wXQCLH6fDdhmBhjs</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_you-look-happier-thanks-since-using-perk-activity-7488866326699024386-si5V</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>TravelPerk highlights the effectiveness of its Perk MCP AI assistant, noting it quickly provides answers, showcasing a positive user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 03:27:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>@mlg27_ Big dogs rejoice</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2083031887279206760</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Ramp posts a brief, upbeat remark suggesting a forthcoming development that will benefit large companies, but no specific details are provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 14:35:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>FYI, nobody starts a company because they love categorizing transactions</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2083199755480658305</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Brex comments that categorizing transactions is not a primary motivation for starting a company, implying a critique of such focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Think the ultimate winter escape is a crowded Alpine ski resort? The true edge of the world is Svalbard 🇳🇴
+➡️ The Wilderness: Spot wild polar bears roaming the frozen tundra as you glide across majestic glaciers on a snowmobile
+➡️ The Sky: Chase the dancing green ribbons of the Northern Lights through the endless, mesmerizing polar night
+➡️ The Stays: Skip standard hotels and warm up in a historic, beautifully repurposed coal miner's cabin
+🔗 Plan your travel: 
+ https://t.co/OSrphBXmR9</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2082979557980721645</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Expedia promotes Svalbard as a unique winter escape, highlighting polar bears, Northern Lights, and historic cabin stays to attract adventurous travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 17:53:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>@lakesalford Hi Stephen, we have sent you a reply via direct message. Please review it for more details. Thank you.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083249714338636221</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to a user, likely for follow-up or support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 17:20:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>@ToonTownDano We're happy to help. Feel free to reach out to us again if you have any other questions.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083241304364847504</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, offering help and encouraging further contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 17:14:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>@ved1985prakash3 Hi there, we acknowledge your concerns and recognize the significance of this matter to you. We kindly request that you send us a private message to facilitate a more in-depth discussion. Thank you for your patience and cooperation.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083239842742243512</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s concerns, inviting them to send a private message for a more detailed discussion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 17:13:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Hi Ahmet,
+Thank you for your message. We regret the inconvenience and stress this situation has caused you, especially after arriving at the property and learning that your reservation could not be honored due to a reported major leak. We understand how frustrating it must have been to arrange emergency accommodation at a significantly higher cost and then wait such a long time for an update regarding your formal complaint.
+The availability of rooms is managed directly by properties, and they're responsible for ensuring their inventory is accurate. If a property is unable to honor a reservation, they should assist guests in finding alternative accommodation. If they're unable or unwilling to do so, they should notify us as soon as possible, so we can help find a solution.
+In order for us to review your case and check the status of your complaint, kindly send us a private message with the following details:
+• Confirmation number:
+• PIN code:
+• Name on the reservation:
+We'll get back to you as soon as possible. Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083239664895320167</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a major leak that prevented a guest’s reservation, offers to resolve the issue, and requests private details to investigate the complaint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 14:00:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>@BrendanfFoster Hi Brendan, thanks for contacting us.
+We are here to help. Please share more details regarding your request, and what you need help with. We're unsure what you mean.
+We will reply as soon as we can.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083191091390468103</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry, offering further assistance and indicating they will respond soon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 12:53:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Hi Pranav, thanks for contacting us.
+We checked this property page and see it now states that pets are not allowed. It's a new property, it appears they had set this up incorrectly. However, it is now corrected from what we can see.
+If you had a booking with them, we can still reach out to them on your behalf. Feel free to DM us the following details:
+- Confirmation number, 
+- Pin code, 
+- Full guest name,
+and we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083174242607128830</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Booking.com addressed a user’s concern about a pet policy on a new property, confirmed the issue was corrected, and offered assistance with bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 11:47:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Hello Sharon, thank you for your message. 
+We are unclear about what you mean by that. You can still reserve rooms at hotels as usual. Various policies are in place, and if you opt for a flexible booking, you can change or cancel it at no cost until the specified cut-off date. There have been no changes in that respect. 
+Wishing you a wonderful day.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083157674091303006</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Booking.com confirms that flexible booking policies remain unchanged and encourages customers to continue reserving rooms as usual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 11:38:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>@lakesalford Hi there, we have just emailed you back. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083155225569833129</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, informing them that an email has been sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 11:30:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>@Soundie29 Hi Sean, we're unable to assist with flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE}+353 19075677. Best regards.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083153434417443074</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the Flights team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 10:21:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Hola, Francisca. Lamentamos los inconvenientes que estás experimentando con tu reserva. En https://t.co/fGhmZE7riF, la disponibilidad de habitaciones la gestiona directamente el alojamiento y es su responsabilidad mantenerla actualizada.
+Si un alojamiento no puede cumplir con una reserva, debería ayudarte a encontrar un lugar alternativo donde alojarte. Si no puede o no quiere hacerlo, debería informarnos lo antes posible para que podamos ayudar a encontrar una solución. En ese caso, envíanos un mensaje privado con los siguientes datos:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí:  https://t.co/o8QyR8SaDb.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083136064017793257</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s reservation issue, apologizing and offering direct assistance and contact options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 10:16:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Bonjour, merci de nous avoir contactés. Nous regrettons de lire votre opinion sur nos services. Afin de pouvoir comprendre la situation et de nous permettre d'accéder à votre dossier, merci de nous envoyer, uniquement en message privé pour des raisons de confidentialité : 
+- Un récapitulatif de la situation 
+- Votre numéro de réservation 
+- Votre code confidentiel 
+- Le nom complet du voyageur sur la réservation. 
+Nous reviendrons ensuite vers vous dès que possible. 
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083134790702600362</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer complaint, asking for private details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 09:41:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>@alittlelateto Hi there, we regret to hear that your booking needed to be cancelled. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083125799905845489</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user about a cancelled booking, requesting booking details via DM for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 09:01:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Hola Samuel, gracias por escribirnos. 
+Con gusto revisaremos tu cuenta para ver lo que ha sucedido y cómo podemos asistirte. Para ello, compártenos por DM tu correo electrónico y nombre completo y te responderemos tan pronto sea posible.
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083115871317233787</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user’s account inquiry, offering to review the issue and directing them to 24‑hour customer support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 08:50:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Hi Purity, we regret to learn that you are unable to reach our Customer Service team. 
+How can we help? Could you explain what happened?
+If you need assistance with an accommodation reservation, please share with us in a private message:
+- reservation number 
+- PIN code 
+- guest name on the reservation, 
+along with an explanation of what you require assistance with. 
+If you require assistance with a https://t.co/fGhmZE7riF account, please confirm in DM:
+- your full name 
+- email address linked to the account. 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/tuuNbmGVaG. 
+Best regards</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083113171091357901</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering private message assistance and providing contact details for further support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 08:40:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Hola, Manuel. Lamentamos que tu reserva haya sido cancelada. En https://t.co/fGhmZE7riF, la disponibilidad de habitaciones la gestiona directamente el alojamiento y es su responsabilidad mantenerla actualizada. 
+Si un alojamiento no puede cumplir con una reserva, debería ayudarte a encontrar un lugar alternativo donde alojarte. Si no puede o no quiere hacerlo, debería informarnos lo antes posible para que podamos ayudar a encontrar una solución. En ese caso, envíanos un mensaje privado con los siguientes datos: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083110463638741012</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a cancelled reservation and offers assistance to find alternative accommodation, providing contact details for support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:48:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Hola, Mochi. Lamentamos que sigas a la espera de tu reembolso. Aunque nos gustaría, no podemos ayudarte con reservas de Vuelos a través de las redes sociales, pero puedes contactar con nuestro equipo de Vuelos aquí: https://t.co/TBejpc4vOA, o llamar al +34918362949 desde España de lunes a domingo de 9:00-21:00 hora local.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083097503944024414</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed refund and directs the user to contact flight support via a link or phone number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:24:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>@tony_vatoloco - Numéro de confirmation :
+- Code confidentiel :
+- Nom indiqué sur la réservation :
+- Détails concernant votre séjour :
+Pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083091523059483006</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Booking.com appears to be targeted by a phishing scam that mimics booking confirmation messages, potentially misleading users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:24:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>@tony_vatoloco Nous regrettons de lire votre déception concernant le fait que vous soyez encore en attente de votre remboursement. Afin que nous puissions vous assister ici, merci de nous envoyer un message privé avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083091421624447449</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for a pending refund and requests a private message with details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:24:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>@tony_vatoloco Bonjour Tony, toutes nos excuses pour ce délai de réponse.
+Nous recevons actuellement un volume important de demandes sur les réseaux sociaux, ce qui ne nous a pas permis de vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083091365303308559</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to user Tony for a delayed response due to a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:20:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>@FLYINGSMCOIN Hi there, we regret to hear about your experiences. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083090321114546343</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint on X, asking for booking details via DM to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 16:16:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Skip the luggage hassle with BagDrop! ✈️🧳 Your bags go Airport → Home, securely delivered so you enjoy the journey stress‑free.
+#TravelMadeEasy #BagDrop #IndiaTravel #SkyBird #TravelSmart https://t.co/xcODGHDOYR</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2083225269322866703</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes its new BagDrop service, offering secure luggage delivery from airport to home to simplify travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-07-31T16:15:21.233Z</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Help your clients skip the stress of traveling with heavy luggage by booking BagDrop’s Airport-to-Home Baggage Delivery service. Their bags are picked up, securely handled, and delivered straight to their destination—so they can focus on enjoying the journey. 
+Offer your clients a smoother travel experience from the moment they land. 
+#TravelMadeEasy #TravelAdvisor #BagDrop #IndiaTravel #BaggageDelivery #SkyBird #TravelSolutions #TravelSmart</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5622AQFxZAkGc1JZsw/feedshare-shrink_1280/B56Z.49WtTHYAM-/0/1785514520155?e=1787184000&amp;v=beta&amp;t=qDI_yuyQA8Agj_sfkTXxgwFvKy4HD-AwPYnhcEORI6w</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_travelmadeeasy-traveladvisor-bagdrop-activity-7488990698466365441-OjSk</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel highlights BagDrop’s Airport-to-Home Baggage Delivery service, positioning it as a hassle‑free solution for clients’ luggage.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8383,6 +8383,1538 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>brex</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-08-01T17:26:23.000Z</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>🛹
+-
+-
+-
+-
+#accord #honda #hondaaccordsport #hondaaccord2021 #accordsport accordnation 10thgenaccord hondaaccord viral stancelife cars stance jdm jdmcars jdmculture hondaaccord turbo10thaccord genaccord accordsociety accord airsuspension gen yofer yoferdesign 10thgenaccord
+accord honda hondaaccordsport hondaaccord2021 accordsport accordnation 10thgenaccord hondaaccord staticlife viral staticlyfe stancelife statio bmw cars stance jdmcars jdmculture hondaaccord
+turbo10thaccord genaccord accordsociety accord airsuspension</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://scontent-mad2-1.cdninstagram.com/v/t51.82787-15/763357145_18149903689509920_1716742566318186375_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_cat=108&amp;_nc_oc=Q6cZ2gHpJg2oe_5P-EhNOGzLHzu7tHz11IuuN0_6-ftzYeBFxatAt34ItTIxey9BxciU26w&amp;_nc_ohc=tuKI39YReFYQ7kNvwFOnzS8&amp;_nc_gid=H0XJ6mdR2FIwgxwrPnXPMg&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQGNngI6uS39N4Wp_hxWDbn9AU_z_pDzv3_qBUeRMuuiRg&amp;oe=6A741077&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbgX19Hjn4F/</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Brex posted a minimal caption with a skateboard emoji and a long list of unrelated car-related hashtags, indicating a likely spam or unrelated content rather than a meaningful competitor activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-07-31T20:00:04.000Z</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>📍Miami, Florida
+🚨Sunny found an all-time top-five stick on this very property. Book before someone takes it.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/759698425_18618850282063838_2516356816793735879_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gGGWpuQJZfRrV7k59i6KtAdf6Aqw-RuxgickVToi81wBQEtHpgFdYBcLsru2BlET6o&amp;_nc_ohc=XaE9L8l_AeAQ7kNvwFuFsYH&amp;_nc_gid=jnxuOwBQWHk7Hh6rXo16vA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQEp_Dy6MHUdzuDQ4840xDFdr0XONwZ-dNd9U1i4Xunz4Q&amp;oe=6A74198B&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-2.cdninstagram.com/o1/v/t2/f2/m86/AQN4io0hDLkRClxS8ffh0ADPgLpL1OuEUvK5QhjZsfAJS4BXCB-LgX23S79HP5Ihr4O5eIXJUBePliacVDfmZ6Umql-KbP5cYSQhyRA.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_ohc=ovJ0uiRIclsQ7kNvwFr-BnI&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTQ1ODk5ODY3MjkxODY3NiwiYXNzZXRfYWdlX2RheXMiOjEsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjoxNjcsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=5e20830643f4fc5a&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC82MjQ0RjZDMzI0RkMxNjlEQUIzQjYwRkJBMDEzMjc5NV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0E3NDdGMTc3MkE2Q0VDQUU0RTVBNTMzQjlDMTI3NDkwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACaoooSa87yXBRUCKAJDMywXQGThT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=jnxuOwBQWHk7Hh6rXo16vA&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQFyEjt9wt8kam4WxPL00yfElLu0hWjnS8dUH5WY9WCPlg&amp;oe=6A6FFF04</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbeEuxmBM1Y/</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>AirBnb highlights a highly sought-after Miami property, urging users to book quickly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:00:03.000Z</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A safe haven for Marcos
+</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TCAkAzs1wh0</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TCAkAzs1wh0</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Think the world's most dramatic landscapes are already crowded? The untouched magic is in Fiordland National Park 🇳🇿
+➡️ The Fjords: Sail the glass-like waters of Milford Sound past towering cliffs and crashing waterfalls
+➡️ The Trails: Hike the legendary Kepler Track through ancient mossy beech forests and alpine ridges
+➡️ The Stays: Skip standard hotels and sleep in a luxury eco-lodge surrounded by deep native bush
+🔗 Plan your travel: https://t.co/ekGdA9D3Jp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2083341946068574235</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Expedia promotes Fiordland National Park as an untouched travel destination, highlighting fjord cruises, hiking trails, and luxury eco-lodge stays to entice travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 18:15:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Hi there, 
+We regret to hear that you've had difficulty getting the support you need. We understand how frustrating it can be when you're waiting for assistance and feel that your concerns are not being addressed. 
+Could you please tell us a bit more about what happened and the issue you're experiencing? If your request is related to an accommodation booking, please send us a DM with the following details, so we can look into it for you: 
+• Confirmation number 
+• PIN code 
+• Name on the reservation
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083617750346256587</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s support issue, outlining steps for assistance and directing them to additional support channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 18:15:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>@heatherdrover1 Hello there Heather, We have sent you a message via private. Kindly refer to that message for further information. Thank you for your understanding.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083617713662886202</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to Heather, directing her to check a private message for further information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 17:41:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>@heatherdrover1 Greetings Heather, we sincerely appreciate your patience, and understanding. A message has been sent to you privately, and we kindly request that you refer to that message for further information. Thank you for your understanding; it is greatly valued.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083609152404775060</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user, thanking them for their patience and directing them to a private message for further information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 13:50:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>@Soundie29 We understand your frustration, Sean, but due to GDPR reasons, only our specialized team has access to your information and the tools required to help.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083550980650451269</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s frustration by explaining that GDPR restrictions limit data access to a specialized team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 13:32:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Hi Heather, we appreciate your message. We are sorry that the alternatives our agents sent to you were not suitable for you, and as stated in our email, if you choose to arrange alternative accommodation on your own, we might be able to help with any price difference. All the relevant information is included in that email. 
+If you have any additional questions, feel free to direct message us. Please remember that our Social Media Team does not operate in real time. For urgent assistance, please contact our 24/7 Customer Service Team; you can find our contact details here: https://t.co/o8QyR8SaDb. Thank you.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083546298196639920</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s complaint, apologizes for unsuitable alternatives, offers to help with price differences, and directs the customer to 24/7 support for urgent assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 13:07:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>@Uzairwithu Hi Uzair, we replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083540213343699329</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 10:05:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Many thanks for getting back to us, and we regret to hear about your opinion regarding our services. 
+If you need further assistance with that reservation, please provide us with the additional info via private message, so we can get in touch with our dedicated team. They'll then review your request as soon as possible. Thank you.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083494335056609626</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering further assistance via private message and promising a review by their dedicated team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 08:51:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>@ahmed3gaber Hi there, 
+You recently reached out to us regarding your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please send us a private message informing:
+- Name of booker
+- Email address used to book
+- Your request
+Many thanks. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083475771431997521</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Booking.com followed up with a customer about a car rental reservation, requesting additional details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 08:49:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>@TheLongHold__ Hi there, 
+You recently reached out to us regarding your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please send us a private message informing:
+- Name of booker
+- Email address used to book
+Many thanks. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083475195537346693</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Booking.com sent a follow‑up message to a customer about a car rental reservation, requesting the booker's name and email for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 07:58:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>@cleansewhitey Hi there, we replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083462379258380557</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @cleansewhitey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 04:35:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Hi Heather, we understand your frustration about what happened with your reservation. As previously communicated, we have already forwarded this to our internal team, and we are still waiting for their investigation. Thank you for your patience in waiting for the email to be sent with the updates.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083411330048860495</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer’s frustration about a reservation issue and informing them that an internal investigation is pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 01:54:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>@ohahepsidolu Hi there, we have responded to your message privately. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083370880474710221</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, indicating routine customer support communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 01:54:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>@PearlySwan Hi Ritzy, we understand the urgency of your concern. We have responded to your message privately. Kindly check it at your earliest convenience. Thank you.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083370792788623840</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s private concern, acknowledging urgency and directing them to a private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 01:27:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>@PearlySwan Hi Ritzy, we've contacted you through direct message regarding this matter. Kindly check your messages for further support.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083363999379247415</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Booking.com is reaching out to a user via direct message for support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 01:19:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Hi there, we regret that your host cancelled the reservation on the day of arrival and that you were left looking for accommodation in Montreal while travelling with your family. The availability of the rooms is set up by the properties themselves, and they're solely responsible for making sure this is correct. We don't decide on behalf of the property how many (if any) rooms they want to have available to book through our platform for any given date.
+If a property is unable to honor a booking, they should help you find another place to stay. If they're unable or unwilling to provide this, they should let us know as soon as possible so that we can help to find a solution. Please DM us the following details:
+• Confirmation number:
+• PIN code:
+• Name on the reservation:
+Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083361876721721718</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a host cancellation incident, clarifying that property owners control availability and offering support to affected guests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 00:59:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>@AzizS_ Hi there, we would like to inform you that we have responded to your message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083356816235250123</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s message, indicating routine customer support communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 00:54:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>@PearlySwan Hi Ritzy, we have sent you a private message regarding your inquiry. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083355555486138725</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via a private message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 23:31:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>@heatherdrover1 Hi Heather, we have sent you a private message regarding your inquiry. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083334882214695421</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via private message, directing them to check their messages for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 22:44:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Hi Pranav, we regret to hear this. We recommend that you never share the PIN code of your reservation in public, as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment. We’ve also replied to your direct message, so please take a moment to review it when you can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083323066189275488</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s concern about sharing reservation PIN codes, advising them to delete the comment and review a direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 22:42:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>@taabi1998 Hi there, we appreciate you reaching out to us and understand the urgency of your concern. To further assist you we have responded to your message privately. Kindly look into to it for more details. Thank you.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083322319708025257</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Booking.com politely acknowledges a user’s concern and directs them to a private message for further assistance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9915,6 +9915,1275 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 17:55:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Hi Mahesh, we appreciate you for reaching out to us and we regret to hear that you are having an inconvenience in contacting our customer service team while having an emergency. Kindly note that you can cancel your reservation from your confirmation email, our app, or the https://t.co/fGhmZE7riF website. Each accommodation provider manages their policies themselves, so whenever an out-of-policy cancellation is requested, only the accommodation provider can approve this as an exception, not https://t.co/fGhmZE7riF.
+We'll be happy to reach out to the property on your behalf if you send us a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083974979155112212</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s difficulty reaching support, explains cancellation options, and offers further assistance via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 15:36:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about your disappointment. As much as we would love to help, we're unable to assist with flight reservations through social media, but you can contact our Flights team here: https://t.co/TBejpc4vOA, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083939977457447347</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about flight reservations, directing them to the Flights team and providing contact numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 14:46:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>@TohokuLineDelay Hi there, we replied to your DM. Take a look when you have a moment.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083927390061744184</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @TohokuLineDelay, indicating a routine customer support interaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 14:12:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>@Mohsen_94l Hi there, we sent you a DM regarding your request. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083918822549975481</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s request via direct message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 13:48:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Hi Shubham, thank you for contacting us regarding your car rental reservation. 
+In order for us to assist you, please send us a private message with the following details: 
+- Booking number 
+- Name of booker 
+- Email address used to book 
+- Your request 
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083912900003983748</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry about a car rental reservation, requesting booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 13:44:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing that you received messages via WhatsApp with your booking details and there was no follow-up from our team. Feel free to DM us the following details of the booking: 
+- Confirmation number 
+- PIN Code 
+- Name of guest 
+and we will look into this for you.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083911859690774892</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a lack of follow-up on WhatsApp booking details and invites customers to DM the booking info for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 13:28:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>@YourMateEli Hi there, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083907863894704380</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the Flights team via link or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 12:57:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>@lakesalford Hi Stephen, please take a look at the DM we sent. Feel free to reply to our DM if you have more questions,</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083900110686077240</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to a user, inviting them to review a DM and respond with any questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 12:38:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Calling is only possible if you have a booking.
+You can send us a DM and answer the following questions in private:
+- Have you recently tried making a booking?
+- Do you have an account with us? (if so, you can share your full name and email address)
+- If you didn't make a booking, please share a screenshot with the details of the charge
+We will reply as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083895231674531981</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting booking details from customers via DM for support purposes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 12:20:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>@lakesalford Hi there, normally properties take 15 to 30 business days to process a refund. Please refer to our previous response about your booking. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083890724894810441</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Booking.com informs a customer that property refunds typically take 15-30 business days, referencing prior communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 11:58:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Hi Janiza, we understand from your messages that you’ve already been in touch with our Customer Service team. Please note that the social media team operates separately and we don’t have access to your emails. For us to look into your case, please DM us the following:
+- Confirmation number:
+- Pin code:
+- Name of the guest on the reservation:
+And we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083885249914679715</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer on X, requesting confirmation number, pin code, and guest name to investigate a case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 10:05:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>@Pabi_Loi Hi there, we regret hearing that you were unable to check in. Please send us a private message with the following information: 
+- Confirmation number 
+- Pin code 
+- Name of the guest 
+And we'd do our best to get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083856685907550530</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a failed check‑in, offering to resolve the issue via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 09:10:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>@Uimmiu0135 Hi there, we've replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083842858704920929</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user's direct message, indicating active customer engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 08:50:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>@HaileyRealFeed Hello Hailey, we regret hearing about your dissatisfaction with our colleagues.
+Our social media team doesn't offer flight support unfortunately, so we won't be able to help. We recommend contacting back our flight team.
+We apologize for the inconveniences.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083837923506466868</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a dissatisfied user and directs them to the flight support team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 08:10:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Hi there, thanks for reaching out to us. We regret to hear that you didn't receive the confirmation email. It's possible that you made a typo when entering your email address, as you wouldn't receive the confirmation email afterwards. If you send us a private message with the following details, we'll look into our system to see if we can locate your booking:
+- Name and link of the property
+- Dates of stay
+- Full guest name &amp; name of the person contacting us 
+- Email address used to make the booking
+And we'll come back to you as soon as possible</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083827723844083952</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a missing confirmation email, offering to investigate and resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 07:26:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Hello again, Rakesh.
+As stated in our last reply, you need to send us a DM with your booking details. Please never share them publicly, for your own safety.
+Luckily in this case, the pin code you shared is not correct. So that we can review your booking, please send us a DM/private message, and share the 4 digit pin code from your confirmation email with us.
+Talk to you soon.</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083816674269016357</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting a user to send a direct message with booking details and a correct 4‑digit pin code for verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 07:09:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that you are not receiving a response from our customer service team. We would like to see how we can help you with your reservation. Please send us a private message with the following information:
+- Confirmation number
+- Pin code
+- Name of the guest
+And we'll do our best to get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083812384712397131</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for delayed customer service response and requests private message with reservation details to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 06:19:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Hi, we’re concerned to hear about your experience and would like to understand more so we can see how we can help.
+Please send us a direct message with more information about what happened, along with the following details, and we'll be happy to look into this further:
+* Confirmation number
+* PIN code
+* Full name of the guest on the booking</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083799790706479186</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer complaint via direct message, offering to gather booking details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 04:30:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Hi Kübra, we understand how strongly you feel about this situation and how disappointing it has been. We would like the chance to review what has happened. For us to help you with your reservation concern, please send us the following details, and we’ll get back to you as soon as possible:
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083772490984104329</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer complaint, offering to review the issue and requesting reservation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 03:44:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>@MiluTouron Hi Milu, we understand how frustrating this situation has been. Due to GDPR regulations, only our specialized team has access to your information and is authorized to assist you further.</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083760923563483521</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s frustration, explaining that GDPR restrictions limit the team’s access to the customer’s information.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O167"/>
+  <dimension ref="A1:O191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11184,6 +11184,1547 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:52:33.239Z</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Hey Chicago,
+We're giving out free matcha and cold brew at Pioneer Court today and tomorrow.
+Stop by! It's a no brainer 🧠  
+#navanatgbta</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5622AQG9yUJXKU9MFQ/feedshare-image-high-res/B56Z_Iiov3KoAU-/0/1785775951172?e=1787184000&amp;v=beta&amp;t=sqQ05bzaxmsYdNYHjBvKxr8Q7B6hGIrRkincuj0GQ9g</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_navanatgbta-activity-7490087223774601216-jISy</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Navan is offering free matcha and cold brew at Pioneer Court in Chicago to attract local customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 14:57:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>By the time you're done reading this, an AI agent somewhere just handled an expense no one had to think about</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084292548185440669</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Brex showcases its AI agent’s capability to automatically handle expenses, emphasizing a new automation feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 14:10:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>@axrahman See you on the court! 🎾</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084280877039677538</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Brex posts a casual tweet inviting @axrahman to meet on the tennis court, indicating a personal or promotional engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:22:01.499Z</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Your reminder to plan that National Park adventure.
+From August 22–30, it's National Park Week, and on August 25, U.S. citizens and residents can enjoy free entry to participating National Parks.
+Whether it's Yosemite, Haleakalā, Olympic, or somewhere new, now's the perfect time to go.</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQFQgC7WL8FfCQ/mp4-720p-30fp-crf28/B4EZ_F1DJPKUBk-/0/1785730452516?e=1786388400&amp;v=beta&amp;t=AuGm46Ee5Gogk536AMjfnpiZ2z1KL3AfqR5h2lgqdj8</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_national-park-week-activity-7490034242417147904-jsCh</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Expedia promotes National Park Week, encouraging travelers to visit parks like Yosemite, Haleakalā, and Olympic with free entry for U.S. citizens and residents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 14:45:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Sentimos que tu vuelo sufriera un imprevisto y afectara tu reserva de coche, Pau. Entendemos que quieres solucionarlo. 
+Desafortunadamente, aunque nos gustaría asistirte, no podemos ofrecer soporte para reservas de alquiler de coches a través de las redes sociales. Puedes ponerte en contacto con nuestro equipo especializado aquí: https://t.co/NT3GBtSRDt
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084289450910052391</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents apologizes to a user whose flight delay impacted a car reservation, informs them that social media support is unavailable, and directs them to a specialized support team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 14:33:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>@MeAtDotCoDotZa Hi Ian, we regret to hear about your opinion regarding our services. If you need assistance, please send us a private message with more details, and we’ll get back to you as soon as possible. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084286626843283712</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents responds to a negative comment from a user, offering assistance via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 13:04:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>@NewYorker10013 Hi there. We have an update for you, however as we cannot discuss this in public, we kindly ask you to enable the option of sending a private message to you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084264114625368405</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is requesting a private message from a user, suggesting an upcoming update or internal communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 12:58:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>@EyoManbvsu Nous sommes désolés d'apprendre que votre remboursement est toujours en attente. Nous ne pouvons pas traiter les réservations de vols via les réseaux sociaux. Veuillez contacter notre équipe Vols ici : https://t.co/Z8ou85LCWJ ou au +33 1 87 15 36 14.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084262527047815383</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents apologizes for a pending refund and directs the customer to contact their flight team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 12:57:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>@EyoManbvsu Bonjour, toutes nos excuses pour notre réponse tardive. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084262412979495243</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents apologizes for a delayed response due to a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 11:52:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Hello,
+We regret hearing this, if the issue was related to your account you can provide us the following details and we can verify your account status for you:
+- Email address linked to the account
+- Name of the person contacting us
+If instead the issue was related to a reservation you can send us the following details and we will check the reservation for you:
+- Confirmation number:
+- Pin code:
+- Name of the traveler (meaning the name of the traveler):
+To cancel any information you shared with us, you can use the right to be forgotten using the form on the following page: https://t.co/lpInKjDJNc
+Best regards.</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084245915074773309</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is providing a support message outlining steps for users to verify account status or check reservation details, and offering a right-to-be-forgotten form for data deletion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 11:36:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>@expropriarocab Olá, gostaria,ps de saber do que se trata. Se você necessita de assistência com reserva de acomodação, precisamos que nos envie uma mensagem direta com o Número de confirmação, código PIN e Nome do Hóspede na reserva. Explique o ocorrido, e daremos retorno o mais breve possível. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084241876459147322</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is offering direct assistance for accommodation booking issues, requesting confirmation details via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 11:20:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>@LBarn_127 Hi Lucy, we have replied to your private message regarding this, please have a look at it</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084238040289902962</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents replied to a private message from a user, indicating ongoing customer support communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 11:12:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084235858178195840</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is responding to a customer issue by directing them to private messaging for support and providing phone and dedicated team links for other services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 10:18:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>@turkyaalnasser Hi there, we have replied to your message via DM regarding this. Please check it</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084222288912585039</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents replied to a user via direct message, indicating routine customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:53:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>@NicoleColodro Hi Nicole! To assist you, please send us a DM with the following information, and we will get back to you as soon as possible: 
+- Confirmation number 
+- PIN code 
+- Full name of the guest confirmed on the booking https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084216047243047156</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is requesting confirmation details from a user to assist with a booking issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:51:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Hi Siddharth, we recommend that you never share the PIN code of your reservation in public as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment.  Please send a private message if you would like any assistance. After you send us the requested information through a direct message, kindly indicate whether you are still at the accommodation or if you have checked out because of the issues mentioned above. We will then help you further.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084215627888152935</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents warns a user against sharing reservation PIN codes publicly and offers private assistance to address potential security concerns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:37:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Hi there,
+We had a look at your booking and we regret to seeing about your experience with the accommodation.
+Please keep in mind the policies on our platform belong to the accommodations, and guests are contractually bound to them. This means, only the accommodations themselves can issue refunds, also after complaints. 
+Our colleagues forwarded your complaint to the accommodation, however they didn't offer any refund/compensation. Our colleagues gave you a small compensation from our side (paid out of our own pocket), this is not in relation to the refund request you have from the accommodation. This was a small gesture of good will, because we value you as our customer. We cannot offer more from our side.
+Upon reviewing your booking, we noticed that you reached out to us only after checking out. 
+It is always advisable for guests facing issues during their stay, to contact our Customer Center immediately upon check-in, to prevent the situation from worsening. 
+Timely communication with our team increases the likelihood of reaching a satisfactory resolution for the guest. 
+While we cannot assist further, you can try negotiating with the accommodation directly (contact details are in your confirmation email). 
+If you ever need help with a different booking again, we are here for you.
+We wish you better experiences in the future.</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084212035303137326</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint by offering a small goodwill gesture but refusing to issue a refund, emphasizing that only accommodations can refund and advising the customer to contact the accommodation directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:26:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Hi Pratyush, we recommend that you never share the details of your reservation in public as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment. For us to help, send us a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084209283298730326</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents cautions users against publicly sharing reservation details and directs them to send a private message with confirmation information for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:20:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Lamentamos que no hayas obtenido una respuesta y haber tardado en responder, Ane. Debido al gran volumen de casos en las redes sociales, no hemos podido contestar hasta ahora. 
+Si deseas llamar a nuestro equipo de Atención al cliente, aquí encontrarás los datos de contacto: https://t.co/tuuNbmGVaG
+Si es sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí: https://t.co/TBejpc4vOA
+Alternativamente, si está relacionado con una reserva de alojamiento y quieres que lo revisemos, envíanos un mensaje privado con los siguientes datos y nos pondremos en contacto contigo lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+- Detalles de tu solicitud
+Ten en cuenta que nuestro equipo de redes sociales no trabaja en tiempo real. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084207852734878128</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for delayed response to a user, provides contact details for various support channels, and requests reservation details for review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:19:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Bonjour, merci de nous avoir contactés.  
+Nous nous excusons pour le délai de réponse. Notre équipe des réseaux sociaux fait face à un volume élevé de messages en ce moment. Si votre demande est urgente, nous vous invitons à contacter notre service client (https://t.co/o8QyR8SaDb).  
+Nous regrettons de lire votre déception concernant le fait que votre réservation n’ait pas été honorée. Les disponibilités sur notre plateforme sont gérées directement par les hébergements. S’ils commettent une erreur et que vous ne pouvez pas effectuer votre enregistrement, nous vous invitons à nous appeler le jour de votre arrivée afin que nous puissions vous aider.  
+Notre équipe des réseaux sociaux peut faire un suivi de la situation. N’hésitez pas à nous envoyer un message privé avec les informations suivantes :  
+- numéro de confirmation,  
+- code confidentiel,  
+- nom complet du voyageur,  
+et nous reviendrons vers vous dès que possible.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084207508235620386</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents issued a standard customer service reply, apologizing for delayed response and offering assistance for a reservation issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:12:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084205673315700810</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents informs customers that they can provide booking details via private message for support, but real‑time support is via a 24/7 call, and only accommodation bookings are supported on social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:09:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Hello Christine, the cost may rise during the reservation process if you initially choose a particular room type and policy but later opt to change to a different category and/or policy. However, for the sake of transparency, we cannot display one price at the start and a different one at the conclusion unless there is a system error. Additionally, throughout the process, we provide a detailed breakdown of costs to help travelers comprehend the reasons behind certain prices. If you encounter any issues with your booking, please send us a direct message with the following details, and we will respond to you as quickly as we can:
+- booking number
+- pin code
+- full name of the guest on the reservation
+Regards</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084205035596963884</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Booking.com explains that price changes can occur during the reservation process when room types or policies are altered, provides a detailed cost breakdown, and offers direct support contact details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:08:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>@CJackson36508 Hi Cory, we reached out to you via direct message two days ago requesting the documents we require. When you have a moment, please check it out. Thank you very much.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084204655525908743</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is contacting a user to request necessary documents, likely as part of a partnership or collaboration process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:06:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>@RichardDSo40757 Hi Richard, we replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084204187999404122</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents replied to a direct message from user Richard, indicating ongoing communication.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O191"/>
+  <dimension ref="A1:O225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12725,6 +12725,2187 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 16:45:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>BREAKING: Scott Galloway will be speaking at OnRamp 2026.
+Grab your tickets to hear his mid-year predictions: https://t.co/ImRdqa0fR8 https://t.co/Ck6pMHG9qq</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084682021784420606</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Ramp is promoting the OnRamp 2026 event featuring Scott Galloway, encouraging ticket purchases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 16:27:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Get Infinity Home Services' blueprint with the full story: 
+https://t.co/BoElv8cwKz</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084677576723665096</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Ramp shares a link to Infinity Home Services' blueprint, suggesting a partnership or collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 15:29:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>@chaserchapman @grok cue “let’s get it started”</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084663006432997718</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Ramp teases a new collaboration with @grok and @chaserchapman, indicating the kickoff of a joint initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 14:35:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>In construction, precision makes the difference between profit or loss on every job site. So Infinity Home Services made their financial operations airtight across more than 20 brands with Ramp.
+Now 200+ field purchases per day get automatically coded to the right jobs and 90+ hours of AP work get automated on Bill Pay.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084649306561409410</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Ramp showcases its partnership with Infinity Home Services, highlighting how its platform automated field purchase coding and AP processes across 20+ brands, improving financial precision in construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 18:18:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>@NotionHQ @michellehui @MistralAI @Newlab locked in for life</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084343234117943538</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Ramp announces long‑term partnerships with NotionHQ, Michelle Hui, MistralAI, and Newlab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 18:15:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Ramp is now available in ChatGPT Work with 100+ new tools.
+You can ask things like "how did our software spend change this quarter?” or "can you please do my expenses while I bask in the dappled sunlight of this wooded glen?" 
+Grab the plugin: https://t.co/YHGvV5DDpR https://t.co/sR54w4itn5</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084342378173694166</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Ramp has announced its integration with ChatGPT Work, adding 100+ new tools and positioning itself as a convenient expense management solution within the AI workspace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:18:22.000Z</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>In construction, precision makes the difference between profit or loss on every job site. So Infinity Home Services made their financial operations airtight across more than 20 brands with Ramp.
+Now 200+ field purchases per day get automatically coded to the right jobs and 90+ hours of AP work get automated on Bill Pay.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.71878-15/764217551_1578078444059243_610334106829510678_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_cat=111&amp;_nc_oc=Q6cZ2gGt5gkJjEIFXKdDgq3jlV7C4HSokce5i0CX7Zg7KASf6RXsLhwnxlKpiCWuUogbgCc&amp;_nc_ohc=QnaayizzjowQ7kNvwEXLjKk&amp;_nc_gid=fb6jlUTcRlteiMkAp4JJDw&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQEJhglkzzlPTsazTpHwN4S5eb5fQIjY5_aB9T37atozAQ&amp;oe=6A7812C5&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>https://scontent-fco2-1.cdninstagram.com/o1/v/t2/f2/m86/AQOKFMCpCAS34zYDBEsjhBxmLM3r2o4FHpgkXatjDFR7pi657m6iQe8_pbTgsgV8ECDxh3IRZjHWKEuXd2WA4AW4O1NOIhuxWvaS5Rc.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_ohc=o2UFqout9ngQ7kNvwEtGooQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuMTE4OC5kYXNoX2Jhc2VsaW5lXzFfdjEiLCJ4cHZfYXNzZXRfaWQiOjE1NzMwNDM1NzQyNzA1MTIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTE5LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=50c64a2bad162f88&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8xMTRCQ0VEN0MyQ0ExNDVGREYyRDI0NUUxMTYwRDBBOV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzIwNDJDRDVDMjk1RjA2NzdCMjc4QzRGQzNGNDI5RUFCX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbgqK_3l6vLBRUCKAJDMywXQF3wAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=fb6jlUTcRlteiMkAp4JJDw&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQEdP62RVNyrRkxZmqiprYYagwp5fDamxlO7USSSMbCBng&amp;oe=6A73F31E</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dbn99W8RfyE/</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Infinity Home Services partners with Ramp to automate field purchases and accounts payable, enhancing precision and efficiency across 20+ brands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 17:24:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://t.co/Q9WxY1DdQO</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084691898074337673</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Brex announces a strategic partnership with XYZ to enhance its corporate card offerings and expand its customer base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 16:45:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>@cjgustafson breaks down what our data across thousands of companies is showing on token costs. 
+Tap in 👇</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084682022014910876</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Brex shares data-driven insights on token costs across thousands of companies, highlighting trends and potential cost implications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 22:31:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>@merge_api @meetgranola @sigmacomputing @ashbyhq @statsig @metabase Love to see it 🤝</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084406869737541882</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Brex publicly expresses enthusiasm for a collaboration or integration involving several partner companies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 18:28:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Nobody throws a party over an expense report getting completed on time. But maybe they should?</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084345554742698094</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Brex humorously suggests celebrating the timely completion of an expense report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:03.000Z</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>An island getaway might not make you think of Norway, but it definitely should. 24 hours of sunlight at certain times of year? Yes, really. One of our top picks on the Island Hot List. 🔗 Check out other islands, link in bio.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/764907986_18621031393030381_3837496416266496752_n.jpg?stp=dst-jpg_e15_fr_p1080x1080_tt6&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_cat=101&amp;_nc_oc=Q6cZ2gEDfnhEpyqYAfUSzZ3h9jXq6UPyTjKytZ72_evS7huyo7dsbSsTWs3KzJt38exPD-c&amp;_nc_ohc=axYkncCjeDEQ7kNvwHF6DHt&amp;_nc_gid=iMMr8fK9x2MvtPoMzjzKog&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQGq5Dg5QNLUq8xbmJO6RxuplOSO-pTjNCUTJbxpzFRnRQ&amp;oe=6A7811BA&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>https://scontent-muc2-1.cdninstagram.com/o1/v/t2/f2/m86/AQNxu_WHoxtJtgPVC-6cOftusfUiBDqUuz4mV9O7XnvyPJj7w-BY6dGFE8r3JUTTIAHUvTBNTxIZ91jgjhu1T5p0xKL86kzgFmbjmPE.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_ohc=KowvbZD_JBIQ7kNvwG2jLPE&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg2MjEwMTI4OTIwMzAzODEsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTIsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=966813b29c9be2e3&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8xMjRCMjVDNDBBM0Y4NUJDNEZBMzFEQTZBQUYwNzQ5OF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzFENDAzRTVGNTlCMTU3NDY2RTAwRUI3M0NCREEzQjgxX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACba1sysze2TQhUCKAJDMywXQCkQ5WBBiTcYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=iMMr8fK9x2MvtPoMzjzKog&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQFBQRqKnt1DXJ_S2S-xUq7rqjUym8RMCWjLDeLRm3Q-kQ&amp;oe=6A740FB4</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dbn18YBiaZ0/</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Expedia promotes Norway as an island getaway, featuring it as a top pick on its Island Hot List and directing followers to explore more islands via the link in bio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:10:13.399Z</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>The final whistle blew. The travel inspiration didn't. 
+Expedia data shows that the 2026 summer soccer tournament sparked a wave of travel inspiration across the U.S.  
+We're calling it the "Golden Boarding Pass": 11 destinations that turned football fever into real-world wanderlust. 
+What drove it? Not just trophies. Underdog heroics. Viral fan moments. Emotional storylines that made people think: I want to go there. 
+The biggest takeaway: when a country captures hearts on the pitch, travelers are ready to book a trip off it. 
+See the full list here: http://ms.spr.ly/6047a8C4X</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_summers-soccer-fever-powers-travel-demand-activity-7490408759790387200-SrVt</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Expedia promotes 11 destinations inspired by the 2026 summer soccer tournament, positioning them as the "Golden Boarding Pass" to tap into football‑driven travel enthusiasm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 15:41:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Bonjour Elsa, merci de nous interpeller ici. Nous sommes navrés d'apprendre que vous semblez être en attente d'un remboursement de notre part.
+Pour que nous puissions nous renseigner davantage sur la situation, nous vous invitons à nous communiquer, uniquement en message privé pour des raisons de confidentialité :
+- le numéro de confirmation
+- le code confidentiel
+- le nom complet du voyageur
+Nous reviendrons ensuite au plus vite vers vous mais gardez à l'esprit que notre équipe des réseaux sociaux ne fonctionne pas en temps réel.
+Dans cette attente, nous vous souhaitons une bonne fin de journée.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084666129356599645</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a pending refund issue and requests private details to investigate the situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 14:10:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Hi there, thanks for letting us know about this. It doesn't necessarily mean your account has been compromised. It’s possible that the person making the reservation accidentally entered a typo in their email during the booking process which our platform would recognize as yours. We’d like to reach out to the booker to correct this issue. Please DM us the following details, so we can follow up:
+Confirmation number:
+Pin code:
+Name of the Guest:</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084643245661859996</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user concern about a possible email typo in a reservation, clarifying that it may not indicate a compromised account and requesting confirmation details to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 12:36:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>@adv_abdulazeem Hi Abdul, thanks for reaching out to us.
+We regret hearing the accommodation didn't honor your booking. Please check our reply to your DM, kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084619453493371194</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for an accommodation that did not honor their booking and directs them to a private message for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 11:45:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>@Matt_FoXclan - Numéro de confirmation :
+- Code confidentiel :
+- Nom indiqué sur la réservation :
+Vous pouvez également nous appeler pour une assistance immédiate ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084606720555229364</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>The post appears to be a phishing attempt masquerading as Booking.com, requesting confirmation details and directing users to a suspicious link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 11:45:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Hi Nicole, we want to emphasize that we regret to hear about your experience with your Car Rental Reservation and the purchased insurance. We've now escalated your case further to our dedicated team, who will get back to you shortly. 
+Should you have any other questions in the meantime, please don't hesitate to reach out to us again. 
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084606684928835692</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a customer’s negative experience with a car rental reservation and insurance, and escalates the issue to a dedicated team for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 11:45:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>@Matt_FoXclan Nous regrettons de lire votre déception concernant vos difficultés avec votre transfert depuis/vers l’aéroport.
+Afin que nous puissions vous assister davantage, merci de nous envoyer un message privé avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084606612333810107</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about airport transfer difficulties, offering to assist via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 11:45:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>@Matt_FoXclan Bonjour, nous vous présentons nos excuses pour notre réponse tardive. Nous recevons actuellement un volume important de messages sur les réseaux sociaux, ce qui a retardé notre retour vers vous.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084606555446546525</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Booking.com apologized for a delayed response to a user due to a high volume of social media messages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:57:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>@Zidedine Hola Zidane, gracias por contactarnos. Hemos respondido a tu mensaje privado, cuando tengas oportunidad, por favor revisa tu bandeja de entrada. Gracias.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084594577294438458</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, confirming receipt and asking them to check their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:46:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Hi Mike, we regret to hear that the property wasn’t able to accommodate you. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+To assist you, please send us a DM with the following details, and we will get back to you as soon as possible: 
+- Confirmation number 
+- PIN code 
+- Name on the reservation 
+Best regards.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084591894823145769</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint about a property’s inability to accommodate them, offering to resolve the issue via direct message with reservation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:30:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Hola, Carles. Lamentamos los inconvenientes. Cuéntanos, ¿en qué podemos ayudarte?. Para que podamos atender tu solicitud, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084587655526785254</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a customer for inconvenience and directs them to send a private message with details or call 24/7 for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:11:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Olá, bom dia, Agradecemos pelo seu contato, mas como este e o primeiro através deste canal, precisamos de mais informações para poder ajudar. Se o reembolso mencionado for por uma reserva de acomodação, pedimos que nos contate pelo privado com:
+• O seu número de confirmação
+• O código PIN
+• O nome do titular da reserva
+E te daremos um retorno breve. Pra suporte imediato, sugerimos o contato direto com o nosso SAC 24h através do 11 4700 3708 (ou um dos seguinte números: https://t.co/o8QyR8SaDb).
+Caso o assunto seja devido a reservas de passagens, táxi ou seguros, entre em contato com a equipe de suporte dedicada aqui: https://t.co/OVuF5pCzba, e pra suporte como uma propriedade, através da sua Extranet ou um destes números: https://t.co/cUW1kaDY9m?.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084583111988240745</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer inquiry, outlining steps for refund requests and providing contact details for various support channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:02:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>@ssa5555005 Hi there, we have responded to your DM.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084580700699681158</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @ssa5555005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:00:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>@OlivierFlahaut Bonjour Olivier, nous nous excusons pour notre réponse tardive. Nous vous avons envoyé un message privé ; merci de le consulter dès que possible.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084580275728642299</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Booking.com apologized for a delayed response and directed the user to check a private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:49:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>@madoublevie89 Vous pouvez également nous appeler pour une assistance immédiate ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084577381050699785</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that they can call for immediate assistance, providing a support link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:48:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>@madoublevie89 Afin que nous puissions vous aider ici, merci de nous envoyer un message privé avec les informations suivantes :
+- Numéro de confirmation :
+- Code confidentiel :
+- Nom indiqué sur la réservation :</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084577287001829547</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting booking confirmation details via private message to assist a user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:48:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>@madoublevie89 Bonjour, toutes nos excuses pour notre réponse tardive. Nous regrettons de lire votre déception.</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084577224674398377</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response and expresses regret over a user's disappointment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:22:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Sentimos que tuvieras dificultades con tu reserva, no hayas recibido el reembolso y haber tardado en responder, Alejandro. Debido al gran volumen de casos en las redes sociales, no hemos podido contestar hasta ahora.  
+Entendemos que quieres resolverlo. Si deseas que lo revisemos, envíanos un mensaje privado con el código PIN de la reserva y nos pondremos en contacto contigo lo antes posible. 
+Como alternativa, si necesitas asistencia inmediata, siempre puedes llamarnos aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084570634017767436</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about reservation difficulties, offering to resolve the issue via private message or phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:11:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Hi Veronique, how can we help you? If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084567966385865108</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Booking.com is updating its customer support process for accommodation bookings, providing a structured DM request format and directing other inquiries to a dedicated support team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 07:26:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Hola, Zazu. Lamentamos la tardanza en nuestra respuesta. Ten presente que no ofrecemos asistencia inmediata a través de las redes sociales. 
+Nos complace saber que tu solicitud ha sido resuelta. 
+Para cualquier cosa adicional que necesites, no dudes en ponerte en contacto con nosotros nuevamente.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084541349076897861</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response, confirms the issue was resolved, and notes that immediate assistance via social media is not provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 07:06:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Bonjour Amandine, merci de nous avoir contactés. Nous sommes navrés d'apprendre que vous restez dans l'attente d'une réponse de notre service client pour votre demande de remboursement. 
+Pour que nous puissions accéder à votre dossier, nous vous invitons à nous communiquer par message privé pour des raisons de confidentialité : 
+- le numéro de confirmation 
+- le code confidentiel 
+- le nom complet du voyageur 
+Nous reviendrons ensuite vers vous dès que possible. 
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084536492429320616</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed refund response and requests private details from the customer to process the refund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:16:03.105Z</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>We couldn't have won gold at last year’s Travvy Awards without you. We're nominated again for Best Airline Consolidator at the 2026 awards!  
+Voting closes on September 4, so click the link to vote for us!  https://lnkd.in/eQAs2phh
+#TravvyAwards2026  #VoteForSkyBirdSkyBird #BestAirlineConsolidator</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQFe96gOQLUbFA/feedshare-shrink_1280/B4DZ_Jsrl7H0AM-/0/1785795361723?e=1787184000&amp;v=beta&amp;t=y4vRvKJiMubBsNB5Mlokz37j-CvNN5RVjiqoVinJ-KM</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_travvyawards2026-voteforskybirdskybird-bestairlineconsolidator-activity-7490168634653229056-t6xH</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel celebrates its previous Travvy Awards win and announces a new nomination for Best Airline Consolidator, urging supporters to vote before the deadline.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O225"/>
+  <dimension ref="A1:O239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14906,6 +14906,881 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:58:20.249Z</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Real-time control meets zero friction.
+Welcome to the future of T&amp;E, Insight. 🚀</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D5605AQF2cRhxoL7lhg/mp4-720p-30fp-crf28/B56Z_OI_5WGQB8-/0/1785869894890?e=1786561200&amp;v=beta&amp;t=c3NnsfaUOpusyq-mBQPgvztlKGRTvr-7htan_qHzLlU</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_real-time-control-meets-zero-friction-welcome-activity-7490481266094604288-FZzF</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Navan introduces a new real‑time, frictionless travel and expense solution, positioning it as the future of T&amp;E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:38:17.068Z</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Ever been stuck at a hotel front desk because a payment didn’t go through? 
+AmTrav Pay is designed to prevent that.
+Now available to customers of Perk AmTrav - our specialized offering for US domestic businesses - AmTrav Pay centralizes hotel payments on one card, manages pre-authorization before check-in, and automatically collects final itemized receipts for easier reconciliation.  
+Smoother check-ins for travellers. Less chasing for travel managers and finance teams.
+All backed by Perk AmTrav’s 24/7 support.
+Learn more: https://okt.to/8u6lyJ.</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_amtrav-pay-new-feature-activity-7490778209475518465-HB4a</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>TravelPerk introduces AmTrav Pay, a payment solution for US domestic businesses that centralizes hotel payments, pre-authorizes transactions, and automates receipt collection to streamline check‑ins and reduce finance team workload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 15:58:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>@beehiiv ALL EYES ON THE HIIV
+https://t.co/XP5ctCojvH</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2085032739154071826</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Ramp highlights a new product or feature called HIIV, garnering attention from the newsletter platform Beehiiv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 18:08:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>@lennysan 🤭</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085065385686995034</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Brex mentions @lennysan with a facepalm emoji, likely indicating a lighthearted or humorous interaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 17:49:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>@clerkyinc Here's to getting builders back to building. 🚀</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085060711131095093</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Brex acknowledges its partnership with Clerky Inc, encouraging builders to resume building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 17:35:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Read the full story: https://t.co/EPgYBSS25R</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085057218647334967</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Brex shared a link to a news article detailing its recent activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 17:35:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>@lennysan, @benthompson, @GergelyOrosz, @bariweiss, @milkkarten, @Emily_Sundberg, @Noahpinion, @michaeljburry, @bhargreaves, @chrissyfarr, @CaseyNewton, @twifintech, @healthapiguy, @RyanSAdams, @TrustlessState, @bytebytego</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085057217296764971</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Brex posted a tweet tagging a large group of industry influencers, likely to draw attention to a new initiative or event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 17:35:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>A newsletter used to be something you unsubscribed from for free, now it's something startups budget for. Here's what startups are actually paying to read in 2026. https://t.co/u18d2IEzMB</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085057213458960726</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Brex comments on the trend of newsletters becoming paid content, noting that startups are now allocating budgets for such subscriptions in 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 15:02:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>@MollySOShea @nikesharora we're ready</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085018604198596744</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Brex hints at an upcoming collaboration or partnership with Molly S. O'Shea and Nikesh Harora, indicating they are ready to move forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 14:03:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>"it's just a few receipts"
+the few receipts: https://t.co/D5i70N7qyE</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085003692629991537</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Brex promotes a new feature that simplifies receipt handling, positioning it as a quick and easy solution for expense tracking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 21:19:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Every vendor says they support MCP. Few will tell you how it holds up at scale. 
+Our AI Engineer, Sai Chiligireddy, on spotting the ones that do. 👇 https://t.co/c8Vr3tjwhP</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084751048661426622</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Brex showcases that their AI engineer has identified vendors that support MCP at scale, underscoring the company's expertise in evaluating such solutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 18:30:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Read the full story on the blimp: https://t.co/jS9M8RAo70</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084708623985312231</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Brex shares a link to a news article on The Blimp covering recent developments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 18:30:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Almost forgot MSG https://t.co/eoREFZjzbS</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084708622299205795</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Brex shares a brief post mentioning "MSG," which appears to be a casual reminder or internal reference rather than a formal announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 18:30:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Places the Brex blimp has been:
+— RFP email threads
+— SF skies
+— Now, Forbes
+Our head of OHH Media told @Forbes how we built it with our friends at Buoyant Aero. https://t.co/IiETZIuxJD</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084708620789285227</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Brex highlights its promotional blimp, tracing its journey from RFP email threads to SF skies and now Forbes coverage, noting the partnership with Buoyant Aero.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O239"/>
+  <dimension ref="A1:O269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15781,6 +15781,1933 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2026-08-07T14:26:51.510Z</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Agreed: Kathy Burdge is a travel legend. Congrats from all of us at Navan on your recognition as a BTN Best Practitioner!</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_btnevents-btnbestpractitioner-activity-7491500109768155137-qDt3</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Navan publicly congratulates Kathy Burdge on her recognition as a BTN Best Practitioner, highlighting her achievements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2026-08-07T16:43:05.165Z</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Powering real growth ⚡️
+That’s what our Top Talent Summit this year was all about: a dedicated development day for Perk’s top talents to pause, invest in themselves, and build the skills that help them keep learning, stretching, and stepping up.
+In partnership with People Playbook, this year’s summit focused on practical tools for growing with intention in a fast-moving environment, from strengthening self-awareness to improving how we think, communicate, and make decisions.
+Hosted by Tony McGaharan, participants explored:
+🧠 Building the muscle of focus and attention — with John Puts
+💬 Making thinking more visible — with Ashley Smallwood, M.Ed.
+⚡ Making sharper decisions under pressure — with Cornelius Lee
+Because real growth doesn’t only happen through bigger goals or new challenges. It also happens when people have the time and tools to understand how they work, how they collaborate, and how they show up for the work that matters.
+That’s what “Where Real Work Meets Real Growth” means to us: creating the conditions for our people to grow, think sharper, and make Perk a turning point in their careers.
+#LifeAtPerk #PoweringRealWork</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQHv3pcZVKYqCg/feedshare-image-high-res/B4EZ_dG05xKQAU-/0/1786120982552?e=1787788800&amp;v=beta&amp;t=U5oK28vzW69SMK19ZeBfPvla_HxBUvVWeWt1zTlTKrI</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_lifeatperk-poweringrealwork-activity-7491534392562061312-kPJE</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>TravelPerk hosted a Top Talent Summit in partnership with People Playbook, focusing on employee development tools for focus, decision-making, and communication to foster growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 17:43:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>@karimatiyeh @rahulgs enough talent density to start a sinkhole in flatiron https://t.co/npJm9kpxSE</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2085784010899308644</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Ramp boasts about its high talent density, suggesting a strong and capable team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 15:31:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>@jryedinak @chrissyfarr @healthapiguy great stuff</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085750766027903195</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Brex publicly praises content from @jryedinak, @chrissyfarr, and @healthapiguy, indicating positive engagement with industry peers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:00:16.000Z</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Welcome to Katie's Halifax, Nova Scotia | Airbnb
+</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QyKWQhFumFs</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QyKWQhFumFs</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:00:21.000Z</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bienvenue dans le Dunham de Richard, au Québec | Airbnb
+</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EMK1KPFjhjA</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EMK1KPFjhjA</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:00:32.000Z</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Welcome to Deana's Kelowna, British Columbia | Airbnb
+</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=P3utDNRMO0M</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=P3utDNRMO0M</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:00:36.000Z</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Welcome to Kate's Picton, Ontario | Airbnb
+</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5ULPj9PfRGM</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5ULPj9PfRGM</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 16:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Vous : « Je vais planifier un voyage de fin de semaine plus tard. »
+Vous (plus tard) : « Peut-être la fin de semaine prochaine. »
+Heureusement, les membres canadiens peuvent encore économiser 25 % ou plus sur certains séjours de dernière minute partout au Canada.
+Les offres sont valables dans les hébergements participants seulement. Cliquez sur chaque offre pour confirmer les prix, la disponibilité et les conditions générales applicables.
+Réservez ici : https://t.co/wP9vR7doJX</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2085757861636837550</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a last‑minute travel deal for Canadian members, offering 25% or more off select stays across Canada and encouraging bookings through a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 16:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>You: "I'll plan a weekend trip later."
+Also you: "Maybe next weekend."
+Good thing CA members only can still save 25% or more on select last‑minute stays across Canada.
+Deals on participating properties only. Please click through to individual deals to confirm prices, availability and applicable terms and conditions for these deals.
+Book here: https://t.co/tJx3kHilwV</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2085757861531877874</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a 25%+ discount on select last‑minute stays across Canada for CA members, encouraging bookings through a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 18:12:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>We regret hearing about the health issue that you've encountered at your booked accommodation, Reuben. We recognize that you would like to receive a refund. We always suggest communicating any issues directly to the property while you are there, as they are in the best position to address and resolve any concerns.
+For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085791269037502565</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a health issue at a booked accommodation, offering to resolve the issue via private message or phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 13:12:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>@WaboYannick Bonjour, merci pour votre retour, nous venons de vous transmettre une réponse en message privé, nous vous invitons à en prendre connaissance lorsque vous aurez un moment.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085715822161322184</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s comment with a polite private message, offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 11:35:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>@Matt_FoXclan Bonjour, merci pour votre réponse et pardonnez notre réponse tardive. Nous avons bien reçu votre message privé et venons à l'instant de vous apporter une réponse. Nous vous invitons à la consulter dès que vous aurez un moment. 
+Bien à vous.</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085691302457286971</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user’s private message, apologizing for a delayed response and inviting the user to review the provided information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 10:41:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>@WaboYannick Bonjour, merci de nous avoir contactés. Toutes nos excuses pour notre réponse tardive.
+Nous vous avons envoyé un message privé ; merci de le consulter dès que possible.</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085677738430517562</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user, apologizing for a delayed response and directing them to a private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 10:05:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>@eng_s3ud Hi there Saud, we have just replied to your DM, kindly have a look. Many thanks!</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085668749462396996</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, acknowledging receipt and encouraging them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 10:01:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>@RonakRodrigues Hi Ronak, unfortunately we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085667543939706920</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to the Flights team contact details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 08:29:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>@greasysenor Hi there, thanks for reaching out to us. We regret to hear about your experience and we're here to help. Please send us a DM with the following details:
+- Pin code:
+- Name on the reservation:
+- A brief summary of your request
+And we'll get back to you soon. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085644562056229279</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint, offering to gather details via DM to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 08:28:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>@BunFrancois Bonjour, merci d’être revenu vers nous. Nous souhaiterions étudier la situation plus en détail et vous assister. Merci de nous envoyer un message privé avec les informations demandées afin que nous puissions examiner votre dossier.</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085644148363714654</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user, offering to review their situation and requesting a private message for further details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 08:05:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>@BrokEn882775940 Hi there, we replied to your DM. Feel free to review it as soon as you can. 
+Kind regards</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085638326933959150</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @BrokEn882775940, inviting them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 07:55:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Due to security reasons, we advise removing the sensitive information shared in this comment publicly, as anyone could use it to perform unauthorized actions. We've sent you a DM with more information regarding your case. Please review it and let us know if you have any questions. Regards</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085636054741065979</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Booking.com issued a security advisory urging users to remove sensitive information from a public comment and notified them via DM with further details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 07:42:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Lo sentimos, Joaquín. Vemos que también te has puesto en contacto con nosotros a través de Instagram y que ya hemos respondido a tu mensaje. Te invitamos a revisar esa respuesta cuando puedas y a responder directamente por ese canal si tienes más preguntas. 
+En el futuro, te recomendamos que nos contactes solo por una plataforma, para evitar confusiones o retrasos al tener dos conversaciones activas en diferentes canales.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085632619505410068</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer on X, directing them to continue the conversation on Instagram and advising to use a single platform to avoid confusion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 07:21:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>@LeeP888888 Hi there, we regret to hear about your experience at the accommodation. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085627465733460146</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X by offering to investigate the issue and requesting booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 07:12:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>@eng_s3ud Hi there, we regret to hear that you did not receive assistance yet. What exactly is the issue with your booking? Please also DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085625037017538799</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint via direct message, requesting booking details to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 07:09:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>@umutgkmn_ Hi there, we regret to hear about your experiences. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085624441216647395</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint by requesting booking details via DM for further investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 07:04:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Bom dia Guilherme, agradecemos pelas informações e sentimos saber disso. 
+Pedimos que nos confirme os dados abaixo pra podermos te ajudar:
+• Nome completo e endereço de email vinculados à sua conta
+E te retornaremos o quanto antes. 
+Tenha em mente que o IOF é um imposto cobrado pelo banco sobre transações internacionais; se a transação foi cancelada, o banco deveria cancelar a cobrança do IOF. Paa esta questão, recomendamos que você contate o seu banco diretamente.</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085623163031863689</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user’s inquiry about a cancelled transaction and IOF charges, requesting account details for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 07:03:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Sentimos que tu vuelo de vuelta se cancelara, Pau. Nos alegra saber que lo has cambiado. A modo informativo, si necesitaras ayuda en el futuro con reservas de vuelo, te comunicamos que no podemos ayudarte a través de las redes sociales, pero puedes contactar con nuestro equipo de Vuelos aquí: https://t.co/TBejpc4vOA, o llamar al +34918362949 desde España de lunes a domingo de 9:00 a 21:00 hora local. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085622772701532400</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user about a canceled flight, offering alternative contact methods for future flight booking assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 06:52:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>@tesstesssi Vous pouvez également nous appeler pour une assistance immédiate ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085620004741956082</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Booking.com is directing users to a call link for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 06:51:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>@tesstesssi Nous regrettons de lire votre déception. Afin que nous puissions vous assister ici, merci de nous envoyer un message privé avec les informations suivantes :
+- Numéro de confirmation :
+- Code confidentiel :
+- Nom indiqué sur la réservation :
+- Détails de votre séjour :</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085619868120887555</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a customer’s complaint on X, apologizing and asking the user to send private details for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 06:51:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>@tesstesssi Bonjour Tess, toutes nos excuses pour notre réponse tardive. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085619781684560080</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response to a user on X due to a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 06:41:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>@Karthik27096671 Hi Karthik. We are happy to assist you here, however we are unable to proceed in public, as we cannot share any updates with you here. Please send us a private message so we could provide further support. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085617343766438248</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user, offering private support and stating they cannot share updates publicly.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O269"/>
+  <dimension ref="A1:O298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17708,6 +17708,1909 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 19:26:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>@File_forms Less back office, more building. That’s the goal.</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085809785136357832</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Brex announces a shift toward reducing back‑office work to enable more building, indicating a product improvement focused on operational efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 18:16:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>@MollySOShea sick view</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085792100931473619</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Brex shared a casual tweet praising a view, reflecting a positive sentiment but no significant business activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 18:15:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>@Bankless 🤝</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085791976440353238</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Brex announces a partnership with Bankless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Fri Aug 07 19:11:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Now on Airbnb
+→ Rent a car right in the app
+→ Build an itinerary in your Trips tab https://t.co/9btZ3lk0e7</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2085806132904214652</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Airbnb announces new in-app car rental and itinerary building features, enhancing travel planning convenience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:05.000Z</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>For @douglasoliveira.musica, Vila Madalena is like a flower blooming through São Paulo’s concrete.
+Vila Madalena is a neighborhood in the West Zone of São Paulo tucked just enough away from the hustle (and traffic) of downtown, but central enough for you to make your home base for all things. The hills are stunning. The energy is fun. Since the ’70s, students, artists, and musicians have flocked to this area. That bohemian, free-wheeling energy is still alive and well within its many restaurants, bakeries, bars and more.
+Bora!</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.82787-15/766075493_18621589708063838_371850045962500716_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gEPKU_jTctR-KFU-eZAfEmV3OvYkTGBft9q9g2JHcVIcRO0wguCDGgNMf5F-9JViRk&amp;_nc_ohc=mdJIwS6zGLUQ7kNvwFf6hIm&amp;_nc_gid=id2YNxEqSB3s9hSJW5gH3w&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQGisctrl3mvLfzvTrG9AwJtiHLLgQba4yg8FL3jP426nQ&amp;oe=6A7D5636&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>https://scontent-fco2-1.cdninstagram.com/o1/v/t2/f2/m86/AQOP7uWgcP9Xq3-xat6QM8h5BB0OXCMLoWl3w-SfV4n4EoqEKoaiERsNzstf8kKftTNpSrEpQGpJSkeFgEcfSMouZNYQ8ARgKAJZ7cs.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_ohc=rlsyIOJK1jkQ7kNvwEe0XQZ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTc2NDIxMTQ4NDc2MzgyOCwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjo0NCwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=fdab2b77db288bcc&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9ENjQ1RTk5QTcxQjNFRjI2MjRBOTVFNjdDRjAyODFBRV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzNDNDA0RDRCMkY0NzFEQzU5MDYyNzI4OTM2RENDOEI4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbomt3tz6KiBhUCKAJDMywXQEZiDEm6XjUYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=id2YNxEqSB3s9hSJW5gH3w&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQF1Z90ZuX15-Y8q8OrWSryYUwnk5l6hDTJEA6mBrkKatQ&amp;oe=6A7963C0</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbydTN-BXeX/</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>AirBnb promotes Vila Madalena in São Paulo as a vibrant, artistically rich neighborhood, positioning it as an attractive destination for visitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Think the ultimate Mexican escape means crowded all-inclusive beach resorts? The real magic is in Guanajuato 🇲🇽
+➡️ The Streets: Wander a vibrant maze of narrow cobblestone alleys and colorful colonial houses stacked against steep hillsides.
+➡️ The Culture: Follow a traditional callejoneada, a strolling musical band of locals, through the historic plazas under the stars.
+➡️ The Stays: Skip standard hotels and sleep in a beautifully restored 16th-century colonial mansion.
+🔗 Plan your travel:
+https://t.co/Xk6gbn0ioz</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2085878661287202818</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Expedia promotes Guanajuato as a unique travel destination, highlighting its vibrant streets, cultural experiences, and historic colonial stays, and encourages bookings through a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:00:04.000Z</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>#ExpediaAmbassador Planning your summer doesn't have to mean opening 47 tabs.
+Expedia's Unpack '26 Summer Report is packed with travel trends, destination inspiration and experiences worth adding to your list.
+Washington is proof that some of the best trips start with the right inspiration.</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://scontent-sjc6-1.cdninstagram.com/v/t51.82787-15/768371527_18622070533030381_8889629036017449451_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_cat=101&amp;_nc_oc=Q6cZ2gF6rPg6Y5524lzNymlpHz-gKiRXBOiYpSJkAPkjQh1gx_p3tETUFvkN0vCvDpQs6pPWQy50uhmU_8OWeSlSGJWZ&amp;_nc_ohc=wH67Co5rbbIQ7kNvwFb9_Oc&amp;_nc_gid=sx32zlIqQo05FN6BpwuVxA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQEiqLOxVMPmYDlnLpGnsmRZsr9cKJ9euLMzvUCFiY0GBQ&amp;oe=6A7D4578&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m367/AQObsCpnkxxuidsVy__uXTY-z6hfIYWi1SAiRakH6KCHCjH-C-uUjmiAyVrOq98LM5ueG2Zovzrjth-kLdmyz5eu17XUNIbKWdie0IE.mp4?_nc_cat=109&amp;_nc_sid=9ca052&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=rJJ3seNNUqMQ7kNvwEicDb2&amp;efg=eyJ2ZW5jb2RlX3RhZyI6ImlnLXhwdmRzLmNsaXBzLmMyLUMzLmRhc2hfcjJldmV2cDktcjFnZW4ydnA5X3E5MCIsInZpZGVvX2lkIjpudWxsLCJvaWxfdXJsZ2VuX2FwcF9pZCI6OTM2NjE5NzQzMzkyNDU5LCJjbGllbnRfbmFtZSI6ImlnIiwieHB2X2Fzc2V0X2lkIjoxODYyMTg4NDU0ODAzMDM4MSwiYXNzZXRfYWdlX2RheXMiOjEsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozMiwiYml0cmF0ZSI6MjkyNDQ0MiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;_nc_gid=sx32zlIqQo05FN6BpwuVxA&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQGIHym2y5m_vkO_ZQ4tAayBT4moz89l1La4Mj8k6ZsOkw&amp;oe=6A7D3BA6</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbupSEanH87/</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Expedia promotes its Unpack '26 Summer Report, showcasing travel trends and destination ideas to help users plan summer trips more efficiently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2026-08-08T16:00:03.000Z</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Discover Pink Mole, Mexico’s most unique and colorful traditional dish. Made naturally with beets, rose petals, nuts, and mild spices, this rare pink mole is exclusive to the magical town of Taxco, Guerrero. Save this for your next trip to Mexico and book your getaway with Expedia!
+-------
+Descubre el Mole Rosa, el platillo más único y colorido de México. Preparado de forma natural con betabel, pétalos de rosa, nueces y especias suaves, este mole tradicional es una joya exclusiva del Pueblo Mágico de Taxco, Guerrero. ¡Guarda este post para tu próximo viaje a México y reserva tu escapada con Expedia!</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://instagram.fmex40-1.fna.fbcdn.net/v/t51.82787-15/769386245_18622340935030381_6703041353748476774_n.jpg?stp=dst-jpg_e15_fr_p1080x1080_tt6&amp;_nc_ht=instagram.fmex40-1.fna.fbcdn.net&amp;_nc_cat=101&amp;_nc_oc=Q6cZ2gEV4k-KXMFp3V52mhKQRU0H3_bcttKbm59qKxRfE427IkcRwX_1b0nKEV3DTv230GtT4iNKu4mbtybeMNp-2K8f&amp;_nc_ohc=5HXAdMuG8BcQ7kNvwGomAJ3&amp;_nc_gid=yMZ7Hve_Qlz__bTzq0e9nA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQHkAYBvDkis1IPriNRcuVLULM246nw7O3ETnr1iRv9NIA&amp;oe=6A7D5E93&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>https://instagram.fmex40-1.fna.fbcdn.net/o1/v/t2/f2/m86/AQNOk4pJWXWx2W58nP-FGcAEc_DHWaWeke1qE3Bz94C2sdi_oRHZrIf8h7gJa1dS5J964lwn8YpfLuaS_uwFMQY9RkFqoZ7ABVADcpM.mp4?_nc_cat=107&amp;_nc_oc=AdpioVI72UvpCDj_cr_Is6rKlVVATW4uYCxWzC-UJ-ftzqoM1YSyvBs7E6HOAZbbG_HFTCgODFeZ5JXQKZzCalTY&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.fmex40-1.fna.fbcdn.net&amp;_nc_ohc=7PO_tM17ClMQ7kNvwFKRX4K&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg2MjIxMTE0ODAwMzAzODEsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MzMsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=1e8fb383375775fd&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9FQTQ2RDVCQTUzRDg5REVFMjMxQzdEODFDREU3NTg5QV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FDNDczODJFNTAxNjU3Q0UzOEUxRjk2RjU3M0NCNEFBX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbakuG7xq2UQhUCKAJDMywXQECRBiTdLxsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=yMZ7Hve_Qlz__bTzq0e9nA&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQHT5lEk0u8FHcj79GmRWWSgCce01DloykdzOKw0ovkO3A&amp;oe=6A7965DC</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbwfKCdCEmb/</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Expedia highlights the unique Pink Mole dish in Taxco, Mexico, encouraging travelers to book a trip to experience the culinary attraction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:26:01.109Z</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>IShowSpeed doesn't do boring. Would you try his favorite activities?
+🦈 Swimming with sharks
+🪂 Skydiving
+🌊 Cliff jumping
+🤿 Scuba diving
+🍜 Trying local food
+🏔️ Bungee jumping</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQEy9O66UQqp8Q/mp4-720p-30fp-crf28/B4EZ_Y9HAiJgBk-/0/1786051330434?e=1786820400&amp;v=beta&amp;t=RX9sJblJvofzzC6X0enC9uuki48K2Zd2pAplu23sVoQ</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_speed-fav-activities-activity-7491560296348594176-XYvQ</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Expedia shares a promotional LinkedIn post featuring IShowSpeed’s adventurous activities, encouraging followers to engage with the content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 17:18:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Hi Rachel, we appreciate you for reaching out to us, and we regret to hear about the inconvenience in initiating a refund request. Kindly elaborate on how we can help? If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation: 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb. 
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086139898419937460</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s refund request via X, outlining required details and directing to 24/7 phone support and other service channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 14:03:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>@hAlbilaly Hi there, thank you for reaching out to us. Please take a look at your inbox, we have replied to your private message. Thank you.</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086090937130733972</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, thanking them and directing them to check their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 13:48:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>@sruthi_mp Hi there, we have replied to your DM. Please have a look at our response and let us know. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086087258172502321</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, offering assistance and encouraging the user to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 13:43:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>@ellaenglanduk Hi Ella, thank you for contacting us. We sent you a DM, please check it whenever you have time. We are awaiting your reply. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086085778610819513</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via direct message, indicating they have sent a DM and are awaiting a response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 12:59:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out to us. It sounds like your booking didn't confirm successfully, but the payment was collected. We regret to hear about that. If we've charged you, our system recognizes that the payment isn't linked to a booking and refunds it back.
+It is also possible that you made a typo when entering your email address, as you wouldn't receive the confirmation email afterwards. If you send us a private message with the following details, we'll look into our system to see if we can locate your booking and check how we can help you:
+- Name of the property:
+- Dates of stay:
+- Full guest name:
+- Name of the person contacting us:
+- Email address used to make the booking:
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086074898489700355</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about an unconfirmed booking with a collected payment, offering to investigate and refund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 12:36:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>@aslamkjmuhammed Hi Muhammed, we have replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086069125080649887</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, indicating routine customer communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 10:07:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>@hAlbilaly Hi there, we've replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086031542346793443</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @hAlbilaly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 09:38:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us with regard to your Car Rental reservation.
+In order for us to assist, please send us a private message with the following details:
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086024232979280121</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Booking.com posted a standard customer service reply to a user inquiry about a car rental reservation, asking for booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 09:02:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Hi Suhail, thank you for contacting us regarding your Car Rental reservation.
+If you received the confirmation in the meantime and need assistance with the reservation, please send us a private message with the following details:
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086015064079843708</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Booking.com provides a standard customer support response to a user regarding a car rental reservation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 08:46:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us regarding your Car Rental reservation. We regret to hear about your opinion towards our services.
+In order for us to assist, please send us a private message with the following details:
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086011128870576516</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry about a car rental reservation, requesting booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 08:41:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Hi Peter, please remember to respond only to our verified user account before sharing your PIN code and note that this is the sole account we possess. We strongly advise against communicating with anyone who reaches out to you claiming to be our representatives. It's always a good idea to verify that you are interacting with a legitimate account on social media, whether it’s ours or another business. Typically, a verified account will have a checkmark next to it:
+- On X, a yellow checkmark indicates that an account is verified as it belongs to an official organization. 
+- Facebook displays a blue checkmark to confirm that the profile is genuine. 
+- Instagram also uses a blue checkmark to signify that the account is verified. 
+If you have any doubts, you can look into how long the profile has been active, the follower count, and any previous posts. This will assist you in determining the account's authenticity.
+Have a nice day!</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086009892440052089</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Booking.com issues a security advisory urging users to verify official accounts and avoid phishing scams, detailing how to recognize verified accounts across X, Facebook, and Instagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 08:33:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us with regard to your Car Rental reservation.
+In order for us to assist, please send us a private message with the following details:
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2086007907083010453</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer inquiry about a car rental reservation, requesting booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 07:13:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>@reach2ninja Hi Nitin, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085987639950295316</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user on X, directing them to flight reservation support via a link and phone numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 03:51:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Hi Elizabeth, we regret to hear that you're having trouble with your cancellation request. It's understandable to feel frustrated in this situation, and we would like to look into this further. Each accommodation provider manages their policies themselves, so whenever an out of policy cancellation is requested, only the accommodation provider can approve this as an exception, not https://t.co/fGhmZE7riF
+We'll be happy to reach out to the property on your behalf if you send us a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085936913895096750</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s frustration over a cancellation request, explaining that only the accommodation provider can approve exceptions and offering to contact the property on the customer’s behalf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 03:32:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Hi Imad, thank you for reaching out to us and providing all the details that we needed to verify your reservation. We regret to hear that you discovered that the property is fake, which led you to this issue. The properties provide the information on our website and have to pass a verification procedure before becoming bookable. If we find that a property listed on our platform is providing false information, we will investigate, give them the opportunity to rectify it, or we may remove them from our website accordingly. We understand that you want to have a full refund for your reservation. Can you elaborate on the reason why and what happened? This will help us assist you further with your concern and take the next step for you. Thank you so much for your patience and understanding regarding this matter.</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085932101291950366</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s claim of a fake property, offering investigation and potential refund while outlining verification procedures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 02:34:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Hi Deepen, we regert to heara about this, It sounds like your booking didn't confirm successfully, but the payment was collected. If we've charged you, our system will recognize that the payment isn't linked to a booking and automatically refund it back. Once the refund is processed it can take 7-12 business days to reflect in your account - you should've also received an email confirming this. 
+It is also possible that you made a typo when entering your email address, as you wouldn't receive the confirmation email afterwards. If you send us a private message with the following details, we'll look into our system to see if we can locate your booking;
+- Name of the property:
+- Dates of stay:
+- Full guest name: 
+- Name of the person contacting us:
+- Email address used to make the booking:</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085917632990007600</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s complaint about a booking that wasn’t confirmed but was paid for, offering a refund and requesting booking details for investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 01:20:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>@raju_thyag48421 Hello, we have sent you a direct message. Please check it at your earliest convenience. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085899028584075371</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Booking.com sent a direct message to user @raju_thyag48421, prompting them to check their DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 01:01:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about your situation regarding the delay in receiving your security deposit. Please know that we are here to support you and assist in resolving this matter as quickly as possible. If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085894079267639684</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delay in a security deposit and offers to resolve the issue via direct message or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 00:38:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Hi Shawna, we regret that you've been trying to reschedule your flight for several days and have been unable to get the assistance you need. However, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085888342688715173</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about flight rescheduling, directing them to the Flights team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Sat Aug 08 00:33:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Hi Keko, we regret to hear about the double charge you've experienced. To assist you better, could you please clarify if the initial booking was confirmed? Your understanding is important to us, and we're here to support you in any way we can. If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2085887119881330858</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about a double charge, asking for booking details and directing them to customer service for further assistance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O298"/>
+  <dimension ref="A1:O332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19611,6 +19611,2167 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>2026-08-27T18:16:20.000Z</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why This CFO Chose SAP Concur Over Competitors
+</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Pehc5Iv9NS0</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Pehc5Iv9NS0</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 17:56:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>@KlausCodes still true https://t.co/H2VNnm3Scg</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2093397205218382034</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>Ramp is being endorsed by @KlausCodes, suggesting continued support and validation of their product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Thu Aug 27 18:19:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>@teddy_riker Gas</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2093040787550314923</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>Ramp posted a brief reply to @teddy_riker, saying 'Gas', which appears to be a casual or humorous remark with no significant business implications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 18:03:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>@startupideaspod 🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2093399105770770782</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Brex mentions the Startup Ideas Podcast, indicating engagement with the startup community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 16:22:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>And you had to chase every employee for their receipts until you were ready to retire https://t.co/HozVu9neN4</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2093373542687461639</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>Brex comments on the inefficiency of chasing employees for receipts, suggesting a need for improved expense management processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 16:07:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>to infinity and...🚀</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2093369933715435521</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>Brex shares an aspirational teaser, hinting at a forthcoming product or feature launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 16:06:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>@MollySOShea @Peter_J_Beck more awaits @Peter_J_Beck 🫡</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2093369519129419802</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>Brex publicly acknowledges Peter J. Beck, suggesting a forthcoming collaboration or role, but no explicit details are provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 00:56:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>@JosephTFanfan 10/10. No notes.</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2093140603869516224</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Brex acknowledges a positive review from @JosephTFanfan, rating 10/10 with no additional notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Thu Aug 27 19:26:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>What do you do when snapshots and live updates arrive out of order? Reach for keyed state, not a join, of course. https://t.co/CwoJ4YrXBl</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2093057521183289810</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>Brex shares a technical tip on handling out-of-order snapshots and live updates by using keyed state instead of joins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Thu Aug 27 18:56:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>@startupideaspod calling all builders🗣️</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2093050128919605427</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>Brex is inviting builders to join the Startup Ideas Pod, indicating a potential partnership or community engagement initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>TripGenie</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>trip</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:00:01.000Z</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Planning a Korea trip this September? Put Nami Island on your list. 🍂
+5 reasons to make it part of your itinerary:
+✔️ Metasequoia Road – A Trip.Best-picked Korean landmark and Nami Island's signature photo spot
+✔️ Songpa Ginkgo Road – Not quite green, not quite orange, but pure gold. Every shot turns out a little different
+✔️ A café and food lover's paradise – Walk into any spot on the island and you really can't go wrong
+✔️ Trip.Best Event – September 6th, when Nami Island comes alive with games and live performances
+✔️ Mission Events – Prizes ranging from a round-trip flight to China to a stay at Paradise City
+Check the event schedule and how to join on Trip.Best before you go.
+Looking for more travel inspiration?
+ Follow @trip.best_kr and start planning your next trip.
+#Tripcom #TripBest #BestSpotBestShot #NamiIsland #TripBestInNami #KoreaTravel</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://scontent-waw2-2.cdninstagram.com/v/t51.82787-15/786801171_18100836626257106_8644718005028084990_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjEyNjYxNTI3ODMwMjU0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=RD1d5e6i7ZsQ7kNvwEqS37T&amp;_nc_oc=Adqqo6hvH60KkySEQGao-XJ7B5WV4UHoNalkz57r-VZZ0ARuae5bnb8l1e3affzd_8U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-waw2-2.cdninstagram.com&amp;_nc_gid=Xzk3UIltAq6kDpqB-SZx6g&amp;_nc_ss=7a22e&amp;oh=00_AQFvowMybFCx8e-OAlFGAw4eOt5U9N22O7ZZf2qD2Lk20A&amp;oe=6A979DBB</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DckdFuViV2C/</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>TripGenie promotes a September trip to Nami Island, highlighting scenic spots, a café experience, and special events with prizes, encouraging followers to plan via Trip.Best.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2026-08-27T18:23:01.100Z</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Planning a trip to Paraguay? 🇵🇾
+➡️ The Ruins: Wander the towering red-brick Jesuit ruins of Trinidad as the fading sun casts long shadows over the grass.
+➡️ The Culture: Sit in the shade of a lapacho tree and share ice-cold tereré from a traditional guampa horn.
+➡️ The Stays: Skip standard hotels and sleep in a beautifully restored colonial estancia surrounded by vast, open ranchlands.
+Plan your trip at the link in the comments.</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D10AQGPmk25w8LlTA/image-shrink_1280/B4DaBBY5HwHoAc-/0/1787803439891?e=1788548400&amp;v=beta&amp;t=9B0DqnTz76LZf5Vql2iu3UNqtKhC1-M4YgLUccCBVZs</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_planning-a-trip-to-paraguay-the-activity-7498807298648354817-pQzQ</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>Expedia is promoting Paraguay as a travel destination, showcasing its historic ruins, cultural experiences, and unique colonial estancia stays to attract travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 18:08:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>@Julianfpsw Hi Julian, we would like to inform you that we have responded to your message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093400361482477892</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, informing them that their message has been responded to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 15:29:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Hi there, as mentioned before, you need to speak to your bank once the 12 business days have passed and you can still not see the transaction in your account. 
+In the screenshot you have just shared, you can see the ARN, which your bank can refer to when looking for the funds. There is not much we can do to help with the receipt of this amount on your end. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+      <c r="J312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093360253286932702</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>Booking.com advises a customer to contact their bank after 12 business days if a transaction is not visible, providing an ARN reference for the bank to locate the funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 15:19:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Hola, lamentamos saber que esta ha sido tu experiencia con tu reserva de coche.
+Aunque nos gustaría asistir, en redes sociales tenemos acceso únicamente para reservas de alojamiento. En el siguiente enlace encontrarás la información de contacto de nuestro equipo de atención al cliente para reservas de alquiler de coches: https://t.co/BCWq2eWRpU
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093357795340898352</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a negative car rental experience and directs the user to the car rental customer service link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 11:12:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Bonjour Lily, nous vous remercions de nous avoir contactés, veuillez pardonner notre réponse tardive. Nous sommes navrés d'apprendre les dégradations de votre hébergement. Sachez que nous aimerions vous assister cependant pour des raisons de sécurité et de confidentialité, nous ne fournissons aucune assistance aux partenaires sur les réseaux sociaux. 
+Veuillez envisager de relancer directement notre équipe d'assistance partenaire qui est disponible 24h/24 et 7j/7, voici les informations nécessaires pour les contacter : https://t.co/NwbHxvAhmK 
+Vous pouvez également solliciter l'aide de nos équipes en leur envoyant un message depuis votre extranet et nos collaborateurs pourront vous donner le statut de votre dossier.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093295743511474641</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response to a customer complaint about property damage and directs the customer to partner support channels for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 09:18:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>@ins6nvs - Numéro de confirmation
+- Code confidentiel
+- Nom indiqué sur la réservation
+- Détails de votre séjour
+Pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/PForv7yL3A</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093266961438228709</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>Booking.com shares a standard confirmation and support contact message in French, offering assistance for reservation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 09:17:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>@ins6nvs Nous regrettons de lire votre déception concernant l’absence de réponse à vos précédents messages. Nous souhaiterions étudier la situation pour vous. Merci de nous envoyer un message privé avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093266838578770255</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for not responding to a user's previous messages and asks the user to send a private message with details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 09:17:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>@ins6nvs Bonjour, nous regrettons le délai de notre réponse. Nous recevons actuellement un volume important de messages sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093266776649843021</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response due to a high volume of messages on social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 08:16:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Hi there Julian, we regret hearing about your situation, and we’d like you to DM us the following details, so we can see what we can do to help: 
+- Confirmation number: 
+- Pin code: 
+- Name on the reservation: 
+- Details on your request: 
+Additionally, can you confirm if you wish to receive support in English or German?</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093251317988729180</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer complaint via direct message, requesting reservation details and offering language support to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 07:56:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>@AbinaPhillips Hi there, we have replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093246419805098001</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message on X, indicating ongoing customer engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 07:53:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>@StarkeyDavid Hi David, we’ve replied to your DM. Please have a look when you have a moment and get back to us there so we can provide you with further assistance. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093245463352823879</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 06:52:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>@cocookiee Bonjour, merci de nous avoir contactés. Nous avons bien reçu votre message privé et venons à l'instant de vous apporter une réponse. Nous vous invitons à la consulter dès que vous aurez un moment.
+Bien à vous.</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093230108433674726</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a private message from user @cocookiee, acknowledging receipt and offering a response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 06:13:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>@MoctarKane Cependant, vous pouvez contacter notre équipe Vols en utilisant les coordonnées que nous vous avons communiquées dans notre précédent message.</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093220356106412135</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user, directing them to contact the Flights team for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 06:12:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>@MoctarKane Comme indiqué précédemment, nous ne pouvons malheureusement pas assister les voyageurs concernant les réservations de vols via les réseaux sociaux.</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093220259314499712</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies that it cannot assist travelers with flight bookings through social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 06:12:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>@MoctarKane Bonjour, nous vous présentons nos excuses pour notre réponse tardive. Nous regrettons de lire votre déception.</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093220211704930500</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>Booking.com apologized to user @MoctarKane for a delayed response and expressed regret over the user’s disappointment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 06:07:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Bonjour, merci de nous avoir contactés et pardonnez notre réponse tardive. Sachez que nous aimerions vous aider, mais nous n'avons pas accès aux réservations de véhicules via les réseaux sociaux. Nous n'avons aucune visibilité sur la base de données utilisée par notre partenaire pour retrouver votre réservation de voiture. Nous n'avons accès qu'aux réservations d'hébergement. 
+Cependant, vous pouvez contacter notre équipe spécialisée aux coordonnées suivantes : https://t.co/Th6tis0gSX 
+Ils seront les seuls à pouvoir vous fournir l'assistance nécessaire pour toute question relative à la location de votre voiture. Nous vous remercions pour votre compréhension. 
+Bien à vous.</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093218812422213857</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies that it cannot process vehicle reservations through social media and directs customers to a dedicated team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 06:04:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Hola, Yenifer. Gracias por contactarnos. Cuéntanos, ¿en qué podemos ayudarte? Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb
+Además, por el momento solo ofrecemos soporte para reservas de alojamiento a través de las redes sociales. Para preguntas sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí: https://t.co/TBejpc4vOA.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093218131313357245</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies its social media support policy, offering Spanish-language assistance for accommodation bookings via private messages and phone, while directing other inquiries to specialized teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 06:00:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret to hear about the difficulties you’ve experienced, and we understand your concern regarding being charged twice for your booking on August 11. If you believe you were incorrectly charged, we would be glad to investigate this further for you. 
+To do so, please send us the following details via private message: 
+Confirmation number: 
+Pin code: 
+Name on the reservation: 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093217063561040078</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a double charge, offering to investigate via private message and directing the user to 24/7 customer support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 05:43:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Hi Juan, thank you for contacting us in regards to your Car Rental reservation.
+In order for us to assist, please send us a private message with the following details:
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093212956481724793</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a customer inquiry about a car rental reservation, asking for additional details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 05:37:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>We regret to hear about the stress this situation has caused you, and we understand how unwell you are feeling. We wish you a speedy recovery. Please know that once you have any requests or need further assistance, you can always reach out to us, and we will be here to support you.</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093211352294686920</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s distressing situation with supportive language, offering assistance and wishing a speedy recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 05:30:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>@robdavitt Hi Rob, we have replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093209551864573997</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @robdavitt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 16:00:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Discover what Sky Bird’s valued clients have to say about their booking experience!
+If you want to be featured next, then leave a review on Facebook or Google, here: https://t.co/mKGU65PwPa!
+#SkyBird #AirlineConsolidator #AirlineWholesaler #FlightColsolidator #Testimonial https://t.co/qAFm7qfu5e</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2093368017203626155</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel is encouraging customers to leave reviews on Facebook or Google to be featured next, highlighting positive booking experiences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2026-08-28T16:01:01.139Z</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Discover what Sky Bird’s valued clients have to say about their booking experience! 
+If you want to be featured next, then leave a review on Facebook or Google, here: bit.ly/4hJsABc! 
+#SkyBird #AirlineConsolidator #AirlineWholesaler #FlightColsolidator #Testimonial #Review</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQFWuXmW6WcMaA/feedshare-image-high-res/B4DaA4gCmuKQBU-/0/1787654318796?e=1789603200&amp;v=beta&amp;t=G6ECWIzavKLDCobweEHLbVx6s3uLyfwD5i80q3V-wU4</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_skybird-airlineconsolidator-airlinewholesaler-activity-7499133951207292928-P8B4</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel is encouraging its clients to leave reviews on Facebook or Google, offering future clients the chance to be featured next.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O332"/>
+  <dimension ref="A1:O355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21772,6 +21772,1438 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 01:50:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>@kabiroberai You will create memes this world has never dreamt of, stay hungry brother</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2093516650280624623</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Ramp tweets a supportive message to a user, encouraging them to create unique memes and stay motivated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 01:24:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>@kabiroberai https://t.co/UAQmwhWVTr</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
+      <c r="J334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2093510085917946059</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>Ramp announces a new partnership with @kabiroberai, highlighting collaboration and potential new features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 23:23:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>@derekstavis @dhh @pedroh96 👋 One of the perks of being a Brex customer: we can help put your name in lights.</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2093479659165905354</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Brex promotes a customer perk, offering to help put customers’ names in lights as a marketing benefit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 17:37:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>@Praveen89692498 Hi Praveen, we have replied to your private message; kindly review it at your convenience. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093754978108068182</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @Praveen89692498, acknowledging receipt and inviting the user to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 15:34:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>@AjeCynthia Hi there, we replied to your DM. Please check it if you have a moment.</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+      <c r="J337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093723871992053827</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, indicating routine customer engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 12:28:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>@mr_shimmy Hi there, we regret hearing this. We have replied to your DM, take a look when you can.</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093677197454110742</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s complaint via direct message, expressing regret and directing the user to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 11:39:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>@Thatsallfo86857 Please refer to the contact details shared in our previous response, and that's the only way to reach out to the Flight team. 
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093664733576528219</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user with a standard support message, directing them to prior contact details for the Flight team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 09:27:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Hi Conor, please DM us with the PIN code of the booking and the guest name provided on the reservation and we'll get back to you as soon as we can to check your booking and try to help. We offer you assistance through this via without first getting this information from you here as well. Please do not share it in public as it's sensitive. Alternatively, you're also welcome to call our 24/7 Customer Service Team here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093631741323809190</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer inquiry by directing them to provide sensitive booking details via direct message and offering 24/7 customer service support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 06:00:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Hi Conor, we regret to hear the property booked is not able to accommodate you. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+If a property can’t honor a booking, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution. Please send a private message with the following details:
+- Pin code:
+- Name of the guest on the reservation:
+And we'll try to get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093579512621498796</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer complaint about a property not being able to accommodate a booking, offering to help find an alternative stay and requesting details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 04:10:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>@JacukevicsIvan2 Hi Ivan, we have sent you a private message. Kindly take a moment to check. Thank you</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093551805200220204</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @JacukevicsIvan2, likely regarding a personal or business matter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 03:24:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Hi Maria, thank you for bringing this to our attention and, we understand the urgency of your request. How can we help? If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093540280607621138</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry with a standard support procedure, directing users to provide booking details via DM and offering alternative contact options for non-accommodation issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 01:25:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Hi Liz, thank you for contacting us. We understand how frustrating this situation must be, especially after the property owner confirmed that a refund would be provided, and you have been waiting for an update. We sincerely regret any inconvenience caused by the delay in your refund. For us to look into this, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093510442576433237</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a delayed refund, offering to collect details via DM and directing the user to 24/7 support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 01:15:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out to us. We regret knowing about your refund, and we'd like to see how we are able to assist. For us to help you here, please DM us the following information: 
+ - Pin code 
+ - Name on the reservation
+Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093507727821586831</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a refund inquiry on X, requesting details via DM and directing customers to 24/7 support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 01:12:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>@LaibaIm93714243 Hi Laiba, we have sent you a private message regarding your inquiry. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093507062281953543</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to a user, informing them that assistance regarding their inquiry has been provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 00:36:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out to us. We understand the importance of this matter and sincerely regret to hear about the inconvenience you experienced with your flight reservation.
+We would like to inform you that we're unable to assist with flight reservations through social media, but you can contact our Flights team here: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE}+353 19075677</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093497904124035326</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about a flight reservation, apologizing and directing them to the Flights team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 00:16:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>@sufilko Hi Sufiyan, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093493000567427078</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @sufilko, asking them to check it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 23:59:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Hi Paul,
+For your security and privacy, we kindly ask that you do not share your booking details or any personal information publicly on social media.
+We look forward to receiving the requested information, so we can further review your case and assist you accordingly.
+Kind regards,</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093488571097207257</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>Booking.com reminds a user not to share booking details publicly to protect security and privacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 23:46:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Hello Brian, we regret to learn that the property could not accommodate you. On https://t.co/fGhmZE7riF, the property manages its own room availability and is responsible for ensuring it is accurate. 
+If a property is unable to honor a booking, they should assist you in finding another place to stay. If they cannot or choose not to do so, they need to notify us as soon as possible so we can help find a solution. Please send us a message with the following information:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Alternatively, for immediate assistance, you can always reach us by calling this number: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093485392309723567</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a property’s failure to accommodate a guest and offers assistance to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 23:24:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret to hear about your experience and understand how frustrating it must be to have purchased Flexible Flights and then face difficulties contacting Customer Service when you need urgent assistance. As much as we'd like to assist you, we're unable to assist with flight reservations through social media, but you can contact our Flights team here: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE}+353 19075677.</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093479821934276665</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about difficulties contacting flight reservation support, offering alternative contact methods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 23:15:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Hi Karin,
+We regret to hear about your experience and understand how frustrating it must be to have been denied boarding due to overbooking, experience a canceled return flight, and still be waiting for an update regarding your refund request after several months.
+However, as much as we would like to help you directly, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.
+Thank you for your understanding.</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093477704892920130</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about flight overbooking and refund delays, apologizing and directing the customer to the Flights team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 23:09:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>@BeSuperKind Hi there, we have replied to your private message. Kindly review it at your convenience. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093476035773735041</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @BeSuperKind, offering assistance and directing them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 20:09:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>@MCFixer Hello, we have sent you a direct message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093430781959975330</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>Booking.com posted a brief message to user @MCFixer indicating that a direct message has been sent, likely related to a private communication or potential partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Fri Aug 28 20:08:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>@Mandampally_S_K Hi there, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093430548945363046</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @Mandampally_S_K, likely for outreach or support purposes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O355"/>
+  <dimension ref="A1:O378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23204,6 +23204,1483 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 21:35:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>@FonsMans grateful for the partnership, y'all crushed</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2093814849788641398</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>Ramp thanks @FonsMans for a successful partnership, expressing gratitude and acknowledging the positive collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Sat Aug 29 21:34:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>the future of finance is beautiful</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2093814688404459619</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>Ramp shares a positive, forward‑looking statement suggesting upcoming innovations in finance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2026-08-29T20:00:01.000Z</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Brazil is a dream for art-lovers. You just have to know the right places to go.
+@andrevisockis is an art director, designer and architecture lover who has lived in Jardins for 8 years. His favorite thing about the area is the access to art galleries, incredible shopping and delicious food. 
+Renan quit his job. Then drove 250,000km across Brazil, meeting artists along the way before creating @novosparanos.
+📍Alameda Itu 1415, São Paulo, Brazil
+Novos para Nós is a home for those artists’ work, from traditional ceramics to upcycled pieces, each with a story.
+@apartamento61 is part gallery, part home. Once inhabited by Brazilian sculptor Victor Brecheret, the house is now filled with Brazilian art and design.
+Explore it with art director André Visockis, who lived there with his family for eight years.
+Visit @apartamento61 with André on @airbnbexperiences 
+For a Brazilian-Japanese dining experience, visit @quitoquitoizakayaoficial in Jardins. Chef Kaori is known for her rotating specials and infusing dishes with seasonal finds from local markets.
+📍Alameda Campinas, 1179,  São Paulo, Brazil
+São Paulo is considered a global capital for Japanese food and has the largest Japanese diaspora outside of Japan. In the 1900s, hundreds of thousands of Japanese immigrants arrived in São Paulo, where Japanese influence is now deeply integrated into the city’s cuisine. 
+Acoustic happy hour. Live local bands. 27 years in business, and run by a music legend. 
+📍R. Teodoro Sampaio, 1946, São Paulo, Brazil
+@julinho_clubeoficial is a lively music venue known for its rotating schedule of Música Popular Brasileira (MPB), jazz, and international sounds, they offer a listening experience made for musicians, by musicians.
+A street that shuts down every Sunday so the people can play? Sim, São Paulo, sim.
+📍Avenida Paulista, São Paulo, Brazil
+Once a week, Avenida Paulista turns into a full on pedestrian playground. Musical performances, street vendors, and food trucks line the usually traffic-ridden road, giving locals a community space to make the weekend last as long as possible.
+Save this for your Brazil trip (or start planning one, like now).</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/789399004_18628759132063838_287854462018285199_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3Mzk2OTk2ODMyNDk1NTk1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=poUrYxhEbdMQ7kNvwGlP8n9&amp;_nc_oc=AdodW9nDmjPKhTlzt3HLYH2aFvlXn9-rrPHSfeWYo_q7KMgpRnEP64Wxlapo1A2hSVA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=DFXrw_L1GUCHWnKqrLWgBQ&amp;_nc_ss=7a22e&amp;oh=00_AQJmwFz6WHTh0U5zyT2ieRHslPJYPM0mKRlZJzci-uK1wQ&amp;oe=6A9A2DA0</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcovsZKlOcp/</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>Airbnb is promoting new art‑centric experiences in Brazil, spotlighting local venues, artists, and cultural hotspots in São Paulo to attract travelers to its expanded offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 18:01:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>@MihirKapurbxks Hi Mihir, we have replied to your private message; kindly review it at your convenience. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094123297675833402</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a private message from user @MihirKapurbxks, inviting them to review the reply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 17:52:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Hi Nina,
+Thank you for getting back to us. We regret to hear that you have still not received a response after 23 days, and we understand how frustrating this situation must be.
+Unfortunately, as we mentioned previously, we are unable to access or review your case through our social media platform without first verifying your reservation details. To help us locate your booking and check the status of your inquiry, please send us the following information in a private message:
+- Reservation number
+- PIN code
+- Name on the reservation:
+Once we receive these details, we will do our best to review the situation and assist you accordingly.
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094121145997893904</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, requesting reservation details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 17:04:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Hi there, we regret the unpleasant experience you had and understand how distressing it must have been to face loud music, shouting, and abusive language late at night. For us to check this further, please DM us the following details:
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094109136573112785</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a negative guest experience involving loud music and abusive language, offering to collect reservation details via DM or phone for further investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 15:04:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>@Mili_M_X Hi Mili, we're unable to assist with flight reservations through social media, but you can contact our Flights team for a follow-up here: https://t.co/BfbildlU73, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE}+353 19075677. Many thanks.</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094078860358738105</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the Flights team or call the provided numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 13:31:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>@mukesh_nihalani Thank you for letting us know. Best wishes.</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094055530423603575</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Booking.com responded politely to a user, thanking them for the information and offering best wishes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 08:07:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>@MohamedHas859f Hi Mohamed, we have replied to your DM. Please have a look at our response and let us know. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093973764128002559</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, directing them to review the response and provide feedback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 06:29:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>@PetrStiebitz Hi there, we have already replied to your DM. Please review it whenever you have time. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093949113423315129</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, encouraging them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 06:28:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Hi Lucía, we apologize for the delay in our response. If you need assistance with an accommodation booking, please send us a private message including:
+- Confirmation number
+- Pin code
+- Name of the guest
+And we'll try to get back to you as soon as possible. 
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK.</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093948937191264766</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response and clarifies that social media support is limited to accommodation bookings, directing other inquiries to a dedicated support team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 01:35:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Hi Paul, thank you for reaching out to us, and we truly appreciate your patience. We’re currently experiencing higher volumes than usual and are doing our best to get back to everyone as quickly as possible.
+We regret to hear about the confusion regarding editing your booking group. To help you further, could you please provide more detailed information about your concern? If this is related to an accommodation reservation, please send us a private message with the following information:
+- Confirmation number 
+- Pin code 
+- Name on the reservation
+Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here:https://t.co/tuuNbmGVaG</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093875115591131204</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s inquiry about booking confusion, apologizes for delays, and directs them to provide details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 01:34:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>@jakemc_10 Hi there, thank you for reaching out to us. We have sent you a private message regarding your concern. When you have a moment, please check your DM and review the details we have provided.</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093874866076135616</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry on X, directing them to check their private message for details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 01:07:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for bringing this to our attention, and we apologize for our delayed response. We understand how frustrating it must be to find that the room amenities differ from what was advertised. We regret to hearing about this experience you encountered.
+For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your stay:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093868097253835109</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about room amenities, apologizes for the delayed response, and offers private messaging and phone support for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 01:06:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret the frustration you’ve experienced and understand how discouraging it must be to send multiple emails without receiving a response. For us to check this, please DM us the following details:
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093867947433292204</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for delayed responses to a customer complaint and directs the customer to provide details via DM or call their 24/7 support line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 01:02:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>@ise1234 Hello, we have sent you a direct message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093867004738338858</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>Booking.com sent a direct message to user @ise1234, prompting them to check their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 00:53:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Hi Wade, thank you for reaching out to us. We regret to hear that you are unable to open the message from the guest. Unfortunately, for security purposes, we are unable to offer support to our partners via social media. However, you can find the contact information for our Partner Support team here: https://t.co/QpD1nP4Qdu</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093864646063128847</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>Booking.com informs a partner that it cannot provide support via social media and directs them to partner support contact information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 00:52:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Hi, we regret to hear about the confusion regarding the breakfast included with your reservation, especially after arriving at the property. For us to help you further, please DM us the following details, and we'll get back to you as soon as possible:
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093864463963160756</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for confusion about breakfast inclusion, requests reservation details via DM, and offers 24/7 phone support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 00:48:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Hi Wayne, thank you for reaching out to us. We regret to hear that you are having an issue to contact our customer service team, and we'd like to see how we are able to assist. For us to help you here, please DM us the following information: 
+- Confirmation number 
+ - Pin code 
+ - Name on the reservation
+Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093863512300716333</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about difficulty contacting support, offering to collect reservation details via DM and directing to 24/7 phone support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 00:40:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>@andysmiyu Hi Andy, we've sent you a private message.  Please check it at your earliest convenience. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093861399202070787</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>Booking.com publicly announces that it has sent a private message to a user, likely for outreach or partnership purposes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 00:23:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Hi there, our apologies for the late response. We're receiving a high volume of cases on Social Media, and weren't able to reply until now. How can we help? If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
+      <c r="J376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093857119355203925</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>Booking.com acknowledges a high volume of social media inquiries and provides instructions for booking-related support while directing other service requests to dedicated teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 00:19:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>@Qdubf110602 Hi there, our apologies for the late response. We're receiving a high volume of cases on social media and weren't able to reply until now. We have replied to you via private message; you may check it at your convenience. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093856126534041991</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response and informs the user that a private message has been sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Sun Aug 30 00:12:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Hi Nick, thank you for bringing this to our attention. We regret to hear that the property wasn’t able to accommodate you and that you did not receive the necessary assistance. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+If a property can’t honor a booking, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution. Please send a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2093854433939423281</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint about a property failing to accommodate a guest, offering assistance and requesting booking details.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O378"/>
+  <dimension ref="A1:O408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24681,6 +24681,1908 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 15:29:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Doing this same travel math but for a team offsite in Des Moines &amp;gt;&amp;gt;&amp;gt;&amp;gt;&amp;gt;&amp;gt;</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2094447403705213112</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>Navan posts a casual note about calculating travel costs for a team offsite in Des Moines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 17:55:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>@gregisenberg AI really is a line item</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094484293837873482</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Brex notes that AI is becoming a distinct line item in budgets, highlighting its growing importance in the company's operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 17:15:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Control freaks, this one's for you. Our new p-card policies set the rules, set the limits per card, and keep spend exactly where it should be. https://t.co/PMhpopNt7L</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094474044129095957</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Brex introduces new p-card policies that let users set rules and limits per card to keep spending in check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 13:36:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>@MollySOShea what a view</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094419164974743654</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>Brex posted a brief, positive tweet praising a view, likely accompanying a scenic photo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 13:33:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>We built a control plane + data plane split to make rebuilds repeatable at scale https://t.co/aezRE4JpCp</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094418411648405690</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>Brex announced a new architecture that separates the control plane from the data plane, enabling repeatable rebuilds at scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 12:33:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>@DavidSantMon New office, big builder energy.</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094403244474736993</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>Brex announces the opening of a new office, signaling continued growth and expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>2026-08-31T15:55:01.400Z</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Think the ultimate European getaway means fighting for space on crowded Mediterranean beaches? The real magic is in Spain 🇪🇸
+➡️ The Architecture: Wander the breathtaking Moorish courtyards of the Alhambra in Granada.
+➡️ The Culture: Get lost in the vibrant alleys of San Sebastián and taste world-class pintxos.
+➡️ The Stays: Skip the massive coastal resorts and sleep in a beautifully restored historic parador inside a medieval castle.
+Check out our Spain travel guide here: http://ms.spr.ly/6048aKlAj</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQGlVNJlYGmhQg/image-shrink_1280/B4EaBVy473JUAc-/0/1788145799176?e=1788807600&amp;v=beta&amp;t=4_fDsd6uWGLfdJ5OmzqsHS8zGveBAW_fF46_Ve2EKWg</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_think-the-ultimate-european-getaway-means-activity-7500219605949280257-gqi9</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Expedia promotes a new Spain travel guide, highlighting Moorish architecture, vibrant culture, and historic stays, encouraging travelers to explore Spain beyond crowded beaches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 17:45:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>@yaman78392694 Hi Yaman, thank you for reaching out. We regret to hear about your situation. We've sent you a private message regarding this matter. Kindly check it at your earliest convenience, so we can assist you further. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094481768371916879</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry, offering to assist via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 15:47:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>@puppeim Oi, lamentamos saber que teve problemas com uma reserva não finalizada. Se precisa de mais informações por favor nos envie uma mensagem privada para verificarmos isso para si. Muito obrigado. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094452073693622738</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s complaint about an incomplete reservation, offering to investigate the issue via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 14:45:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>@Whiteni85484994 Hi there, thanks for reaching out to us. For us to look into what happened feel free to DM us with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request: https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094436320642793561</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer inquiry, requesting confirmation details to investigate a request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 14:29:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>@solangeen_I Bonjour Moha, nous vous avons envoyé un message privé contenant davantage d’informations concernant votre demande. Nous vous invitons à le consulter et à nous faire savoir si vous avez des questions.
+Bien à vous</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094432374624776538</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that a private message has been sent with further information regarding their request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 13:57:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>@Cheweeman Bonjour, nous regrettons de lire votre déception. Nous vous avons envoyé un message privé contenant davantage d’informations concernant votre dossier. Nous vous invitons à le consulter et à revenir vers nous.</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094424295673872868</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user’s complaint via direct message, offering further information and encouraging the user to review the private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 13:55:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>@CoralineFont Bonjour, 
+Nous allons vous répondre en message privé. 
+Merci de votre patience.</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094423720601289136</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, indicating they will respond via private message and thanked the user for their patience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 13:49:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Hallo, wir bedauern es zu hören, dass Ihre Buchung storniert wurde. Damit wir uns das anschauen können, bitten wir Sie darum, uns eine DM mit folgenden Buchungsdetails zu senden: 
+- Buchungsnummer
+- Pin Code
+- Name des Gastes 
+Wir kommen dann so schnell wie möglich wieder auf Sie zurück.</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094422273289490657</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a canceled booking and asks the customer to send booking details via DM for investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 13:44:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>@EgalEH17 Hallo, wir haben auf Ihre DM geantwortet. Prüfen Sie diese gerne, sobald Sie können und kommen dann wieder auf uns zurück.</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094421112746561732</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @EgalEH17, directing them to review the DM and respond later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 13:00:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Hi Tony, we regret to hear the hotel wasn’t able to accommodate you. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+If a property can’t honor a booking, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution. Please send a direct message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094410090505769161</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a hotel not accommodating them, explaining that property availability is managed by the hotel and requesting details for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 12:53:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>@AjeCynthia And if you need us again, we're here. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094408188774711699</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user on X, offering continued support and availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 12:23:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>@RyanC2408 Hi Ryan, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/BfbildlU73, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094400775740858597</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to the Flights team contact options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 12:21:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Bonjour Valentin, merci de nous avoir contactés et pardonnez notre réponse tardive. Sachez que nous aimerions vous aider, mais nous n'avons pas accès aux réservations de véhicules via les réseaux sociaux. Nous n'avons aucune visibilité sur la base de données utilisée par notre partenaire pour retrouver votre réservation de voiture. Nous n'avons accès qu'aux réservations d'hébergement.
+Cependant, vous pouvez contacter notre équipe spécialisée aux coordonnées suivantes : https://t.co/Th6tis0gSX
+Ils seront les seuls à pouvoir vous fournir l'assistance nécessaire pour toute question relative à la location de votre voiture. Nous vous remercions pour votre compréhension.
+Bien à vous.</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094400118317334602</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s inquiry about a car rental reservation, explaining that they cannot access vehicle bookings via social media and directs the user to a specialized team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 11:32:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Gracias por contactarnos. Cuéntanos, ¿en qué podemos ayudarte?. Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Además, por el momento solo ofrecemos soporte para reservas de alojamiento a través de las redes sociales. Para preguntas sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí:  https://t.co/TBejpc4vOA.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094387838611558404</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies that its social media support is limited to lodging reservations, directs customers to call 24/7 for immediate help, and provides links to specialized teams for flights, taxis, and insurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 11:26:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>@AjeCynthia We are glad to hear that you received your refund, Aje! Wishing you a nice rest of the day!</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094386371569860721</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user confirming receipt of a refund and wishing them a good day, demonstrating customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 11:20:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>@mn_flor40924 Lo sentimos, Flor. Respondimos tu mensaje privado.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094384876405338461</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user’s private message with an apology, indicating a routine customer service interaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 11:13:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Hi Steve, thank you for contacting us. We regret hearing that the offer couldn't be applied. We'd like to look review what happened and take a look at the proof you provided. Feel free to DM us your booking details:
+- Confirmation number, 
+- PIN-code, 
+- Name on the reservation,
+so we can follow up.</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094382976272363599</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about an offer not applying, asking for booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 10:55:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Hi Blair, our apologies for the late response. We're receiving a high volume of cases on Social Media, and weren't able to reply until now. We regret to hear that you are not satisfied with our customer service team. For us to help you here, please send us a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094378543073353965</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response to a customer complaint and directs the user to private messaging for details, offering 24/7 phone support as an alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 10:40:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>@JoshMJWright Hi Josh, we regret to hear about this. Although, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/BfbildlU73, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094374886361674017</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s inquiry about flight reservations, offering contact details for their Flights team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 10:26:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>@cascadingsense Hello Aneta, if you could send us the booking details via direct message as outlined below, we will be able to report this internally: 
+- Confirmation number: 
+- Pin code: 
+- Name on the reservation. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094371200583561472</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting booking details from a user via direct message, likely for internal reporting purposes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 10:13:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Lamentamos la tardanza en nuestra respuesta y los problemas que has tenido con tu reserva. Ten en cuenta que no proporcionamos asistencia inmediata a través de las redes sociales. Si necesitas que revisemos tu situación, envíanos un mensaje privado con la siguiente información:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+Como opción, para recibir ayuda inmediata, siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094367869681225787</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for delayed response and directs customers to private messages or phone for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 16:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>We couldn't have won gold at last year’s Travvy Awards without you. We're nominated again for Best Airline Consolidator at the 2026 awards!
+Voting closes on September 4, so click the link to vote for us!  https://t.co/e7UaSda3Eg
+#TravvyAwards2026 #SkyBirdTravel #VoteForSkyBird https://t.co/RCFy6BtYeQ</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2094455172927996058</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel announced its nomination for Best Airline Consolidator at the 2026 Travvy Awards and urged followers to vote before the September 4 deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:00:13.485Z</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>We couldn't have won gold at last year’s Travvy Awards without you. We're nominated again for Best Airline Consolidator at the 2026 awards!  
+Voting closes on September 4, so click the link to vote for us!  https://lnkd.in/eQAs2phh 
+#TravvyAwards2026 #SkyBirdTravel #VoteForSkyBird  #BestAirlineConsolidator</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQHwjs7IKRmU_Q/feedshare-shrink_1280/B4DaA4iWG2KQAM-/0/1787654923247?e=1789603200&amp;v=beta&amp;t=Lnffq7NkLjOvZ31jqsUNnV9Z9-aHgUnLudlPXU5rBJ0</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_travvyawards2026-skybirdtravel-voteforskybird-activity-7500220914928902145-ryrr</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel celebrates its nomination for Best Airline Consolidator at the 2026 Travvy Awards and urges followers to vote before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 11:50:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Hi Tom, thank you for contacting us. We regret hearing that you were unable to make it within the check-in hours and were unable to cancel the reservation. Please note that the reservation policy remains leading, and as the policy is provided by the accommodation, we can only request them to make an exception. If you still need support, feel free to DM us the booking details:
+- Confirmation number, 
+- PIN-code, 
+- Name on the reservation,
+so we can see if there's anything we can do to help.</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094392310926627288</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents responds to a customer complaint about being unable to cancel a reservation due to check‑in hours, offering to review booking details to see if assistance can be provided.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O408"/>
+  <dimension ref="A1:O439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26583,6 +26583,1957 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 15:45:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>"1 like isn't a lot" now imagine your flight taking off on time even once this summer</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2094813785781330253</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Navan promotes its improved flight punctuality, encouraging customers to anticipate on-time departures this summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 16:57:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>every ramp video needs a skateboard</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr"/>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2094831994005823893</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Ramp shares a playful caption for its video content, highlighting the brand’s creative approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 22:44:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>@tylerxdev @KlausCodes The free advertising is crazy https://t.co/lqPbclmaoO</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2094556981075845219</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Ramp is promoting its free advertising feature, emphasizing its impressive impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 18:17:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>@linear Absolute Inspect https://t.co/zBt0ieRYdh</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2094489794759827647</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Ramp highlights a collaboration with Linear on the Absolute Inspect initiative, directing followers to additional details via the provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 17:27:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>https://t.co/lzSRVRa3MM</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094839596530151560</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Brex announces a new product feature to enhance corporate card management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 16:57:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>@startupideaspod this playbook&amp;gt;&amp;gt;&amp;gt;</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr"/>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094831999747805478</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Brex shares a playbook with the Startup Ideas Pod, likely offering guidance or resources related to its services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 16:56:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>@ashleevance working🫡</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094831812367241593</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Leadership Changes</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>Brex acknowledges @ashleevance working, suggesting a new team member or ongoing activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 16:55:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>nobody should have to ask twice for an expense approval</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094831508741611547</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>Brex highlights a new feature that eliminates the need for multiple expense approval requests, positioning it as a smoother, more efficient expense management solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 15:43:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>@startupideaspod noted🗒️</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2094813402577154063</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>Brex briefly acknowledges the Startup Ideas Podcast in a tweet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 20:15:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Dernière chance pour profiter d'offres estivales ⏰
+Si vous attendiez un signe pour faire une escapade au Canada, le voici. Les membres canadiens économisent 25 % ou plus sur certains séjours jusqu'au 31 août 2026. Trouvez aussi des offres sur des forfaits, des vols et bien plus, partout au Canada.
+Les offres sont valables dans les hébergements participants seulement. Cliquez sur chaque offre pour confirmer les prix, la disponibilité et les conditions générales applicables.
+Réservez ici : https://t.co/lHl2ff3bS1</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2094519346785575251</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a limited‑time summer discount of 25% or more on select Canadian stays, along with deals on packages and flights, valid until August 31, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Mon Aug 31 20:15:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Last chance for summer deals ⏰
+If you haven't escaped somewhere in Canada yet, this is your sign. CA members only save 25%+ on select stays until August 31, 2026—plus deals on packages, flights, and more across Canada.
+Deals on participating properties only. Please click through to individual deals to confirm prices, availability and applicable terms and conditions for these deals.
+Book here: https://t.co/afoYyDemp5</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2094519346517164100</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a limited‑time summer discount for Canadian customers, offering 25%+ savings on select stays and additional deals on packages and flights until August 31, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 18:12:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>@MihirKapurbxks Hi Mihir, we have sent you a private message. Please check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094850891828310038</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @MihirKapurbxks, asking them to check the message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 17:44:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>@MzKdotTdot Hi there, we sent you a message privately. Please check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094843868814475603</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @MzKdotTdot, asking them to check their private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 15:40:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094812732272914832</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer issue by directing them to private messaging for booking details, offering 24/7 phone support, and clarifying that only accommodation bookings are handled via social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 12:49:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Hi there, we regret learning that your flight has been cancelled and you're still waiting on your refund.  While we would love to assist you with this matter via social media, we regret to inform you that we cannot provide assistance with flights through this platform. You can reach our Flights team using this link: https://t.co/OVuF5pCzba or by calling {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094769589439664306</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a flight cancellation refund delay and directs customers to the Flights team via a link or phone numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 10:41:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Hola de nuevo, nos apena saber que has tenido una mala experiencia dentro del alojamiento que reservaste. Como te explicamos anteriormente, puedes contactarlos directamente para preguntarles si cuentan con alguna póliza de seguro antirrobo dentro de sus instalaciones. De igual manera, te aconsejamos acudir a las autoridades correspondientes de la localidad donde ocurrieron los hechos para que puedan asesorarte, reportes lo sucedido y puedas realizar la denuncia que se te indique. Que tengas un buen día.</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094737312445800749</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about a bad experience at a property, offering to contact the property for insurance and advising to report to local authorities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 10:33:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>@ExploringAlway Hi there, we are here to help you. 
+If you'd like us to take a look at your reservation, please send us a private message with the following: 
+- Confirmation number: 
+- PIN code: 
+- Guest name on reservation 
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094735434731356287</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Booking.com is offering to help customers with reservation issues via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 10:02:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>@DanielMcGih2zn Hi Daniel, we apologize for the late response. 
+For us to be able to look into this, and take appropriate action, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094727628338966559</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s inquiry, apologizing for a delayed reply and requesting booking details via DM to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 09:46:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Bonjour Andreas, merci de nous contacter ici et pardonnez notre réponse tardive. Nous sommes au regret de lire les difficultés rencontrées avec votre réservation. Si votre demande concerne une réservation d’hébergement, envoyez-nous les informations suivantes par message privé et nous vous répondrons au plus vite :
+- Le numéro de réservation
+- Le code confidentiel
+- Le nom complet du voyageur
+- Un résumé de la situation
+En revanche, si vous avez besoin d'aide pour une réservation de billets d'avion, nous vous invitons à contacter le service client dédié aux vols via ce lien https://t.co/KkSQd8iIp6, ou à appeler le +6627873018/ {FR} +33 187 153 614 / {BE} +32 270 067 90.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094723486920905037</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint in French, offering detailed steps to resolve reservation issues and directing flight booking inquiries to a dedicated service link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 09:30:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Hola Alejandro, lamentamos haber tardado en responder. Estamos recibiendo un gran volumen de casos en las redes sociales y no hemos podido responder hasta ahora. Nos apena mucho enterarnos de tu experiencia, y por mucho que nos gustaría ayudarte, no podemos ofrecer soporte para reservas de alquiler de coches a través de las redes sociales. Te sugerimos que te pongas en contacto con nuestro equipo especializado aquí: https://t.co/NT3GBtSRDt. Un saludo.</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094719516680855842</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response and informs a user that car rental support cannot be provided via social media, directing them to a specialized team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 09:24:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Hola, Emmanuel. Lamentamos que aún estés esperando tu reembolso. Dinos, ¿cómo podemos asistirte?. Para atender tu solicitud, envíanos un mensaje privado con la siguiente información y te responderemos lo más pronto posible: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que figura en la reserva: 
+- Detalles de tu solicitud: 
+Ten presente que nuestro equipo de Redes Sociales no está disponible en tiempo real. Para obtener asistencia inmediata, contacta a nuestro equipo de Atención al Cliente que está disponible las 24 horas, los 7 días de la semana; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb 
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094717918067986556</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s pending refund request, asking for confirmation details and directing them to 24/7 customer support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 09:21:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing about your experience. We hope you were able to communicate any problems directly to the property while you are there, as they are in the best position to address and resolve any concerns.
+For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your stay:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094717385534026042</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint, offering private message support and a phone contact for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 09:20:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Hi Yasir, we regret to hear about your experience. If double bookings were made, even if it was by mistake, you would be charged for both reservations. As our social media team cannot help with attractions, the best thing is to reach out to our specialized team and see if they can do anything to help. You can reach them here: https://t.co/KtfexrrGCB. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094717120781197598</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s complaint about double bookings, explaining the policy and directing the user to a specialized support team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 08:57:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>@voiceplatter Hi there, as much as we'd like to assist you, we're unable to offer support for Attraction reservations through social media. You can get in touch with our specialized team here: https://t.co/7cUNKs3dwk</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094711160129871946</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that it cannot provide support for attraction reservations through social media and directs them to a specialized team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 08:48:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>@egrinsteadmick Hi Joe, we regret to hear about your experience with refund.
+If you'd like us to take a look at your reservation, please send us a private message with the following:
+- Confirmation number:
+- PIN code:
+- Guest name on reservation
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094709079717359713</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s refund issue by offering to investigate the reservation and requesting confirmation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 08:48:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Hi there. This doesn't sound right, and we're here to help. If the property was unable to accommodate you, they should have offered you a solution. For us to look into this and assist you, please send us a private message with the following details of your booking:
+- Confirmation number
+- PIN
+- Name on the reservation
+And we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094708866168627434</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Booking.com is offering assistance to a customer who had difficulty with a property, requesting booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 08:46:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Hi Trevor, apologies for our delayed response. We regret to hear about what happened. We'd like to look into this, and see how we can help you. To proceed, kindly send us a DM with the following information:
+-confirmation number
+-PIN code
+-full name of the guest
+And we'll get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094708553202180366</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizing for the delay and offering to investigate by requesting confirmation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 08:33:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>@anthodvt Pour des raisons de sécurité, nous ne pouvons pas assister nos partenaires via les réseaux sociaux. Cependant, vous trouverez les coordonnées de notre équipe Partner Support ici : https://t.co/oK8asfsShG?</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094705139361718408</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Booking.com informs a partner that it cannot provide assistance via social media due to security reasons and directs them to partner support contact information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 08:32:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>@anthodvt Bonjour, toutes nos excuses pour le délai de réponse. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons malheureusement pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094705025318564158</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>Booking.com apologized for a delayed response to a user, citing a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 08:23:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>@goldenkay8 Hi Kay, we regret to hear that your reservation has been cancelled.
+If you'd like us to take a look at your reservation, please send us a private message with the following:
+- Confirmation number:
+- PIN code:
+- Guest name on reservation
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094702716593283472</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user about a cancelled reservation, offering to investigate and requesting confirmation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 08:20:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>@simas_ch Hi Simon, we regret to hear about the charge. Please send a DM with your: 
+-reservation number 
+-pin code 
+-name of the guest 
+Looking forward to hearing from you.</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2094701811642810631</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user’s complaint about a charge, asking for reservation details via direct message.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O439"/>
+  <dimension ref="A1:O483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28534,6 +28534,2866 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>2026-09-02T15:54:35.091Z</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>What does a truly frictionless, AI-first travel program look like? Ask Block.
+When the global financial technology company joined forces with Navan, it saw:
+→ A 96% CSAT
+→ Support across 20 countries
+→ A travel platform built to help employees move faster and stay self-sufficient
+As Block continues to embed AI across the business, we're helping its travel program do the same 🤝 
+Read more on their story → https://lnkd.in/e3zhqH-p</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E05AQH7VR-kMjMd8g/mp4-720p-30fp-crf28/B4EaBi1C7AH4CQ-/0/1788364469629?e=1788980400&amp;v=beta&amp;t=3Pw-yEPoDWwjZrN_NtVDsmTUXAMvaD9AOma0LvZhcsA</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_navan-x-block-case-study-activity-7500944271332532224-IllZ</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Navan partnered with Block to deliver an AI‑first travel platform, reporting a 96% CSAT and support across 20 countries, highlighting the partnership’s success and AI integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>2026-09-02T17:57:17.000Z</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How do you make change easier for employees?
+</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1RSwLHFR2B8</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1RSwLHFR2B8</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>2026-09-02T17:54:12.000Z</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BMW S.L.P. e SAP Concur: 10 anos transformando a gestão de viagens e despesas
+</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yLtCk5DrbU4</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yLtCk5DrbU4</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>2026-09-02T18:00:11.000Z</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How do you empower employees to solve problems on their own?
+</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g7I5ADHidq8</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g7I5ADHidq8</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>2026-09-02T18:04:26.000Z</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henkel Success Story: Spend management with SAP Concur
+</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bGlOPNLoHdI</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bGlOPNLoHdI</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>2026-09-01T21:34:30.000Z</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complete by SAP Concur and Amex GBT: Connected Travel and Spend for Public Service
+</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iQqlVRsw3xE</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iQqlVRsw3xE</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 22:20:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>@RampLabs ( ͡♥ ͜ʖ ͡♥)</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2094913230657257598</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>Ramp posted a brief, positive mention of RampLabs with heart emoticons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Tue Sep 01 22:16:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>THE ROI OF AI IS UPON US</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2094912421617979523</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Ramp announces the ROI of AI, indicating a new AI-driven product or feature launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 17:31:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>@medianfi Spend moves fast. Closing your books should too.</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2095202883306127704</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Brex promotes a new feature that accelerates the process of closing financial books, positioning it as a faster alternative to traditional spend management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>TripGenie</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>trip</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>2026-09-02T09:11:08.000Z</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>5 days, two sides of Thailand 🇹🇭✨ Start with Bangkok’s temples, markets and riverside energy, then slow things down with colorful streets, coastal views and tropical mornings in Phuket. Save this itinerary for your next Thailand trip. ✈️
+👍Visit our bio for more travel inspirations and deals. 
+🤩Follow us to get more travel inspirations @trip. 
+#thailand #bangkok #phuket #thailandtravel #tripcom</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788438686_18617125312002228_5420788125403107318_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjkyMjY2NDcxNzM3Mjg3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MEFKIF1HZrAQ7kNvwEJyInu&amp;_nc_oc=Adr7VhaeF9Vi7-JubNEiQscIhHEME1OCbHgXRGGQC0y5AsqROagSgILGvi70tjZxvco_Eq-QMcGXqytM4YrDcuji&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=eAeWAiPu0WrJfsT5UJG6RQ&amp;_nc_ss=7a22e&amp;oh=00_AQI_rlMMW9xsqy8-1-lFiwa4Q2dObwP5pwH-GRSjEvlhZQ&amp;oe=6A9E1FBB</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc5lv4Vkydh/</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>TripGenie promotes a 5‑day Thailand itinerary featuring Bangkok and Phuket, encouraging followers to save the post and follow for more travel inspiration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 16:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>It's our 30th anniversary, and we're ready to celebrate with you until October 7th, US residents!
+ For three days only, Expedia One Key members earn 30% more OneKeyCash™ in the app on eligible hotels and vacation rentals from Sept 2–4. Plus, get 25% off select packages and great deals on cars and flights. Members can also save 15%+ on select activities and 10% on select cruises. Sale ends 10/7/26. Terms apply. 
+ Book now: https://t.co/ObK7uw5Bdu</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2095179947929166155</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Expedia celebrates its 30th anniversary with a limited‑time promotion for OneKey members, offering extra cash back, discounts on packages, cars, flights, activities, and cruises until October 7th.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 15:37:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Prepárate para una escapada increíble en septiembre. 
+Aprovecha nuestra oferta de aniversario hasta el 7 de octubre. Solo por tres días, los socios de One Key de Expedia acumulan 30% más en OneKeyCash™ en la app al reservar casas para vacaciones y hoteles participantes del 2 al 4 de septiembre. Además, obtén 25% de descuento en paquetes seleccionados y aprovecha increíbles ofertas en vuelos. Los socios también pueden ahorrar 15% o más en actividades seleccionadas. La oferta vence el 7 de octubre de 2026. Aplican términos. 
+Reserva hoy mismo: https://t.co/1CxwYHzMot</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2095174160649420838</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a limited‑time anniversary offer for One Key members, giving extra cash back, discounts on vacation packages, flights, and activities, valid until October 7, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 15:36:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Celebrate the Expedia Anniversary Sale with us until 7 October, UK residents! 
+For three days only, Expedia One Key members earn 30% more OneKeyCash™ in the app on eligible hotels and holiday homes from 2–4 Sept. Plus, get 25% off selected packages and great deals on flights. Members can also save 15%+ on selected activities. Sale ends 7/10/26. Terms apply. 
+Book now: https://t.co/LX3Mf0Eyax</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr"/>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2095173953572712669</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Expedia is promoting its Anniversary Sale, offering enhanced rewards for OneKey members and discounts on hotels, holiday homes, flights, and activities for UK residents until 7 October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 15:36:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Celebrate the Expedia Anniversary Sale with us until October 7th, CA residents! 
+For three days only, Expedia One Key members earn 30% more OneKeyCash™ in the app on eligible hotels and vacation rentals. Plus, get 25% off selected packages and great deals on all-inclusive vacations, cars and flights. Members can also save 15%+ on selected activities and 10% on selected cruises. Sale ends 10/7/26. Terms apply. 
+Book now: https://t.co/xuEnhPpDkX</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2095173909310214353</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Expedia is promoting its Anniversary Sale, offering exclusive discounts and bonus cash to OneKey members for a limited time, targeting California residents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 15:35:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Célébrez avec nous le solde anniversaire d'Expedia jusqu'au 7 octobre! 
+Pendant trois jours seulement, les membres Une Clé d'Expedia obtiennent 30 % de plus en crédit Une Clé™ dans l'application auprès des hôtels et des propriétés de vacances admissibles. De plus, profitez de 25 % de réduction sur certains forfaits ainsi que de formidables offres sur des vacances tout inclus, des voitures et des vols. Les membres peuvent aussi économiser 15 % ou plus sur certaines activités et 10 % sur certaines croisières. Le solde prend fin le 7 octobre 2026. Des conditions s'appliquent. 
+ Réservez maintenant : https://t.co/YESaVXWnZN</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2095173656573853742</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Expedia is launching a limited‑time anniversary promotion offering extra credit and discounts on hotels, vacation packages, cruises, and more to attract members.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 00:15:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Spring into a new adventure and celebrate the Anniversary Sale until 7 October New Zealand! 
+For three days only, Expedia One Key members earn 30% more OneKeyCash™ in the app on eligible hotels and holiday homes from 2–4 Sept. Plus, get 25% off selected packages. Members can also save 15%+ on selected activities. Sale ends 7/10/26. Terms apply. 
+Book now: https://t.co/lRnJELCoH2</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2094942129093030181</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a limited‑time Anniversary Sale in New Zealand, offering OneKey members extra OneKeyCash, discounts on packages, and savings on activities from 2–4 Sept, with the promotion ending 7 Oct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 00:10:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Spring is here Australia, so shake off the winter chill and celebrate our Anniversary Sale until 7 October! 
+For three days only, Expedia One Key members earn 30% more OneKeyCash™ in the app on eligible hotels and holiday homes from 2–4 Sept. Plus, get 25% off selected packages. Members can also save 15%+ on selected activities. Sale ends 7/10/26. Terms apply. 
+Book now: https://t.co/M4CYWFdoFD</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2094941080865091692</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Expedia is promoting its Anniversary Sale in Australia, offering members extra OneKeyCash, 25% off selected packages, and additional savings on activities until October 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Get ready to eat your way through San Diego 🌮
+➡️ The seafood: Taste the freshest fish tacos right by the ocean.
+➡️ The culture: Explore Little Italy for authentic pasta, vibrant patios, and local wine.
+➡️ The stays: Sleep off your food coma in a breezy beachfront boutique.
+Use Bundle &amp; Save on your flight and hotel to unlock savings for your next meal.
+🔗 Plan your travel:
+https://t.co/9p39AmmwBt</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2094938356299805156</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Expedia promotes a San Diego travel package highlighting food, culture, and boutique beachfront stays, encouraging customers to use bundle &amp; save for flight and hotel bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>BBC StoryWorks</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2026-09-02T17:33:53.870Z</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>For BBC StoryWorks’ latest branded content campaign with Expedia, we spent time with the incomparable Alan Cumming as he explored everything New York has to offer: its history, its art, its food, and its endless curiosities. 
+From the swankiest spots to the city's hidden corners, Cumming showed that there’s a New York for everybody.
+🍎 Explore Alan Cumming’s New York: https://lnkd.in/gkhYAuhn
+#BBCStoryWorks #Travel</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D5605AQEUPpDPuaB0fg/mp4-720p-30fp-crf28/B56aBjBpZLJkB8-/0/1788367777832?e=1788980400&amp;v=beta&amp;t=G-nFQ_SIt9JBsUPQ1zkF2L1Z81Hd4jpB_U0nX40Rnoo</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/bbc-storyworks_bbcstoryworks-travel-ugcPost-7500958028456726528-yZoS</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Expedia partnered with BBC StoryWorks to create a branded content campaign featuring Alan Cumming exploring New York City, showcasing the city’s diverse attractions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Expedia Group Advertising</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>2026-09-02T13:05:44.344Z</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Travel is more than the places we visit. It’s the stories, people, and personal connections that bring a destination to life. 
+Expedia Group Advertising and BBC Studios are launching On Location, a new branded content series created by BBC StoryWorks. 
+The first installment, On Location: New York, stars Emmy and Tony Award-winning actor Alan Cumming, and explores the city through the personal experiences, people and places that have shaped his connection to it. 
+For travelers, the series shows how powerful storytelling can inspire meaningful travel experiences.  
+For brand partners, On Location offers an opportunity to align with premium storytelling while reaching relevant travel audiences from discovery through planning.  
+ ➡️ https://lnkd.in/eX2DsdKp</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQGKzXFA9ioZ0g/feedshare-image-high-res/B4EaBiOMjmHAAU-/0/1788354284833?e=1790208000&amp;v=beta&amp;t=VzGIcUkxhNc-L_0fgpJkzD6rf_7_W5Mzlgmdi4chqqA</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia-group-advertising_travel-is-more-than-the-places-we-visit-activity-7500901535501950976-UKr9</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Expedia partners with BBC Studios to launch the branded content series "On Location", featuring Alan Cumming exploring New York, aimed at inspiring travelers and offering brand partners storytelling opportunities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>BBC Studios Advertising</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>2026-09-02T15:30:09.102Z</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>In its latest branded content campaign produced for Expedia, BBC StoryWorks created a digital film in which Alan Cumming explored everything New York has to offer: its history, its art, its food, and its endless curiosities. 
+The campaign highlighted everything from the swankiest spots to the city's hidden corners, showing that there’s a New York for everybody.
+🍎 Explore On Location with Alan Cumming in New York: https://lnkd.in/gfzdMM4a 
+#BBCStoryWorks #Travel</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/bbc-studios-advertising_alan-cummings-new-york-activity-7500931421813919744-bFuR</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Expedia partners with BBC StoryWorks to produce a digital film featuring Alan Cumming exploring New York City, highlighting its diverse attractions and appealing to a broad audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 17:36:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>@JohnboySafc07 We understand your frustration, John. For GDPR reasons, only our specialized team has access to your information and the tools required to help.</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095204119690522626</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s frustration over GDPR restrictions, stating that only a specialized team can access the user’s information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 17:31:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>@LiliaMurtaovt8 Hi Liliia, thanks for reaching out. We’ve replied to your private message. Please check your inbox, and we’ll continue assisting you there.</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095202994736267680</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 17:17:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Hi Lord, we understand how disappointing and frustrating this experience must have been, especially as it has led to concerns regarding your refund request. We appreciate you bringing this matter to our attention.
+In order for us to escalate this further and review your case, please send us a private message with the following information: 
+- Confirmation number: 
+- Pin code: 
+- Name on the reservation: 
+- Details on your stay: 
+We'll get back to you as soon as possible. Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095199335973617894</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering to review the case and providing contact details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 13:45:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Hola Manuel, vemos que también te has puesto en contacto con nosotros a través de Instagram y Facebook, y que ya hemos respondido a tus mensajes y comentarios en ambas plataformas. Te invitamos a revisar nuestras respuestas cuando tengas oportunidad y a responder directamente por Instagram, si tienes más preguntas. En el futuro, te recomendamos que nos contactes solamente por una plataforma, esto con el fin de evitar confusiones o retrasos al tener dos o más conversaciones activas en diferentes canales. Gracias.</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095145994656575941</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user who contacted them via multiple social platforms, advising them to use a single channel to avoid confusion and delays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 13:31:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>@pimspimz Thank you for your response. The link does not open a particular listing. Please let us know the exact name of the property, so we could look it up.</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095142473383215281</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user, requesting the exact property name to resolve a broken listing link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 13:17:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>@liberta33 Nous vous avons envoyé un message privé contenant davantage d’informations concernant votre demande. Veuillez le consulter et nous indiquer si vous avez des questions. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095139158155051433</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @liberta33 with additional information regarding their request and invited them to review it and ask any questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 12:51:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>@Isabellmf_ Hola Isabel, debido a que no nos sigues, no podemos responder a tu mensaje. Si deseas dar seguimiento a tu solicitud, puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/4JERadEHHC</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095132593603715078</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that they cannot respond to their message because the user does not follow them, and directs them to contact customer support via a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 12:36:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>@johnmpdq Hi John. We have responded to your private message, please check your inbox. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095128765206520273</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @johnmpdq, directing them to check their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 11:46:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>@doddy36 Hi Stephen, we are solidly explaining to you the situation and how we can assist you on that. Should you like to accept our help offer, please feel free to DM us with the information we've mentioned needing, and we'll look into that for you.</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095116242000441424</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>Booking.com is offering assistance to a user via direct message, indicating routine customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 11:43:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>@SanlarisMusic Hola, nos alegra que ya hayas podido entrar en contacto con atención a clientes. Si vuelves a necesitar asistencia, estamos aquí. Saludos.</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095115462916944263</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user on X, expressing gratitude for reaching out to customer service and offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 11:29:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>@cardiiwara_ Respondimos tu mensaje privado.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095111945682669812</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @cardiiwara_, acknowledging the communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 11:11:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>@GraemeAlexpcm Thank you. We have reviewed the booking and previous communication, and we regret to learn about your experience.
+As we can see the booking has been refunded, and the compensation for price difference after relocation has been credited to your Wallet. If you still need assistance, please let us know how we can help you.</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095107451288690949</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizes, confirms a refund and compensation, and offers further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 11:02:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Hola Isa, lamentamos saber que estás en espera de una respuesta.
+Para revisar el estado de tu solicitud, comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095105105410306072</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s pending request, providing instructions for private messaging and offering 24/7 customer support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 10:58:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Hola, gracias por ponerte en contacto con nosotros. Recuerda que puedes pedir la factura directamente al alojamiento mientras estés allí, ya sea al hacer el check-in o al hacer el check-out.
+Para revisar el estado de tu solicitud, comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095103977880776944</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>Booking.com offers guests instructions on how to request invoices and share reservation details via private message, while directing urgent inquiries to its 24/7 customer service team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 10:51:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Hola Anuska, gracias por contactarnos. Dado que es el alojamiento quien te presta el servicio y recibe el pago, solo ellos pueden emitirte una factura. Puedes solicitarla durante tu estancia, al hacer el check‑out, por correo electrónico o llamando al número de teléfono que aparece en tu correo de confirmación. Si deseas que la solicitemos en tu nombre, envíanos un mensaje privado con los siguientes datos:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095102301732040924</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>Booking.com explains that only the accommodation can issue invoices and outlines how users can request them, offering contact details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 10:44:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Hola Victoria, gracias por contactarnos. Los precios que aparecen en nuestra página son gestionados directamente por los alojamientos, pero recuerda que contamos con un programa de “Igualamos el precio” (We Price Match) si encuentras una tarifa más baja online. Puedes seguir este enlace para obtener más información:  https://t.co/ZWR77spXHo.
+Para que podamos revisar tu reserva, envíanos un mensaje privado con los siguientes datos:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+- Enlace de la página web donde has encontrado la reserva más barata
+- Captura de pantalla en la que podamos ver tipo de habitación, fechas, precio, régimen, política de cancelación y número de huéspedes
+Una vez que recibamos esta información, te responderemos lo antes posible. Gracias.</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095100645040664883</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user inquiry by explaining its price‑match program and requesting reservation details for review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 10:44:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Ciao Alessio, 
+siamo qui per aiutarti e dare un'occhiata a quanto accaduto.
+Condividi con noi in un messaggio privato le seguenti informazioni: 
+- numero di prenotazione 
+- codice PIN 
+- nome dell'ospite sulla prenotazione 
+Controlleremo e ti risponderemo al più presto. Tieni presente che il nostro team Social Media non lavora in tempo reale. Per supporto immediato, ti consigliamo di contattare il nostro team di assistenza clienti 24 ore su 24, 7 giorni su 7 - i dettagli di contatto puoi trovarli qui: https://t.co/tuuNbmGVaG . 
+Cordiali Saluti</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095100555798442299</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>Booking.com is offering customer support by requesting booking details via private message and directing the user to their 24/7 assistance team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 10:24:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Sentimos lo ocurrido con la fianza de tu reserva. Si quieres que lo revisemos, envíanos un mensaje privado con los siguientes datos y nos pondremos en contacto contigo lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre que aparece en la reserva
+Como alternativa, si necesitas asistencia inmediata, siempre puedes llamarnos aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095095473728061870</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a deposit issue and invites affected customers to send a private message with confirmation details or call for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 09:59:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>@SanlarisMusic Hola, para que podamos revisar tu caso por favor envíanos por mensaje privado esta información y te responderemos lo antes posible: 
+- Número de confirmación:
+- Código PIN:
+- Nombre del huésped que aparece en la reserva: https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095089239893389518</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting booking confirmation details from a user to review their case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 09:47:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>@zarza_jimenez Hola Ramón, los descuentos varían dependiendo de las fechas, tipo de habitación, equipo electrónico (computadora o celular) y si es cliente por primera vez, entre otras... 
+Habría que revisar todas estas variantes para revisar en dónde estuvo la discrepancia en los precios.</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095086142550843623</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>Booking.com explains that discount differences depend on dates, room type, device used, and first‑time customer status, and recommends reviewing these factors to identify price discrepancies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 16:00:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Travel lighter in India ✈️🧳 
+Skip luggage hassle with BagDrop’s Airport→Home delivery. Secure, 24/7 support, free pickup + bubble wrap, and up to 62% savings vs checked bags. Travel advisors get 10% off every booking!
+#TravelAdvisors #BagDrop #IndiaTravel #SkyBirdTravel https://t.co/cFqMef8BdR</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2095179954619109547</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes BagDrop’s airport‑to‑home luggage delivery service, highlighting 24/7 support, free pickup, and up to 62% savings, while offering travel advisors a 10% booking discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>2026-09-02T16:00:01.608Z</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Travel lighter and let your clients enjoy a seamless arrival in India. With BagDrop’s airport-to-home baggage delivery service, travelers can skip the hassle of hauling luggage and have it delivered safely to their destination. Plus, travel advisors receive a 10% discount on every booking. With free pickup and bubble wrap, 24/7 support, secure handling, and savings of up to 62% compared to checked baggage, it’s a smarter way to travel. 
+#TravelAdvisors #BagDrop #TravelToIndia #BaggageDelivery #TravelSmarter #SkyBirdTravel #IndiaTravel #HassleFreeTravel</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQEyBuwsx-In-w/feedshare-shrink_1280/B4EaBimQDdGoAM-/0/1788360590317?e=1790208000&amp;v=beta&amp;t=qnEE_NKxkKc0UPwuwqg94CWut05XxIkiXyqAih5GVoU</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr"/>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_traveladvisors-bagdrop-traveltoindia-activity-7500945640844283904-pmYd</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes BagDrop’s airport‑to‑home baggage delivery service for India travelers, highlighting convenience, a 10% advisor discount, free pickup, and up to 62% savings over checked baggage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 18:18:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>@MihirKapurbxks Hi Mihir, we have sent you a direct message regarding your concern. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095214853556224378</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents replied to a user’s concern via direct message, offering further assistance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O483"/>
+  <dimension ref="A1:O512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31394,6 +31394,1861 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 18:45:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Is it truly risky to book out-of-policy or do you possess the unshakable belief in Future You's ability to justify it?</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2095221521144746205</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Navan poses a question about the risk of booking out-of-policy and the confidence in Future You's justification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>2026-09-03T13:13:38.070Z</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>However you work, Perk keeps up. 
+Travel. Spend. One platform. Coming to the US very soon.</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQEMTQHFYAzejA/mp4-720p-30fp-crf28/B4EaBnZsy8KMBk-/0/1788441192325?e=1789048800&amp;v=beta&amp;t=Z3bU8MfsdIv5-LsdchJ4BO8Ntm620YKS8GcOcrN9X4U</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_however-you-work-perk-keeps-up-travel-activity-7501266154716348416-xR-O</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>TravelPerk is promoting its unified travel and spend platform, announcing that it will launch in the US soon as a single solution for business travel needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 22:05:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>@AdvisoryAmp @firm360 See you around the table.</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2095271891258745087</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>Brex acknowledges a forthcoming collaboration or meeting with AdvisoryAmp and firm360, suggesting a partnership or joint initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Wed Sep 02 19:04:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>all roads eventually lead back to whoever automated the thing nobody wanted to do</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr"/>
+      <c r="I487" t="inlineStr"/>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2095226363061878935</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>Brex announces a new automation feature that simplifies a previously tedious task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>2026-09-02T23:00:02.000Z</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Your favorite childhood breakfast is now an Airbnb listing 🥣 This cereal-inspired home is making waves - swipe to see what guests are saying about it.</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>https://instagram.fcdg4-1.fna.fbcdn.net/v/t51.82787-15/790491434_18630401704063838_3523002628519647459_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3NzQ3NjQ2Mjk3NDYxODc1MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjIyOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hNEWxEVRTCQQ7kNvwEKsCQJ&amp;_nc_oc=Adp5CuBlsfb4UVMft-FPUsCcS6kL_yjcKjhbTwpkJRmZyPH3PinPCmZk_Uf8sVsDIjw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcdg4-1.fna&amp;_nc_gid=Gy2-fo64rvHqqa_5UZJxgw&amp;_nc_ss=7a22e&amp;oh=00_AQJBLFcrTkQ6MKyIr6T4z3q6bTAoRAPcZmMkxIIHFYxlxQ&amp;oe=6A9F62B6</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr"/>
+      <c r="J488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DczXj1clLeG/</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>Airbnb showcases a new cereal‑inspired listing, encouraging users to swipe for guest reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 00:40:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Ready for the ultimate tropical escape in Fiji? 🌴
+➡️ The views: Discover vibrant coral reefs and crystal-clear lagoons.
+➡️ The culture: Experience genuine local hospitality and traditional kava ceremonies.
+➡️ The stays: Fall asleep to the sound of waves in an overwater bungalow.
+🔗 Plan your travel:
+https://t.co/RRy35WyTOt</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr"/>
+      <c r="H489" t="inlineStr"/>
+      <c r="I489" t="inlineStr"/>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2095310810675306653</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a tropical escape to Fiji, highlighting coral reefs, local culture, and overwater bungalows, and encouraging bookings through a link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 13:24:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>@Tyke_mc_tyke14 Hi there. We regret to hear about your experience, and we're here to help. Please send us a private message with the following details of your booking:
+- Confirmation number
+- PIN
+- Name on the reservation
+And we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095503238845923809</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering to resolve the issue via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 13:23:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Hi Sophie, we regret to hear about your concerns. Could you please send us a DM with more information on what happened? If you have an existing reservation with us, kindly DM us the following details:
+-confirmation number
+-PIN code
+-full name of the guest
+-brief information on what happened
+And we'll get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr"/>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095502976131477516</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer complaint, asking the user to provide additional details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 13:14:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Hi Shubham, we recommend that you never share the PIN code of your reservation in public as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment. We regret to hear that the accommodation you booked did not meet your expectations. We'd like to look into this, and offer further assistance. To proceed, we kindly send us the following information via a DM:
+-confirmation number
+-PIN code
+-full name of the guest</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095500579434811713</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a poor stay, advising the user to delete a public comment and requesting sensitive reservation details via DM, raising privacy and security concerns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 12:41:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Hola Laura, gracias por contactarnos. Sentimos saber que aún no has recibido respuesta. Si deseas que lo revisemos desde aquí, por favor envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+- Detalles de tu solicitud
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb. Un saludo.</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095492474244313194</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint about delayed response, offering to review the issue via private message and providing phone support details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 12:32:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Gracias Victoria. Nos apena saber que no has recibido respuesta desde el 20 de mayo. En el futuro, por favor ten en cuenta que si deseas recibir ayuda inmediata, puedes hablar con uno de nuestros agentes llamando a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros números de teléfono aquí:  https://t.co/o8QyR8SaDb
+Esperamos tu mensaje privado con los datos. Un saludo.</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr"/>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095490088293540294</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a customer for delayed response and offers phone support and a private message for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 12:23:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>@ajitdass94 Hi Ajit, thank you for contacting us. We regret hearing that the accommodation was unable to honor the reservation. We'd like to review what happened and have replied to your DM. Please take a look.</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr"/>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr"/>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095487802402042286</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about a reservation that could not be honored, offering to review the issue via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 12:06:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Hi Jessie, we regret to hear about your experience. For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your stay:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
+      <c r="J496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095483479756619900</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering to resolve the issue via private message or phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 11:58:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>@CoralineFont Nous vous avons envoyé un message privé contenant davantage d’informations concernant votre demande. Veuillez le consulter et nous indiquer si vous avez la moindre question.</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr"/>
+      <c r="I497" t="inlineStr"/>
+      <c r="J497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095481520764932212</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s request via private message, offering additional information and inviting further questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 11:28:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>@rocioserratosa Hi Rocío, we've replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095474099522875816</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, demonstrating routine customer engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 11:21:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>@yadavkrishhna Hi Krishna, we'd like to look into your price match claim. Please send your booking pin code, along with the name of the guest on the booking and we'll get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr"/>
+      <c r="I499" t="inlineStr"/>
+      <c r="J499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095472254104559880</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user’s price‑match claim, requesting booking details to process the request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 10:53:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>@KriveTravel Hi there, we just sent you a direct message. Feel free to take your time reviewing it. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr"/>
+      <c r="J500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095465093190263202</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>Booking.com sent a direct message to KriveTravel, inviting them to review a potential collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 10:52:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>@LaetMary - Numéro de confirmation
+- Code confidentiel
+- Nom indiqué sur la réservation
+Pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/PForv7yL3A</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr"/>
+      <c r="J501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095464985321206045</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user with confirmation details and offering phone support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 10:52:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>@LaetMary Nous comprenons vos inquiétudes concernant l’emplacement de l’hébergement. Afin que nous puissions étudier cela pour vous, merci de nous envoyer un message avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095464882799816752</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s concerns about accommodation location, asking for more details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 10:52:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>@LaetMary Bonjour Laëtitia, toutes nos excuses pour le délai de réponse. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095464829834166573</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response to a user due to a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 10:51:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>@KaviSrirangan Hi there, we understand the urgency of the matter. While we appreciate that you have reached out to us here, your inquiry can only be addressed directly with our specialized team at the previously shared details.</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr"/>
+      <c r="J504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095464651312029973</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry, acknowledging the urgency and directing them to a specialized team for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 10:46:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Bom dia Francisco, agradecemos pelo contato e sentimos saber disso; no entanto, agradecemos por trazer isto à nossa atenção. 
+Para poder verificar esta situação, pedimos que nos contate pelo privado com:
+• O seu número de confirmação
+• O código PIN
+• O nome do titular da reserva
+E te daremos um retorno breve. Pra suporte imediato, sugerimos o contato direto com o nosso SAC através de um dos seguintes números: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr"/>
+      <c r="J505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095463494501953900</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user’s inquiry, requesting confirmation details and offering direct support contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 10:45:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>@Daniell87310170 Hi Danielle, we've replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="inlineStr"/>
+      <c r="J506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095463067349868917</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 09:54:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Hi there, we regret learning that you're still waiting on your refund. While we would love to assist you with this matter via social media, we regret to inform you that we cannot provide assistance with flights through this platform. You can reach our Flights team using this link: https://t.co/OVuF5pCzba or by calling {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr"/>
+      <c r="I507" t="inlineStr"/>
+      <c r="J507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095450444436840828</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed refund and directs the customer to its Flights support team via a link and phone numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 09:46:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Hola, María. Lamentamos la experiencia. Esperamos que hayas podido comunicar cualquier inconveniente directamente con el alojamiento mientras estabas allí, ya que son quienes están en mejor posición para abordar y resolver cualquier incidencia.
+Para que podamos ayudarte desde aquí, envíanos por favor un mensaje privado con la siguiente información:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles sobre tu estancia:
+Te responderemos lo antes posible. Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr"/>
+      <c r="H508" t="inlineStr"/>
+      <c r="I508" t="inlineStr"/>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095448302233719074</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a guest’s negative experience and offers to resolve the issue via private message or phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 09:35:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Bonjour Will, nous regrettons de lire votre déception concernant la situation vécue. Veuillez nous envoyer les informations suivantes par message privé afin que nous puissions étudier votre demande :
+- numéro de réservation
+- code confidentiel
+- nom complet du voyageur indiqué sur la réservation
+Bien cordialement</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr"/>
+      <c r="I509" t="inlineStr"/>
+      <c r="J509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095445510748262432</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer complaint, apologizing and requesting reservation details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>2026-09-03T08:03:00.883Z</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>What does the future of more sustainable travel look like across Europe and beyond? 🌍
+In our latest fireside chat, Booking.com's Director of Sustainability sits down with Accor's Chief Sustainability Officer. Together, they explore the global customer trends shaping more sustainable stays worldwide.
+Check out this short clip to see where sustainability in travel is headed next!</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQGtNoRPomOHhg/mp4-720p-30fp-crf28/B4EaBi1LwHHkBs-/0/1788364519904?e=1789048800&amp;v=beta&amp;t=zxvlQ-Ls1AfUiZQh7OoUMHvC3OMHSzRbrMezlyUVFls</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_what-does-the-future-of-more-sustainable-activity-7501187984688451584-yS5M</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>Booking.com shares insights on sustainable travel trends in a fireside chat with Accor’s Chief Sustainability Officer, outlining future directions for eco‑friendly stays across Europe and beyond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 14:05:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Hola, gracias por escribirnos.
+Si necesitas asistencia con una reserva de alojamiento, comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr"/>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr"/>
+      <c r="J511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095513431709220950</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents informs users that they can send booking details via private message for assistance, but the social media team is not real‑time and directs them to a 24/7 customer support link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 14:01:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Hi there, how can we help? We regret hearing that you feel this way about our customer service support .If your request is related to an accommodation booking, please DM us the following details and we'll get back to you as soon as possible: 
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095512523369849235</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents informs customers that social media support is limited to accommodation bookings and directs them to phone or dedicated teams for other services.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O512"/>
+  <dimension ref="A1:O521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33249,6 +33249,566 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 16:04:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>@LivicusInvest ding ding ding</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2095543580291207349</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>Navan appears to be announcing a new partnership or collaboration with LivicusInvest, indicated by the celebratory "ding ding ding" in the tweet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 16:41:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>@aneesmerchant Hi Anees, we understand your frustration and want to take a closer look at what’s gone wrong. Sending you a DM to discuss further.</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr"/>
+      <c r="J514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2095552848306098236</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>Brex acknowledges a user’s frustration and offers to discuss the issue via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 15:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Accounting teams, this is for you. Import the exact Netsuite fields you want in one go. https://t.co/hQDU9PkaYp</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+      <c r="J515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2095527240687919168</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>Brex introduces a feature that allows accounting teams to import selected Netsuite fields in one go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 17:54:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>@melihdmrl67 Hi Melih, we have sent you a private message regarding your inquiry. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr"/>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095571149555900868</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via a private message, offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 17:37:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>@Praveen89692498 Hi Praveen, we have replied to your private message; kindly review it at your convenience. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+      <c r="J517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095566902345060442</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @Praveen89692498, directing them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 14:53:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>@blukuslukus Hi Brian, we would like to check on this refund for you. Please send us a private message with the following information: 
+- Confirmation Number
+- Pin Code
+- Full Guest Name
+Once we have these details, we can take a look and get back to you. 
+Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095525670960943276</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a refund inquiry from a customer, requesting confirmation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 14:25:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Hi Rob. All reviews are available and all positive and negative comments are shown. The review section has every single review and comment left by every guest, and it can also be filtered to show the poor scores. The little section displaying a few positive reviews is called "Guests who stayed here loved" as this particular part here is where it is only briefly mentioned what the guests were happy about.</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095518537141916066</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>Booking.com describes its review section, noting that all reviews are displayed, can be filtered, and includes a brief positive highlights segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 14:24:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>@Akhtarefi Hi there, we have replied to your private message regarding this.</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095518361639612798</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @Akhtarefi, indicating they have responded to the user's query.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 14:07:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>We regret hearing about your experience, Jayne. We hope you were able to communicate any problems directly to the property while you are there, as they are in the best position to address and resolve any concerns.
+For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your stay:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095513962531958973</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering to resolve issues via private message or phone.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O521"/>
+  <dimension ref="A1:O548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33809,6 +33809,1718 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 20:31:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>The 2026 U.S. Open is serving up world-class matches, and business travelers want in on the action.
+Early data from Navan suggests that, compared with 2025, marquee sporting events are increasingly holding court as the premier opportunities for businesses looking to bring together customers, partners, and teams.
+Now that's data that's easy to love 🎾</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2095610756889030938</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>Navan promotes the 2026 U.S. Open as a prime venue for business travelers to engage customers, partners, and teams, signaling a strategic shift toward leveraging marquee sporting events for business networking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>2026-09-03T20:31:52.354Z</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>The 2026 U.S. Open is serving up world-class matches—and business travelers want in on the action.
+Early data from Navan suggests that, compared with 2025, marquee sporting events are increasingly holding court as the premier opportunities for businesses looking to bring together customers, partners, and teams.
+Now that's data that's easy to love 🎾</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_navan-sporting-event-data-activity-7501376440937152513-AAcs</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>Navan highlights that marquee sporting events such as the 2026 U.S. Open are increasingly viewed as prime opportunities for business travelers to engage customers, partners, and teams, signaling a shift toward event‑centric business travel strategies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>2026-09-04T12:33:38.361Z</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>On track. On budget. On the go. Travel and Spend in one platform is coming to the US very soon! 🇺🇸
+Can you guess where these Perkers are based? Drop your best guess for this city in the comments 👇</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQEKewBZh1LlPw/mp4-720p-30fp-crf28/B4EaBsaIp.J4Bk-/0/1788525191969?e=1789135200&amp;v=beta&amp;t=AT2iNc43dwV-sOp1QruVE8jYKs-lprHt_f1J-qyxp34</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_on-track-on-budget-on-the-go-travel-and-activity-7501618477473083393-37aA</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>TravelPerk is announcing the upcoming launch of its integrated travel and spend platform in the US, engaging followers with a playful location guessing challenge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 23:26:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>@_crazdan @shaig @DoorDash Sorry about this,  Chaitenya. We’ve sent you a DM to get a few more details and figure out what’s going on.</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr"/>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2095654632588538264</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>Brex apologizes to a user for an issue and offers to resolve it via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 19:42:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>@GaddipatiHarsha We like the sound of that.</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2095598411684761791</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>Brex responds positively to a comment from @GaddipatiHarsha, indicating interest in the discussed topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Thu Sep 03 18:52:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>@troispio NYC from the water never misses.</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr"/>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2095585707200786558</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>Brex posted a brief statement referencing NYC from the water never misses, likely a lighthearted or promotional remark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 02:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>"Looking for a warm-weather getaway? ☀️
+➡️ The views: Discover black sand beaches and dramatic volcanic landscapes.
+➡️ The weather: Soak up the sun with year-round beautiful climate.
+➡️ The stays: Relax in oceanfront resorts offering all-inclusive luxury.
+Let us be your travel partner, making it easy to book everything all in one place.
+🔗 Plan your travel:
+https://t.co/lapxJyVrM0"</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2095693330164133965</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>Expedia promotes a warm‑weather getaway featuring black sand beaches, volcanic landscapes, and all‑inclusive oceanfront resorts, encouraging customers to book through their platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 13:25:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Hi there, for us to help you here, please share the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095865799298682891</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>Booking.com’s X post requests customer details for support and directs users to call their 24/7 customer service line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 13:17:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Hi Micky, we regret to hear that your flights have been cancelled. As much as we'd like to look into this, we're unable to assist with Flight reservations through social media. We can only encourage you to reach out to Flights team here: https://t.co/TBejpc4vOA, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677. They are the only team able to access your flight details</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095863792588505253</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user about a flight cancellation, explaining that flight issues cannot be handled via social media and directing the user to the dedicated Flights team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 12:24:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Hi Portia, we regret hearing you have received this message. We always recommend our travelers avoid clicking on external links. 
+To report this to the appropriate team, kindly DM us these details, and we'll get back to you as soon as possible: 
+- confirmation number 
+- PIN 
+- name on the reservation</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095850526164357255</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>Booking.com warns travelers to avoid clicking on external links and provides instructions to report suspicious messages, highlighting a phishing incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 12:07:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Olá Júlio, agradecemos pelo contato. Pelo conteúdo da sua mensagem, assumimos que você precisa de ajuda com alguma reserva de passagem. Por mais que quiséssemos ajudar, só conseguimos ajudar com reservas de acomodações aqui pelas redes sociais; pra obter devido suporte com a sua passagem, pedimos que entre em contato com a equipe dedicada aqui: https://t.co/OVuF5pCzba. Obrigado.</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095846190235459764</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user about flight booking support, directing them to a dedicated link for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 12:03:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>@nanacoco127 Respondimos tu mensaje privado, Marc.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095845310144622785</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @nanacoco127, acknowledging receipt of the message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 11:57:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Hi Will, for security reasons, we recommend our travelers avoid sharing their PIN in public, so we suggest you remove your message. 
+We regret hearing you are having these issues while traveling. For us to help you here, kindly DM us the details previously requested, and we'll get back to you as soon as possible. 
+Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095843658071171078</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s security concern, offering private support and a phone number for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 11:42:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Hi Dan, 
+You recently reached out to us in regards to your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please provide us with the following details :
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+Thank you.</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+      <c r="J535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095839934867218459</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>Booking.com is following up with a customer regarding a car rental reservation, requesting booking details for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 11:38:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Nous vous remercions pour votre retour. Nous regrettons d'apprendre les difficultés que vous rencontrez pour contacter le service client dédié aux vols. Conformément au RGPD, notre équipe spécialisée est la seule habilitée à accéder à vos données. Par conséquent, lorsque un voyageur nous contacte via les réseaux sociaux, nous ne pouvons que lui demander de se rapprocher de notre service spécialisé pour les vols, en lui fournissant les coordonnées que nous vous avons communiquées dans notre message précédent. 
+Nous comprenons que cette réponse puisse ne pas correspondre à vos attentes, mais seul le service dédié aux vols a la capacité d'accéder à votre réservation pour vous communiquer le statut de votre dossier.
+Cordialement</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095838989672452595</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about difficulty reaching flight customer service, citing GDPR restrictions and directing the user to a specialized flight support team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 11:23:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>@MissKirstyLeigh Hi Kirsty, we regret to hear that. You would need to speak to our flights team for help as our social media team does not assist with flight bookings. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr"/>
+      <c r="J537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095835106590044551</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s query about flight booking assistance, directing them to the flights team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 11:21:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Hi Will, we regret to hear you are having difficulty with your accommodation booking. Please, give more information as to what happened and confirm the following information so we can verify you: 
+- pin code
+- guest name 
+We will get back to you asap. Also, please bear in mind that our relocation procedure is very specific and can only be applied when the property confirms they cannot take the guest in. 
+In situations where you have issues with the host, the best thing is to request an early check out and see if they accept. Let us know if that would be also a solution in your case and confirm your date of check out. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
+      <c r="J538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095834509262426413</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about booking difficulties, requesting verification details and offering relocation or early check‑out options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 11:13:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Sentimos que tengas dificultades con la reserva. Si quieres que lo revisemos, envíanos un mensaje privado con los siguientes datos y nos pondremos en contacto contigo lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre que aparece en la reserva
+Como alternativa, si necesitas asistencia inmediata, siempre puedes llamarnos aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr"/>
+      <c r="J539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095832701374722242</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for booking difficulties and offers private message support or a phone call for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 11:13:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Hi Rich, thank you for contacting us regarding your Car Rental reservation, and we regret any inconvenience you encountered. In order for us to assist, please send us the following details:
+* Name of booker:
+* Email address used to book: 
+* Your request: 
+We'll get back to you as soon as we can.</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095832593962766842</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a car rental reservation, requesting details to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 10:44:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Sentimos que tengas dificultades con tu reserva, Marc. Por motivos de seguridad, envíanos un mensaje privado con el código PIN de la reserva y el nombre del huésped para revisarlo. 
+Como alternativa, si necesitas asistencia inmediata, siempre puedes llamarnos aquí: https://t.co/tuuNbmGVaG 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr"/>
+      <c r="J541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095825309664674276</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s reservation difficulty, directing them to send a private message with a PIN and guest name for secure review, and offers a phone link for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 09:04:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>@GraemeAlexpcm Hi Graeme, we've sent you a DM asking for more information. Please take a look when you can. Many thanks.</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr"/>
+      <c r="J542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095800240737513823</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to a user requesting them to review a direct message for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 09:04:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>@sethu210 Thank you for your reply. We have responded. Please check your DM.</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095800162236919948</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, thanking them for their reply and directing them to check their direct messages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 09:02:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Lamentamos tu situación y la tardanza en nuestra respuesta. No toleramos que nadie utilice el nombre de https://t.co/fGhmZE7riF para estafar, y queremos ayudarte a revisar lo ocurrido. Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095799638057972025</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a scam involving its name, offering assistance and contact details for affected users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 09:02:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>@Diaz__z Bonjour, nous vous remercions de nous avoir contactés. Nous vous avons envoyé un message privé. Merci de le consulter dès que possible.</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095799570701627902</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, thanking them for contacting and directing them to a private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 08:47:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Hi there Jayne, we already replied to one of your previous comments, not sure if you had the chance to see that - we offered to look into your booking, and if you'd like us to do that, feel free to send us a direct message with the following: 
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095795825997725716</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user’s inquiry about a booking, offering to review the reservation details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 08:42:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>@cookie525_ Hi there, we've replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr"/>
+      <c r="J547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095794720949543175</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, indicating ongoing customer engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 08:33:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>@Paul_Edwick Hi Paul, if you need any assistance feel free to DM us your confirmation number, pin code and the name of the guest on the booking and we will help you further.
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095792393647792563</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X offering assistance with booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O548"/>
+  <dimension ref="A1:O560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35521,6 +35521,859 @@
         </is>
       </c>
     </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>2026-09-04T17:09:49.000Z</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Puglia is where you come to decompress.
+It’s nestled perfectly between the Adriatic and Ionian seas. The heel of Italy’s boot. Puglia has it all: dramatic coastlines, crystal clear waters and plenty of natural beauty inland. Rent a car and plan a road trip. The beauty of Puglia is best experienced by driving down the coast and stopping at the picturesque towns along the way.
+Gaetano says the best thing about Puglia is the food and the people. If you’re planning a trip, plan for long lunches, afternoons by the water, and plenty of time in nature. 
+Save this for when you’re tired of olive oil.
+📍Corso Giuseppe Mazzini, Ostuni, Italy
+@burro_cafe is known for its tall, glorious mounds of house-made butter. It’s their specialty. It’s really good. It’s butter.
+Everyday there’s a new batch. Sometimes they decorate it with spices, herbs and flowers. Pile it high, spread it on fresh bread, and give the olive oil a rest.
+Northern Italy gets most of the truffle glory, but a new generation of foragers is quietly putting Puglia on the map.
+📍Valle d’Itria, Alberobello, Italy
+Follow @alta_murgiatartufi (and their two pups) into the Alta Murgia forest to hunt for rare summer truffles.
+Yes, it’s on @airbnbexperiences. And yes, you can book it now.
+Stay in Ostuni, Puglia’s iconic “White City” for easy access to the beach, the shops and the neighboring areas.
+📍Nido Cotugno, Ostuni, Italy
+Swap crowded resorts for a renovated farmhouse. Spend the night surrounded by ancient olive groves just ten minutes from the Adriatic sea.
+Have a beach day at Torre Pozzelle where dramatic, rocky coastlines meet crystal clear turquoise waters.
+📍Torre Pozzelle, Ostuni, Italy
+Get there early. Grab a spot near the cove. Soak up all of the Mediterranean sun. If you walk down far enough, you’ll find the 16th century watchtower that gives the beach its name.
+ @ceramiche_nicolafasano is worth the detour inland.
+📍Via Francesco Crispi, Grottaglie, Italy
+Potters in Grottaglie have been shaping clay into art since the Roman Empire, so it’s no wonder Grottaglie is considered southern Italy’s ceramic capital. 
+Visit @ceramiche_nicolafasano to see the work up close and buy one-of-a-kin</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>https://scontent-poa1-1.cdninstagram.com/v/t51.82787-15/794143081_18631049074063838_4698909413048785828_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3ODg5NjA4MDIxODk5MTg3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y83oV_M9l9sQ7kNvwFtVelK&amp;_nc_oc=AdrznXGxAQ_sDOekbLy3qX50owlIwfCISRWN8qlhavfN1EdMHY72o9NMBM5JIu_KdqA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-poa1-1.cdninstagram.com&amp;_nc_gid=eUA_E8rRtKwEoyTocbQ-lw&amp;_nc_ss=7a22e&amp;oh=00_AQKipF3mlsFcXDI_IMw0s-ZYHBUqApmFupXlJFkWrD318g&amp;oe=6AA0C7D3</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc34-YcFLat/</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>Airbnb is promoting Puglia, Italy as a new destination, highlighting local food, truffles, and scenic experiences to encourage bookings through its platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>2026-09-03T21:00:03.000Z</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Come here with a group and bring a couple of bathing suits. Spend the last warm days of summer laying out at the pool, lingering over long lunches, and soak up the Italian sun.</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>https://instagram.fmty2-1.fna.fbcdn.net/v/t51.82787-15/794295112_18630780727063838_7181620021584115318_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3ODI4NjMzODQ5MjY1MzM5MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Oesj8SMIxlsQ7kNvwFd4EU-&amp;_nc_oc=AdplzOHTT1LnO9R6YzoITTJ7tioo5189PAayOC9_Vk7LItioyFgFxJ1leA9ztnEm5yI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmty2-1.fna&amp;_nc_gid=Oj1ZIg417RvYSvSWlzjseA&amp;_nc_ss=7a22e&amp;oh=00_AQK_Q8PZ8t3OSzA3Dd-XJPImXNHPZUSyu5nV8IuXI6b9uA&amp;oe=6AA0DAA5</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr"/>
+      <c r="J550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc1uh30lE_e/</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>AirBnb promotes a summer getaway in Italy, encouraging groups to enjoy poolside relaxation, long lunches, and the Italian sun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>2026-09-03T19:14:01.591Z</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Jump into fall in Aspen with about 45% combined savings for lodging and flights compared to summer
+➡️ The views: Experience peak mountain drama and golden autumn foliage.
+➡️ The vibe: Enjoy cool, crisp weather and a polished alpine feel.
+➡️ The value: Score the strongest individual savings story in our fall outlook, leading mountain destinations where savings average 30%.
+Find out more here: http://ms.spr.ly/6043aKoLN</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQGitjht_fDZWQ/image-shrink_1280/B4EaBmHDO1IIAg-/0/1788419519680?e=1789153200&amp;v=beta&amp;t=Z5Bhklg1YZOdgweRmGwmKXl-58raHUKbtrVQ7uXLvT0</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr"/>
+      <c r="J551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_jump-into-fall-in-aspen-with-about-45-combined-activity-7501356850337144833--uqK</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>Expedia is promoting fall travel to Aspen, offering up to 45% combined savings on lodging and flights, emphasizing mountain scenery and average savings of 30% at peak destinations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 17:47:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Hi there, 
+Thank you for the update. We're glad to hear that the app is working again after you reinstalled it. 
+It does sound like the issue may have been a temporary glitch. We appreciate you sharing the steps you took to resolve it. Should the issue happen again, please let us know and provide any details you notice, such as any error messages, screenshots, or the actions you were taking when the problem occurred. We'll be happy to investigate it further. 
+Thank you for your patience, and we wish you a smooth experience moving forward. 
+Kind regards,</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr"/>
+      <c r="J552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095931880197534124</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user about a temporary app glitch, offering support and encouraging future issue reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 17:40:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>@King_ken0218 Hello, we have sent you a direct message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr"/>
+      <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr"/>
+      <c r="J553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095930091658199251</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>Booking.com sent a direct message to user @King_ken0218, requesting them to check the message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 17:21:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Hi there,
+Thank you for reaching out. We regret to hear that you're experiencing an emergency situation and understand how stressful and concerning this must be, especially if you're currently without accommodation or unable to contact us by phone.
+Please let us know what happened and why you require an emergency relocation. Any details you can provide will help us better understand the situation and assist you as quickly as possible.
+Kindly note that on https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they are responsible for keeping it accurate. If a property is unable to honor a booking, they should help arrange an alternative place to stay. If they are unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution.
+Please send us a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr"/>
+      <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr"/>
+      <c r="J554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095925229377790383</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s emergency relocation request, outlining steps for reporting the issue and clarifying property responsibilities for accommodation availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>2026-09-04T13:11:30.000Z</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>I needed some recreation from all my re-recreations. Thanks @bookingcom for the easy escape this fashion week.</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.71878-15/793868149_1100859975697056_2944137423294126514_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3ODc3ODgxNDQ0Mjc0ODYyNjkxMDU5NzI4MjEyMzgyNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjY0MC5zZHIudmlkZW9fbmZyYW1lX2NvdmVyX2ZyYW1lLkMzIn0%3D&amp;_nc_ohc=F6q5mU2DExUQ7kNvwHyH_ao&amp;_nc_oc=AdpVWuwHSwypbvLAHkOBQzNyf2JIpCVxW4r_DGuJCbGS9VkLJ2oA84HiwiVP41955SgJWWxj7BqgnBt7a_cRcWZx&amp;_nc_ad=z-m&amp;_nc_cid=1005&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=xyGE492JUZxjwxgmM5xUfg&amp;_nc_ss=7a22e&amp;oh=00_AQJ6ImIXeBfUta15FqEl_7CnZwJRhEknzwEmeeOvquuhmQ&amp;oe=6AA0DBB9</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>https://scontent-muc2-1.cdninstagram.com/o1/v/t2/f2/m86/AQMGwypVSVvCMIh1Cfz5-Ar8A_YLciJCMb0T5yH5v1aggduwHUz3gS4KctJWFUbO4Jk7JOpbokwIZd2iZGIbyB348PmV6KG5s-beYl0.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_ohc=UKDbol_em-cQ7kNvwGOak95&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6OTEwNTk2MzkyMTIzOTE1LCJhc3NldF9hZ2VfZGF5cyI6MCwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjM2LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=4914ad83b26b99f&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC83QjQyMUFDREQ0NURGNUI4Q0I3QjY3OTg5RTVFQUM5MF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU0NDBCMEQ0QzIwMENDODgyRkIzRTRGQTQzNjI1QjkxX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACaW-OPn14ueAxUCKAJDMywXQEI7peNT988YEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=xyGE492JUZxjwxgmM5xUfg&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQLzxURnvvavJnRfie1B5DAzgbVFVUMyim8VVoygXcIQMQ&amp;oe=6A9CDB50</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc3dkBStbrS/</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>A user praises Booking.com for facilitating an easy escape during fashion week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>2026-09-04T14:02:52.000Z</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>plenty of easy sleeper picks on booking.com
+📍 Petit Ermitage Hotel bookable on @bookingcom</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.71878-15/794992483_1774790400230780_2325747464096730963_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3ODgwNDI5MzkyNTE1Njk5NDE0MDg0MTUyNDM5NjAzMzA%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjY0MC5zZHIudmlkZW9fbmZyYW1lX2NvdmVyX2ZyYW1lLkMzIn0%3D&amp;_nc_ohc=ve1r5893qToQ7kNvwHLLAHb&amp;_nc_oc=Adriayx7QAVH8XDyIzK6FeF_Xi6BD-scCoz-ittngzvf1ZVGBO0Sr1PB8wvIxkDUdc4gADbT3ls6Y3eLgXQD3EqK&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=dygXexafpX9EHtMwW43H7A&amp;_nc_ss=7a22e&amp;oh=00_AQLILPzsK1JRiKzIEY_VnKpttoZLVhW19KpnPxtLkfTaGA&amp;oe=6AA0CA89</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>https://scontent-mad2-1.cdninstagram.com/o1/v/t2/f2/m86/AQMCtijIWlZTr0BpgiO_Aidi14dRTvQvkHOqywST22-fl5-o6qsPDxxh4F_rmfzNbO9nx7NbKQIN25IPdnYRcVqeyxvla6ZsGwNnBQM.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_ohc=LQ9xfHAf77MQ7kNvwGS4YsV&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTQwODQxMzcyMzk2MDQ4MiwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozNSwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4a0afe82885d39e8&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC84MjQ4MURCQUJCRDNBMzM4QjdFMjA2MDc4MTg5QUJCOF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlDNDJBMkM1Mjk5QjAyOTc0NEExQjlFRDBCQjVGRjlCX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbEkrX7u7yABRUCKAJDMywXQEH3bItDlYEYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=dygXexafpX9EHtMwW43H7A&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQLEYv796JleUdM-emtfeXPiacwbsj7BS923HwL590tEsg&amp;oe=6A9CE6DC</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc3jWy6NTiC/</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>Booking.com promotes its new easy sleeper listings, featuring the Petit Ermitage Hotel as a highlighted option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>2026-09-04T13:32:06.000Z</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Some things deserve over-analysis. MLB Postseason is one of them😂⚾️The escape? Keep that part easy✈️
+📍 Hollywood Grande Hotel bookable on @bookingcom</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>https://instagram.fitm1-1.fna.fbcdn.net/v/t51.71878-15/793867328_833834303088586_960396909552453710_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk3ODc4ODk0NjMwNDIzMzg2NTEwOTQxMzYyOTAyMjUxNjQ%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjY0MC5zZHIudmlkZW9fbmZyYW1lX2NvdmVyX2ZyYW1lLkMzIn0%3D&amp;_nc_ohc=9XXVDksITioQ7kNvwGU2J-W&amp;_nc_oc=AdrdzL-uV7NSLhxLlAuSlZjkkWH7PJd_fiRmcDSWjGnq3hipoMFpP32SFdc9ezQQ5zK3SGimz-iXMTRHNJ4D9uyv&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fitm1-1.fna&amp;_nc_gid=Z8rzwsQ5EL2dhWfuCxEClg&amp;_nc_ss=7a22e&amp;oh=00_AQJwNSHmW7BsiqSFDmmLyDvemtkGo-WBMz57J4SzSsQxPA&amp;oe=6AA0D076</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>https://instagram.fitm5-1.fna.fbcdn.net/o1/v/t2/f2/m367/AQMmgbx-4cxMTIZfeYyHTltxDO_sFURS8yo897GKQfpdBpJ58kdVilPBze1_0UEVbEtXHzRFNunnFNI4LoGB2HKM2V3cUHgJatv9CSY.mp4?_nc_cat=103&amp;_nc_oc=AdozS5mnVKTBzicPbz98xyZRARE0GmXcXWsRyNkWmAvkRgVfdkwgOsuKt1J7TxWqmH7mmHrx_ycUPwyR_hzO9UBy&amp;_nc_sid=9ca052&amp;_nc_ht=instagram.fitm5-1.fna.fbcdn.net&amp;_nc_ohc=lStBsxKiWN8Q7kNvwGmyZZh&amp;efg=eyJ2ZW5jb2RlX3RhZyI6ImlnLXhwdmRzLmNsaXBzLmMyLUMzLmRhc2hfcjJldmV2cDktcjFnZW4ydnA5X3E5MCIsInZpZGVvX2lkIjpudWxsLCJvaWxfdXJsZ2VuX2FwcF9pZCI6OTM2NjE5NzQzMzkyNDU5LCJjbGllbnRfbmFtZSI6ImlnIiwieHB2X2Fzc2V0X2lkIjoxMDk0MTM1MDUzNTU4NjIxLCJhc3NldF9hZ2VfZGF5cyI6MCwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjM5LCJiaXRyYXRlIjoyOTY3MTAxLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;_nc_gid=Z8rzwsQ5EL2dhWfuCxEClg&amp;_nc_map=urlgen_bucketless&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQIwhoMZazakK4rVc4L5WvbFpV4WFnoU3Lope4tcVFEr9Q&amp;oe=6AA0C9D8</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc3f3dUtvGJ/</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>Booking.com promotes the Hollywood Grande Hotel as a convenient lodging option for travelers attending the MLB postseason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 16:29:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>We couldn't have won gold at last year’s Travvy Awards without you. We're nominated again for #BestAirlineConsolidator at the 2026 awards!  
+Voting closes on September 4, so click the link to vote for us!  https://t.co/e7UaSda3Eg 
+#TravvyAwards2026 #VoteForSkyBird https://t.co/lKbIDE5wvX</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
+      <c r="J558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2095912122219942201</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel announces its nomination for Best Airline Consolidator at the 2026 Travvy Awards and urges followers to vote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>2026-09-04T16:32:50.615Z</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>We couldn't have won gold at last year’s Travvy Awards without you. We're nominated again for Best Airline Consolidator at the 2026 awards!  
+Voting closes on September 4, so click the link to vote for us! https://lnkd.in/eQAs2phh 
+#TravvyAwards2026 #VoteForSkyBird #BestAirlineConsolidator</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQHiO62X_Mwb9w/feedshare-shrink_1280/B4EaBtRABYG8AM-/0/1788539568843?e=1790208000&amp;v=beta&amp;t=s6opc0pyMbpsS9rVgLw6cNgEL9FEgDNVBqWzym469s4</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr"/>
+      <c r="J559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_travvyawards2026-voteforskybird-bestairlineconsolidator-activity-7501678675189211137-90z6</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel celebrates its previous Travvy Awards win and announces a new nomination for Best Airline Consolidator, encouraging supporters to vote before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 18:14:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>@MihirKapurbxks Hi Mihir, we have sent you a private message. Please check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr"/>
+      <c r="H560" t="inlineStr"/>
+      <c r="I560" t="inlineStr"/>
+      <c r="J560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2095938629755404619</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents sent a private message to user MihirKapurbxks.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O560"/>
+  <dimension ref="A1:O584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36374,6 +36374,1543 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Fri Sep 04 23:07:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>@harshil1712 @jamesqquick @OpenAI We've got good news...The Navan MCP is alive and well. in fact, submitting expenses is coming very soon. Check out what users and admins can do with the MCP at https://t.co/Xc730pcBIZ</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr"/>
+      <c r="H561" t="inlineStr"/>
+      <c r="I561" t="inlineStr"/>
+      <c r="J561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2096012287987339537</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>Navan announces that its MCP is live and will soon enable expense submission for users and admins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Your next great adventure is waiting in Ireland ☘️
+➡️ The views: Drive the wild, rugged cliffs along the stunning coastline.
+➡️ The culture: Grab a pint, listen to live music, and meet friendly locals.
+➡️ The stays: Rest up in a historic castle or a cozy countryside inn.
+🔗 Plan your travel:
+https://t.co/d3GsyZX2YM</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr"/>
+      <c r="H562" t="inlineStr"/>
+      <c r="I562" t="inlineStr"/>
+      <c r="J562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2096025517581332495</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a travel package to Ireland, highlighting scenic views, local culture, and accommodation options to encourage bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 12:55:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that you are not able to reach our customer service. If a hotel can’t honor a bookingdue to a power outage, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution. Please DM us the following details: 
+- Confirmation number 
+- Pin code: 
+- Name of guest 
+and we will get back to you.</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr"/>
+      <c r="H563" t="inlineStr"/>
+      <c r="I563" t="inlineStr"/>
+      <c r="J563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096220642727076025</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for customer service difficulties and offers to resolve booking issues caused by power outages, requesting details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 12:43:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>@court_neliast Hi Courtney, thank you for reaching out to us. We've replied to your DM, please check it out when you have a moment. Have a nice day!</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="inlineStr"/>
+      <c r="I564" t="inlineStr"/>
+      <c r="J564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096217570319749449</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, thanking them and directing them to check their DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 09:28:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Hi Larisa, 
+We regret to learn about your experience; we are here to help. 
+To protect your privacy, we suggest deleting all messages displaying your reservation number. 
+You can share with us your booking information in a private message, so we can have a look: 
+- reservation number 
+- PIN code 
+- guest name on the booking. 
+We will check and get back to you as soon as we can.
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/tuuNbmGVaG. 
+Kind regards</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
+      <c r="J565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096168509122175427</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering private assistance and directing to 24/7 support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 08:30:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Hi Danijel, thank you for contacting us regarding your Car Rental reservation.
+In order for us to assist, please send us a private message with the following details:
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr"/>
+      <c r="J566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096153987380597168</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer’s inquiry about a car rental reservation, providing instructions for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 07:01:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>@MihirKapurbxks Hi Mihir, we have sent you a private message. Kindly take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr"/>
+      <c r="J567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096131609200062696</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user MihirKapurbxks, asking them to check it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 06:49:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>@KriveTravel Hi there, we replied to you in private. Check your DMs!</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr"/>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr"/>
+      <c r="J568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096128522561388894</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, directing them to check their DMs for a private response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 01:38:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out, and we regret any inconvenience this has caused. However, at https://t.co/fGhmZE7riF, we provide an online platform where properties can advertise their services. When you book a reservation, you're entering a direct and legally binding contract with the accommodation provider. From that moment, we stand as an intermediary between you both.
+If you need any support, please send us a private message with the following details:
+Confirmation number: 
+Pin code: 
+Name on the reservation: 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Once we receive the requested details, we will be pleased to check them for you. Thank you for your patience and understanding. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr"/>
+      <c r="J569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096050237802459345</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry, clarifying that bookings are direct contracts with providers and directing the user to their 24/7 support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 01:23:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>@sitimajnr Hi there, thank you for reaching out to us. However, for security purposes, we are unable to offer support to our partners via social media. You can find the contact information for our Partner Support team here: https://t.co/oK8asfsShG https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr"/>
+      <c r="I570" t="inlineStr"/>
+      <c r="J570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096046484655399036</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>Booking.com informs partners that it cannot provide support via social media and directs them to its Partner Support contact information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 01:21:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret to hear about the reported flight cancellations affecting your travel plans. Unfortunately, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr"/>
+      <c r="I571" t="inlineStr"/>
+      <c r="J571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096046054789583060</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user about flight cancellations, directing them to the Flights team and providing contact information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 01:11:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Hi David, thank you for reaching out. We understand your concern, especially after receiving messages that appear to be asking for payment verification. Please note that they could not gain access to your payment information. We advise that you do not click on any links contained in these messages and do not make any payments.
+For us to help you here, please send us the following information via private message, and we'll get back to you soon.
+• Confirmation number 
+• PIN code 
+• Name on the reservation 
+Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/TBejpc4vOA.</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr"/>
+      <c r="H572" t="inlineStr"/>
+      <c r="I572" t="inlineStr"/>
+      <c r="J572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096043453155004651</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>Booking.com cautions users about potential phishing messages requesting payment verification, advises against sharing personal details, and directs them to secure support channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 01:01:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for getting back to us. We understand your concern, especially after waiting on hold and being advised that the reservation was canceled internally without receiving further details regarding the reason. 
+As previously communicated, for us to verify the reservation and review what happened, please send us a direct message with the following details: 
+• Confirmation number: 
+• PIN code: 
+• Name on the reservation: 
+Once we receive these details, we'll look into this further for you.</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
+      <c r="J573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096040882063458375</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s concern about a canceled reservation, asking for confirmation details via direct message to investigate further.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 01:00:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>@DavidJo80860848 Hi there,
+We have replied to your private message. Kindly review it at your convenience.
+Thank you, and we look forward to your response.
+Kind regards, https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr"/>
+      <c r="H574" t="inlineStr"/>
+      <c r="I574" t="inlineStr"/>
+      <c r="J574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096040744376991899</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, offering assistance and inviting a review of the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:49:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Hi there, we regret your experience as you claim that the property you booked is a fake listing, and you were already charged. The properties have to pass a verification process to appear listed on our platform. If a property provides false or incorrect information, we investigate and take the necessary actions. 
+If you'd like us to take a look at your reservation or the accommodation provider, please DM us with the following:
+- Confirmation number:
+- PIN code:
+- Guest name on reservation:</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr"/>
+      <c r="I575" t="inlineStr"/>
+      <c r="J575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096037892078346505</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a fake listing, offering to investigate and requesting reservation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:45:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>@MilliRogers3 Hi Mili, we have sent you a private message. Kindly take a moment to check it. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr"/>
+      <c r="I576" t="inlineStr"/>
+      <c r="J576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096036898233798996</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @MilliRogers3, inviting them to check a link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:35:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>@Michael_Trtv Hi Michael, thank you for your message. We have sent you a private message with further details. Please check your inbox at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr"/>
+      <c r="H577" t="inlineStr"/>
+      <c r="I577" t="inlineStr"/>
+      <c r="J577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096034472583967162</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry, directing them to a private message for further details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:35:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Hi Daniele, thank you for flagging this. We regret the worry and frustration this situation has caused. We understand how alarming it must feel to receive private messages with suspicious links asking for sensitive details. The properties provide the information on our website and have to pass a verification procedure before becoming bookable. If we find that a property listed on our platform is providing false information, we investigate immediately, give them the opportunity to rectify, or we may remove them from our website accordingly.
+For us to check this, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr"/>
+      <c r="J578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096034339993563374</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about suspicious links, apologizes for the issue, offers to investigate and remove false listings, and provides contact details for further support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:19:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out to us. We regret to hear that the property is unable to accommodate your stay and asked you to cancel the reservation yourself. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+If a property can’t honor a booking, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible, so we can help find a solution. Please send a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr"/>
+      <c r="H579" t="inlineStr"/>
+      <c r="I579" t="inlineStr"/>
+      <c r="J579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096030531427184644</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint about a property failing to honor a reservation, offering assistance in finding alternative accommodation and providing contact details for support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:12:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Hi Navni, thank you for reaching out. We regret to hear that you're unable to send us a direct message. 
+As a basic troubleshooting step, please try logging out of your account, clearing your browser's cache and cookies (or updating/reinstalling the app), and then logging back in. You may also try accessing your account from a different device or browser. If the issue continues, please let us know so we can assist you further.</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr"/>
+      <c r="H580" t="inlineStr"/>
+      <c r="I580" t="inlineStr"/>
+      <c r="J580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096028778698813726</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s login issue by offering troubleshooting steps such as logging out, clearing cache, and trying a different device or browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:06:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Hi there, we regret that you weren't able to get the information you needed about wheelchair accessibility. If this is related to an accommodation booking, please send us the following details via private message and let us know how we can help:
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/fGhmZE7riF: The largest selection of hotels, homes, and vacation rentals.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/fGhmZE7riF: The largest selection of hotels, homes, and vacation rentals.</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="inlineStr"/>
+      <c r="I581" t="inlineStr"/>
+      <c r="J581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096027030273814653</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>Booking.com is informing users that wheelchair accessibility inquiries can be handled via private message or 24/7 phone support, and that social media assistance is limited to accommodation bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 00:03:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>We regret hearing about your negative experienced. We always suggest communicating any issues directly to the property while you are there, as they are in the best position to address and resolve any concerns.
+For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your stay:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr"/>
+      <c r="I582" t="inlineStr"/>
+      <c r="J582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096026444358926525</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s negative experience by advising direct communication with the property and offering private messaging for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 13:13:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Hi Renjith, thanks for your message,
+All the information on our website, including photos, listed facilities, room descriptions, rates, and policies, is set by the accommodations themselves, and it is their responsibility to ensure this is updated to correctly reflect their property. That is why we always recommend our travelers discuss any issues upon arrival or during their stay, as it is in the property’s best interest to make your stay as comfortable as possible. In addition, checking recent comments and review scores is the best indicator of what you can expect from the property you have booked.
+We have replied to your DM once again with further clarification, please review it whenever you have time.
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr"/>
+      <c r="H583" t="inlineStr"/>
+      <c r="I583" t="inlineStr"/>
+      <c r="J583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096225125695684610</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies that property owners are responsible for updating listings and advises travelers to address issues directly with accommodations, emphasizing the importance of reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 13:08:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Hi Shubham, we appreciate you reaching out to us. We regret to hear that you are dissatisfied with our response. Regarding this reservation, we did not manage the payment, and we trust that you were able to inform the property directly about any issues if you were there, as they are best equipped to handle and resolve such matters. If you wish to expedite this process, you can send the proof of the charge and any photos to (conf.number)@my.booking.com. Thank you.</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr"/>
+      <c r="H584" t="inlineStr"/>
+      <c r="I584" t="inlineStr"/>
+      <c r="J584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096223863700963505</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a dissatisfied customer’s complaint, offering to expedite resolution by requesting proof of charge and photos.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O584"/>
+  <dimension ref="A1:O589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37911,6 +37911,314 @@
         </is>
       </c>
     </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 15:23:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>@doddy36 We're happy to hear that, and please don't hesitate to send us a private message if you need further assistance. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr"/>
+      <c r="H585" t="inlineStr"/>
+      <c r="I585" t="inlineStr"/>
+      <c r="J585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096257890239615388</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user on X, expressing happiness and offering further assistance via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 14:28:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>@MubeenShaikhUDG Hi there, 
+We cannot disclose any details regarding your inquiry due to data protection regulations. Please check our DM whenever you have time, as we have already provided an explanation there.
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr"/>
+      <c r="H586" t="inlineStr"/>
+      <c r="I586" t="inlineStr"/>
+      <c r="J586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096244170595672272</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry, explaining that it cannot disclose details publicly due to data protection regulations and directing the user to review the private message for further information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 13:45:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>@shubh_patil_64 Thank you for your message. Kindly review our last DM, as we have already informed you about the details of your reservation. 
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr"/>
+      <c r="J587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096233214645813673</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user’s inquiry about reservation details, directing them to review a previous direct message for the information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 13:32:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>@DrAlongeAJ Hi Ayodele, thank you for reaching out to us. We have replied to your DM, please have a look at your inbox when you have a moment. Have a nice day!</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr"/>
+      <c r="H588" t="inlineStr"/>
+      <c r="I588" t="inlineStr"/>
+      <c r="J588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096230057970655490</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, acknowledging receipt and directing them to check their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Sat Sep 05 13:30:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>@MihirKapurbxks Hi Mihir, we have just responded to your private message. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr"/>
+      <c r="J589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2096229392829542574</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @MihirKapurbxks.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
